--- a/research/traditional_assets/database/data/indonesia/indonesia_education.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_education.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="idx_idea" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,88 +590,97 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.5961904761904762</v>
+        <v>0.4584681769147788</v>
       </c>
       <c r="H2">
-        <v>0.5961904761904762</v>
+        <v>0.4584681769147788</v>
       </c>
       <c r="I2">
-        <v>0.4895238095238095</v>
+        <v>0.02481121898597627</v>
       </c>
       <c r="J2">
-        <v>0.4838426821405545</v>
+        <v>0.02481121898597627</v>
       </c>
       <c r="K2">
-        <v>0.511</v>
+        <v>-0.123</v>
       </c>
       <c r="L2">
-        <v>0.4866666666666666</v>
+        <v>-0.1326860841423948</v>
       </c>
       <c r="M2">
-        <v>0.646</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.08044831880448319</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.264187866927593</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.646</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.08044831880448319</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.264187866927593</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.787</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.1300826446280992</v>
       </c>
       <c r="X2">
-        <v>0.07381688115883998</v>
+        <v>0.1242355807796863</v>
       </c>
       <c r="AB2">
-        <v>0.07381688115883998</v>
+        <v>0.1152226191017578</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>0.4129999999999999</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.1655172413793103</v>
+      </c>
+      <c r="AI2">
+        <v>0.2247191011235955</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>0.06390221259477022</v>
+      </c>
+      <c r="AK2">
+        <v>0.09070942235888424</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>4.979253112033195</v>
+      </c>
+      <c r="AO2">
+        <v>0.1597222222222222</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.713692946058091</v>
+      </c>
+      <c r="AQ2">
+        <v>0.1608391608391609</v>
       </c>
     </row>
     <row r="3">
@@ -689,87 +700,8808 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5961904761904762</v>
+        <v>0.4584681769147788</v>
       </c>
       <c r="H3">
-        <v>0.5961904761904762</v>
+        <v>0.4584681769147788</v>
       </c>
       <c r="I3">
-        <v>0.4895238095238095</v>
+        <v>0.02481121898597627</v>
       </c>
       <c r="J3">
-        <v>0.4838426821405545</v>
+        <v>0.02481121898597627</v>
       </c>
       <c r="K3">
-        <v>0.511</v>
+        <v>-0.123</v>
       </c>
       <c r="L3">
-        <v>0.4866666666666666</v>
+        <v>-0.1326860841423948</v>
       </c>
       <c r="M3">
-        <v>0.646</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.08044831880448319</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.264187866927593</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.646</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.08044831880448319</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.264187866927593</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>0.787</v>
+      </c>
+      <c r="V3">
+        <v>0.1300826446280992</v>
+      </c>
+      <c r="X3">
+        <v>0.1242355807796863</v>
+      </c>
+      <c r="AB3">
+        <v>0.1152226191017578</v>
+      </c>
+      <c r="AD3">
+        <v>1.2</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1.2</v>
+      </c>
+      <c r="AG3">
+        <v>0.4129999999999999</v>
+      </c>
+      <c r="AH3">
+        <v>0.1655172413793103</v>
+      </c>
+      <c r="AI3">
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="AJ3">
+        <v>0.06390221259477022</v>
+      </c>
+      <c r="AK3">
+        <v>0.09070942235888424</v>
+      </c>
+      <c r="AL3">
+        <v>0.144</v>
+      </c>
+      <c r="AM3">
+        <v>0.143</v>
+      </c>
+      <c r="AN3">
+        <v>4.979253112033195</v>
+      </c>
+      <c r="AO3">
+        <v>0.1597222222222222</v>
+      </c>
+      <c r="AP3">
+        <v>1.713692946058091</v>
+      </c>
+      <c r="AQ3">
+        <v>0.1608391608391609</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PT Idea Indonesia Akademi Tbk (IDX:IDEA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IDX:IDEA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.16551724137931</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>6.05</v>
+      </c>
+      <c r="H2">
+        <v>7.47315938610576</v>
+      </c>
+      <c r="I2">
+        <v>6.463</v>
+      </c>
+      <c r="J2">
+        <v>6.75865938610576</v>
+      </c>
+      <c r="K2">
+        <v>1.2</v>
+      </c>
+      <c r="L2">
+        <v>0.0725</v>
+      </c>
+      <c r="M2">
+        <v>0.115222619101758</v>
+      </c>
+      <c r="N2">
+        <v>0.111879490922422</v>
+      </c>
+      <c r="O2">
+        <v>0.0697822706422018</v>
+      </c>
+      <c r="P2">
+        <v>0.04675</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.124235580779686</v>
+      </c>
+      <c r="T2">
+        <v>0.112537364568103</v>
+      </c>
+      <c r="U2">
+        <v>0.928592842891767</v>
+      </c>
+      <c r="V2">
+        <v>0.801445818788443</v>
+      </c>
+      <c r="W2">
+        <v>5.768025078369905</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>6.05</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.08209678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.241</v>
+      </c>
+      <c r="AH2">
+        <v>0.218</v>
+      </c>
+      <c r="AI2">
+        <v>1.213</v>
+      </c>
+      <c r="AJ2">
+        <v>1.2</v>
+      </c>
+      <c r="AK2">
+        <v>1.2</v>
+      </c>
+      <c r="AL2">
+        <v>0.144</v>
+      </c>
+      <c r="AM2">
+        <v>1.2</v>
+      </c>
+      <c r="AN2">
+        <v>0.787</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1119096554055307</v>
+      </c>
+      <c r="C2">
+        <v>7.542870815078361</v>
+      </c>
+      <c r="D2">
+        <v>6.755870815078361</v>
+      </c>
+      <c r="E2">
+        <v>-1.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.787</v>
+      </c>
+      <c r="H2">
+        <v>6.05</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.241</v>
+      </c>
+      <c r="K2">
+        <v>0.218</v>
+      </c>
+      <c r="L2">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.003449999999999997</v>
+      </c>
+      <c r="P2">
+        <v>0.01954999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>0.23755</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1119096554055307</v>
+      </c>
+      <c r="T2">
+        <v>0.7946232955438741</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1118794909224224</v>
+      </c>
+      <c r="C3">
+        <v>7.473159386105761</v>
+      </c>
+      <c r="D3">
+        <v>6.75865938610576</v>
+      </c>
+      <c r="E3">
+        <v>-1.1275</v>
+      </c>
+      <c r="F3">
+        <v>0.0725</v>
+      </c>
+      <c r="G3">
+        <v>0.787</v>
+      </c>
+      <c r="H3">
+        <v>6.05</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.241</v>
+      </c>
+      <c r="K3">
+        <v>0.218</v>
+      </c>
+      <c r="L3">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.0039875</v>
+      </c>
+      <c r="N3">
+        <v>0.01901249999999999</v>
+      </c>
+      <c r="O3">
+        <v>0.002851874999999998</v>
+      </c>
+      <c r="P3">
+        <v>0.016160625</v>
+      </c>
+      <c r="Q3">
+        <v>0.234160625</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1125373645681035</v>
+      </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.8014458187884428</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0.07381688115883998</v>
-      </c>
-      <c r="AB3">
-        <v>0.07381688115883998</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.04675000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>5.768025078369905</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1144128344765315</v>
+      </c>
+      <c r="C4">
+        <v>7.174216265586002</v>
+      </c>
+      <c r="D4">
+        <v>6.532216265586002</v>
+      </c>
+      <c r="E4">
+        <v>-1.055</v>
+      </c>
+      <c r="F4">
+        <v>0.145</v>
+      </c>
+      <c r="G4">
+        <v>0.787</v>
+      </c>
+      <c r="H4">
+        <v>6.05</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.241</v>
+      </c>
+      <c r="K4">
+        <v>0.218</v>
+      </c>
+      <c r="L4">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.028507</v>
+      </c>
+      <c r="N4">
+        <v>-0.005507000000000005</v>
+      </c>
+      <c r="O4">
+        <v>-0.0008260500000000003</v>
+      </c>
+      <c r="P4">
+        <v>-0.004680950000000005</v>
+      </c>
+      <c r="Q4">
+        <v>0.21331905</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1132211189239765</v>
+      </c>
+      <c r="T4">
+        <v>0.8088774929851348</v>
+      </c>
+      <c r="U4">
+        <v>0.1966</v>
+      </c>
+      <c r="V4">
+        <v>0.1210229066545058</v>
+      </c>
+      <c r="W4">
+        <v>0.1728068965517242</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>0.8068193776967059</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1172881061008758</v>
+      </c>
+      <c r="C5">
+        <v>6.862420186147157</v>
+      </c>
+      <c r="D5">
+        <v>6.292920186147157</v>
+      </c>
+      <c r="E5">
+        <v>-0.9824999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.2175</v>
+      </c>
+      <c r="G5">
+        <v>0.787</v>
+      </c>
+      <c r="H5">
+        <v>6.05</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.241</v>
+      </c>
+      <c r="K5">
+        <v>0.218</v>
+      </c>
+      <c r="L5">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.051939</v>
+      </c>
+      <c r="N5">
+        <v>-0.02893900000000001</v>
+      </c>
+      <c r="O5">
+        <v>-0.004340849999999999</v>
+      </c>
+      <c r="P5">
+        <v>-0.02459815000000001</v>
+      </c>
+      <c r="Q5">
+        <v>0.19340185</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1140205857421044</v>
+      </c>
+      <c r="T5">
+        <v>0.817566837151442</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>0.06642407439496327</v>
+      </c>
+      <c r="W5">
+        <v>0.2229379310344828</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.4428271626330886</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1192881061008758</v>
+      </c>
+      <c r="C6">
+        <v>6.63355123945433</v>
+      </c>
+      <c r="D6">
+        <v>6.13655123945433</v>
+      </c>
+      <c r="E6">
+        <v>-0.9099999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.29</v>
+      </c>
+      <c r="G6">
+        <v>0.787</v>
+      </c>
+      <c r="H6">
+        <v>6.05</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.241</v>
+      </c>
+      <c r="K6">
+        <v>0.218</v>
+      </c>
+      <c r="L6">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.06925199999999999</v>
+      </c>
+      <c r="N6">
+        <v>-0.046252</v>
+      </c>
+      <c r="O6">
+        <v>-0.006937799999999996</v>
+      </c>
+      <c r="P6">
+        <v>-0.03931420000000001</v>
+      </c>
+      <c r="Q6">
+        <v>0.1786858</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1148041335102514</v>
+      </c>
+      <c r="T6">
+        <v>0.8260831583717696</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>0.04981805579622245</v>
+      </c>
+      <c r="W6">
+        <v>0.2269034482758621</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.3321203719748166</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1212881061008758</v>
+      </c>
+      <c r="C7">
+        <v>6.41226491062409</v>
+      </c>
+      <c r="D7">
+        <v>5.98776491062409</v>
+      </c>
+      <c r="E7">
+        <v>-0.8374999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.3625</v>
+      </c>
+      <c r="G7">
+        <v>0.787</v>
+      </c>
+      <c r="H7">
+        <v>6.05</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.241</v>
+      </c>
+      <c r="K7">
+        <v>0.218</v>
+      </c>
+      <c r="L7">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.08656500000000002</v>
+      </c>
+      <c r="N7">
+        <v>-0.06356500000000002</v>
+      </c>
+      <c r="O7">
+        <v>-0.009534749999999998</v>
+      </c>
+      <c r="P7">
+        <v>-0.05403025000000003</v>
+      </c>
+      <c r="Q7">
+        <v>0.16396975</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1156041770208856</v>
+      </c>
+      <c r="T7">
+        <v>0.8347787705651566</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.03985444463697795</v>
+      </c>
+      <c r="W7">
+        <v>0.2292827586206897</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.2656962975798531</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1232881061008758</v>
+      </c>
+      <c r="C8">
+        <v>6.19802271312531</v>
+      </c>
+      <c r="D8">
+        <v>5.84602271312531</v>
+      </c>
+      <c r="E8">
+        <v>-0.7649999999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.435</v>
+      </c>
+      <c r="G8">
+        <v>0.787</v>
+      </c>
+      <c r="H8">
+        <v>6.05</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.241</v>
+      </c>
+      <c r="K8">
+        <v>0.218</v>
+      </c>
+      <c r="L8">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.103878</v>
+      </c>
+      <c r="N8">
+        <v>-0.08087800000000001</v>
+      </c>
+      <c r="O8">
+        <v>-0.01213169999999999</v>
+      </c>
+      <c r="P8">
+        <v>-0.06874630000000001</v>
+      </c>
+      <c r="Q8">
+        <v>0.1492537</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1164212427338737</v>
+      </c>
+      <c r="T8">
+        <v>0.843659395783935</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.03321203719748164</v>
+      </c>
+      <c r="W8">
+        <v>0.2308689655172414</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.2214135813165443</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1252881061008758</v>
+      </c>
+      <c r="C9">
+        <v>5.990335969498233</v>
+      </c>
+      <c r="D9">
+        <v>5.710835969498233</v>
+      </c>
+      <c r="E9">
+        <v>-0.6924999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.5075000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.787</v>
+      </c>
+      <c r="H9">
+        <v>6.05</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.241</v>
+      </c>
+      <c r="K9">
+        <v>0.218</v>
+      </c>
+      <c r="L9">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.121191</v>
+      </c>
+      <c r="N9">
+        <v>-0.09819100000000003</v>
+      </c>
+      <c r="O9">
+        <v>-0.01472865</v>
+      </c>
+      <c r="P9">
+        <v>-0.08346235000000003</v>
+      </c>
+      <c r="Q9">
+        <v>0.13453765</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1172558797525175</v>
+      </c>
+      <c r="T9">
+        <v>0.8527310021902138</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.02846746045498425</v>
+      </c>
+      <c r="W9">
+        <v>0.2320019704433498</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.1897830696998951</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1272881061008758</v>
+      </c>
+      <c r="C10">
+        <v>5.788760182454311</v>
+      </c>
+      <c r="D10">
+        <v>5.581760182454311</v>
+      </c>
+      <c r="E10">
+        <v>-0.62</v>
+      </c>
+      <c r="F10">
+        <v>0.58</v>
+      </c>
+      <c r="G10">
+        <v>0.787</v>
+      </c>
+      <c r="H10">
+        <v>6.05</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.241</v>
+      </c>
+      <c r="K10">
+        <v>0.218</v>
+      </c>
+      <c r="L10">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.138504</v>
+      </c>
+      <c r="N10">
+        <v>-0.115504</v>
+      </c>
+      <c r="O10">
+        <v>-0.01732559999999999</v>
+      </c>
+      <c r="P10">
+        <v>-0.0981784</v>
+      </c>
+      <c r="Q10">
+        <v>0.1198216</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1181086610541753</v>
+      </c>
+      <c r="T10">
+        <v>0.8619998174314117</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.02490902789811122</v>
+      </c>
+      <c r="W10">
+        <v>0.2328517241379311</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.1660601859874082</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1292881061008758</v>
+      </c>
+      <c r="C11">
+        <v>5.592890152447676</v>
+      </c>
+      <c r="D11">
+        <v>5.458390152447675</v>
+      </c>
+      <c r="E11">
+        <v>-0.5475</v>
+      </c>
+      <c r="F11">
+        <v>0.6525</v>
+      </c>
+      <c r="G11">
+        <v>0.787</v>
+      </c>
+      <c r="H11">
+        <v>6.05</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.241</v>
+      </c>
+      <c r="K11">
+        <v>0.218</v>
+      </c>
+      <c r="L11">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.155817</v>
+      </c>
+      <c r="N11">
+        <v>-0.132817</v>
+      </c>
+      <c r="O11">
+        <v>-0.01992254999999999</v>
+      </c>
+      <c r="P11">
+        <v>-0.11289445</v>
+      </c>
+      <c r="Q11">
+        <v>0.10510555</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1189801848020234</v>
+      </c>
+      <c r="T11">
+        <v>0.871472342897691</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.02214135813165442</v>
+      </c>
+      <c r="W11">
+        <v>0.2335126436781609</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.1476090542110295</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1312881061008758</v>
+      </c>
+      <c r="C12">
+        <v>5.402355728724169</v>
+      </c>
+      <c r="D12">
+        <v>5.34035572872417</v>
+      </c>
+      <c r="E12">
+        <v>-0.4749999999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.7250000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.787</v>
+      </c>
+      <c r="H12">
+        <v>6.05</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.241</v>
+      </c>
+      <c r="K12">
+        <v>0.218</v>
+      </c>
+      <c r="L12">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M12">
+        <v>0.17313</v>
+      </c>
+      <c r="N12">
+        <v>-0.15013</v>
+      </c>
+      <c r="O12">
+        <v>-0.02251949999999999</v>
+      </c>
+      <c r="P12">
+        <v>-0.1276105</v>
+      </c>
+      <c r="Q12">
+        <v>0.09038949999999996</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1198710757442681</v>
+      </c>
+      <c r="T12">
+        <v>0.8811553689298876</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.01992722231848897</v>
+      </c>
+      <c r="W12">
+        <v>0.2340413793103449</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.1328481487899266</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1332881061008758</v>
+      </c>
+      <c r="C13">
+        <v>5.216818099987645</v>
+      </c>
+      <c r="D13">
+        <v>5.227318099987645</v>
+      </c>
+      <c r="E13">
+        <v>-0.4025</v>
+      </c>
+      <c r="F13">
+        <v>0.7975</v>
+      </c>
+      <c r="G13">
+        <v>0.787</v>
+      </c>
+      <c r="H13">
+        <v>6.05</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.241</v>
+      </c>
+      <c r="K13">
+        <v>0.218</v>
+      </c>
+      <c r="L13">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M13">
+        <v>0.190443</v>
+      </c>
+      <c r="N13">
+        <v>-0.167443</v>
+      </c>
+      <c r="O13">
+        <v>-0.02511644999999999</v>
+      </c>
+      <c r="P13">
+        <v>-0.14232655</v>
+      </c>
+      <c r="Q13">
+        <v>0.07567344999999998</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1207819867076868</v>
+      </c>
+      <c r="T13">
+        <v>0.8910559910526953</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.0181156566531718</v>
+      </c>
+      <c r="W13">
+        <v>0.2344739811912226</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.1207710443544787</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1352881061008758</v>
+      </c>
+      <c r="C14">
+        <v>5.035966546387397</v>
+      </c>
+      <c r="D14">
+        <v>5.118966546387397</v>
+      </c>
+      <c r="E14">
+        <v>-0.33</v>
+      </c>
+      <c r="F14">
+        <v>0.87</v>
+      </c>
+      <c r="G14">
+        <v>0.787</v>
+      </c>
+      <c r="H14">
+        <v>6.05</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.241</v>
+      </c>
+      <c r="K14">
+        <v>0.218</v>
+      </c>
+      <c r="L14">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M14">
+        <v>0.207756</v>
+      </c>
+      <c r="N14">
+        <v>-0.184756</v>
+      </c>
+      <c r="O14">
+        <v>-0.02771339999999999</v>
+      </c>
+      <c r="P14">
+        <v>-0.1570426</v>
+      </c>
+      <c r="Q14">
+        <v>0.06095739999999997</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1217136001930015</v>
+      </c>
+      <c r="T14">
+        <v>0.9011816273146578</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.01660601859874082</v>
+      </c>
+      <c r="W14">
+        <v>0.2348344827586207</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.1107067906582722</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1372881061008758</v>
+      </c>
+      <c r="C15">
+        <v>4.859515587250376</v>
+      </c>
+      <c r="D15">
+        <v>5.015015587250376</v>
+      </c>
+      <c r="E15">
+        <v>-0.2575</v>
+      </c>
+      <c r="F15">
+        <v>0.9425</v>
+      </c>
+      <c r="G15">
+        <v>0.787</v>
+      </c>
+      <c r="H15">
+        <v>6.05</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.241</v>
+      </c>
+      <c r="K15">
+        <v>0.218</v>
+      </c>
+      <c r="L15">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M15">
+        <v>0.225069</v>
+      </c>
+      <c r="N15">
+        <v>-0.202069</v>
+      </c>
+      <c r="O15">
+        <v>-0.03031034999999999</v>
+      </c>
+      <c r="P15">
+        <v>-0.17175865</v>
+      </c>
+      <c r="Q15">
+        <v>0.04624134999999996</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1226666300802773</v>
+      </c>
+      <c r="T15">
+        <v>0.9115400368240215</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.01532863255268383</v>
+      </c>
+      <c r="W15">
+        <v>0.2351395225464191</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.1021908836845589</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1392881061008758</v>
+      </c>
+      <c r="C16">
+        <v>4.687202469422958</v>
+      </c>
+      <c r="D16">
+        <v>4.915202469422959</v>
+      </c>
+      <c r="E16">
+        <v>-0.1849999999999998</v>
+      </c>
+      <c r="F16">
+        <v>1.015</v>
+      </c>
+      <c r="G16">
+        <v>0.787</v>
+      </c>
+      <c r="H16">
+        <v>6.05</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.241</v>
+      </c>
+      <c r="K16">
+        <v>0.218</v>
+      </c>
+      <c r="L16">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M16">
+        <v>0.242382</v>
+      </c>
+      <c r="N16">
+        <v>-0.219382</v>
+      </c>
+      <c r="O16">
+        <v>-0.03290729999999999</v>
+      </c>
+      <c r="P16">
+        <v>-0.1864747</v>
+      </c>
+      <c r="Q16">
+        <v>0.03152529999999995</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1236418234533038</v>
+      </c>
+      <c r="T16">
+        <v>0.9221393395777893</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.01423373022749213</v>
+      </c>
+      <c r="W16">
+        <v>0.2354009852216749</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.09489153484994761</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1412881061008758</v>
+      </c>
+      <c r="C17">
+        <v>4.518784949694668</v>
+      </c>
+      <c r="D17">
+        <v>4.819284949694667</v>
+      </c>
+      <c r="E17">
+        <v>-0.1125</v>
+      </c>
+      <c r="F17">
+        <v>1.0875</v>
+      </c>
+      <c r="G17">
+        <v>0.787</v>
+      </c>
+      <c r="H17">
+        <v>6.05</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.241</v>
+      </c>
+      <c r="K17">
+        <v>0.218</v>
+      </c>
+      <c r="L17">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M17">
+        <v>0.259695</v>
+      </c>
+      <c r="N17">
+        <v>-0.236695</v>
+      </c>
+      <c r="O17">
+        <v>-0.03550424999999998</v>
+      </c>
+      <c r="P17">
+        <v>-0.20119075</v>
+      </c>
+      <c r="Q17">
+        <v>0.01680924999999997</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1246399625527545</v>
+      </c>
+      <c r="T17">
+        <v>0.9329880376904691</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.01328481487899265</v>
+      </c>
+      <c r="W17">
+        <v>0.2356275862068966</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.08856543252661775</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1432881061008758</v>
+      </c>
+      <c r="C18">
+        <v>4.354039331900774</v>
+      </c>
+      <c r="D18">
+        <v>4.727039331900774</v>
+      </c>
+      <c r="E18">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="F18">
+        <v>1.16</v>
+      </c>
+      <c r="G18">
+        <v>0.787</v>
+      </c>
+      <c r="H18">
+        <v>6.05</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.241</v>
+      </c>
+      <c r="K18">
+        <v>0.218</v>
+      </c>
+      <c r="L18">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M18">
+        <v>0.277008</v>
+      </c>
+      <c r="N18">
+        <v>-0.254008</v>
+      </c>
+      <c r="O18">
+        <v>-0.03810119999999998</v>
+      </c>
+      <c r="P18">
+        <v>-0.2159068</v>
+      </c>
+      <c r="Q18">
+        <v>0.002093199999999962</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1256618668688587</v>
+      </c>
+      <c r="T18">
+        <v>0.9440950381391652</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.01245451394905561</v>
+      </c>
+      <c r="W18">
+        <v>0.2358258620689655</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.08303009299370401</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1452881061008758</v>
+      </c>
+      <c r="C19">
+        <v>4.192758725221133</v>
+      </c>
+      <c r="D19">
+        <v>4.638258725221133</v>
+      </c>
+      <c r="E19">
+        <v>0.0325000000000002</v>
+      </c>
+      <c r="F19">
+        <v>1.2325</v>
+      </c>
+      <c r="G19">
+        <v>0.787</v>
+      </c>
+      <c r="H19">
+        <v>6.05</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.241</v>
+      </c>
+      <c r="K19">
+        <v>0.218</v>
+      </c>
+      <c r="L19">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M19">
+        <v>0.2943210000000001</v>
+      </c>
+      <c r="N19">
+        <v>-0.271321</v>
+      </c>
+      <c r="O19">
+        <v>-0.04069814999999998</v>
+      </c>
+      <c r="P19">
+        <v>-0.23062285</v>
+      </c>
+      <c r="Q19">
+        <v>-0.01262285000000005</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1267083953853509</v>
+      </c>
+      <c r="T19">
+        <v>0.9554696771528901</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.0117218954814641</v>
+      </c>
+      <c r="W19">
+        <v>0.2360008113590264</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.07814596987642752</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1472881061008758</v>
+      </c>
+      <c r="C20">
+        <v>4.034751495130707</v>
+      </c>
+      <c r="D20">
+        <v>4.552751495130707</v>
+      </c>
+      <c r="E20">
+        <v>0.105</v>
+      </c>
+      <c r="F20">
+        <v>1.305</v>
+      </c>
+      <c r="G20">
+        <v>0.787</v>
+      </c>
+      <c r="H20">
+        <v>6.05</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.241</v>
+      </c>
+      <c r="K20">
+        <v>0.218</v>
+      </c>
+      <c r="L20">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M20">
+        <v>0.311634</v>
+      </c>
+      <c r="N20">
+        <v>-0.2886340000000001</v>
+      </c>
+      <c r="O20">
+        <v>-0.04329509999999998</v>
+      </c>
+      <c r="P20">
+        <v>-0.2453389000000001</v>
+      </c>
+      <c r="Q20">
+        <v>-0.02733890000000008</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1277804489876113</v>
+      </c>
+      <c r="T20">
+        <v>0.967121746386462</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.01107067906582721</v>
+      </c>
+      <c r="W20">
+        <v>0.2361563218390805</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.07380452710551466</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1492881061008758</v>
+      </c>
+      <c r="C21">
+        <v>3.879839882590728</v>
+      </c>
+      <c r="D21">
+        <v>4.470339882590728</v>
+      </c>
+      <c r="E21">
+        <v>0.1775</v>
+      </c>
+      <c r="F21">
+        <v>1.3775</v>
+      </c>
+      <c r="G21">
+        <v>0.787</v>
+      </c>
+      <c r="H21">
+        <v>6.05</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.241</v>
+      </c>
+      <c r="K21">
+        <v>0.218</v>
+      </c>
+      <c r="L21">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M21">
+        <v>0.328947</v>
+      </c>
+      <c r="N21">
+        <v>-0.305947</v>
+      </c>
+      <c r="O21">
+        <v>-0.04589204999999997</v>
+      </c>
+      <c r="P21">
+        <v>-0.26005495</v>
+      </c>
+      <c r="Q21">
+        <v>-0.04205495000000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1288789730491868</v>
+      </c>
+      <c r="T21">
+        <v>0.9790615210332083</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.01048801174657315</v>
+      </c>
+      <c r="W21">
+        <v>0.2362954627949184</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.06992007831048774</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1512881061008758</v>
+      </c>
+      <c r="C22">
+        <v>3.727858770541745</v>
+      </c>
+      <c r="D22">
+        <v>4.390858770541746</v>
+      </c>
+      <c r="E22">
+        <v>0.2500000000000002</v>
+      </c>
+      <c r="F22">
+        <v>1.45</v>
+      </c>
+      <c r="G22">
+        <v>0.787</v>
+      </c>
+      <c r="H22">
+        <v>6.05</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.241</v>
+      </c>
+      <c r="K22">
+        <v>0.218</v>
+      </c>
+      <c r="L22">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M22">
+        <v>0.3462600000000001</v>
+      </c>
+      <c r="N22">
+        <v>-0.3232600000000001</v>
+      </c>
+      <c r="O22">
+        <v>-0.04848899999999998</v>
+      </c>
+      <c r="P22">
+        <v>-0.2747710000000001</v>
+      </c>
+      <c r="Q22">
+        <v>-0.0567710000000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1300049602123016</v>
+      </c>
+      <c r="T22">
+        <v>0.9912997900461235</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.009963611159244486</v>
+      </c>
+      <c r="W22">
+        <v>0.2364206896551724</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.06642407439496323</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1532881061008758</v>
+      </c>
+      <c r="C23">
+        <v>3.578654579685921</v>
+      </c>
+      <c r="D23">
+        <v>4.314154579685921</v>
+      </c>
+      <c r="E23">
+        <v>0.3225</v>
+      </c>
+      <c r="F23">
+        <v>1.5225</v>
+      </c>
+      <c r="G23">
+        <v>0.787</v>
+      </c>
+      <c r="H23">
+        <v>6.05</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.241</v>
+      </c>
+      <c r="K23">
+        <v>0.218</v>
+      </c>
+      <c r="L23">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M23">
+        <v>0.363573</v>
+      </c>
+      <c r="N23">
+        <v>-0.340573</v>
+      </c>
+      <c r="O23">
+        <v>-0.05108594999999997</v>
+      </c>
+      <c r="P23">
+        <v>-0.28948705</v>
+      </c>
+      <c r="Q23">
+        <v>-0.07148705000000002</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1311594533795459</v>
+      </c>
+      <c r="T23">
+        <v>1.003847888654302</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.009489153484994751</v>
+      </c>
+      <c r="W23">
+        <v>0.2365339901477833</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.06326102323329841</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1552881061008758</v>
+      </c>
+      <c r="C24">
+        <v>3.432084278020101</v>
+      </c>
+      <c r="D24">
+        <v>4.240084278020101</v>
+      </c>
+      <c r="E24">
+        <v>0.395</v>
+      </c>
+      <c r="F24">
+        <v>1.595</v>
+      </c>
+      <c r="G24">
+        <v>0.787</v>
+      </c>
+      <c r="H24">
+        <v>6.05</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.241</v>
+      </c>
+      <c r="K24">
+        <v>0.218</v>
+      </c>
+      <c r="L24">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M24">
+        <v>0.380886</v>
+      </c>
+      <c r="N24">
+        <v>-0.357886</v>
+      </c>
+      <c r="O24">
+        <v>-0.05368289999999997</v>
+      </c>
+      <c r="P24">
+        <v>-0.3042031000000001</v>
+      </c>
+      <c r="Q24">
+        <v>-0.08620310000000006</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.132343548935694</v>
+      </c>
+      <c r="T24">
+        <v>1.01671773338064</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.009057828326585899</v>
+      </c>
+      <c r="W24">
+        <v>0.2366369905956113</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.06038552217723925</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1572881061008758</v>
+      </c>
+      <c r="C25">
+        <v>3.288014490679416</v>
+      </c>
+      <c r="D25">
+        <v>4.168514490679416</v>
+      </c>
+      <c r="E25">
+        <v>0.4675</v>
+      </c>
+      <c r="F25">
+        <v>1.6675</v>
+      </c>
+      <c r="G25">
+        <v>0.787</v>
+      </c>
+      <c r="H25">
+        <v>6.05</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.241</v>
+      </c>
+      <c r="K25">
+        <v>0.218</v>
+      </c>
+      <c r="L25">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M25">
+        <v>0.398199</v>
+      </c>
+      <c r="N25">
+        <v>-0.3751990000000001</v>
+      </c>
+      <c r="O25">
+        <v>-0.05627984999999998</v>
+      </c>
+      <c r="P25">
+        <v>-0.3189191500000001</v>
+      </c>
+      <c r="Q25">
+        <v>-0.1009191500000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1335584002205731</v>
+      </c>
+      <c r="T25">
+        <v>1.02992185978818</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.008664009703690859</v>
+      </c>
+      <c r="W25">
+        <v>0.2367310344827586</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.05776006469127237</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1592881061008758</v>
+      </c>
+      <c r="C26">
+        <v>3.1463206984359</v>
+      </c>
+      <c r="D26">
+        <v>4.099320698435901</v>
+      </c>
+      <c r="E26">
+        <v>0.54</v>
+      </c>
+      <c r="F26">
+        <v>1.74</v>
+      </c>
+      <c r="G26">
+        <v>0.787</v>
+      </c>
+      <c r="H26">
+        <v>6.05</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.241</v>
+      </c>
+      <c r="K26">
+        <v>0.218</v>
+      </c>
+      <c r="L26">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M26">
+        <v>0.415512</v>
+      </c>
+      <c r="N26">
+        <v>-0.392512</v>
+      </c>
+      <c r="O26">
+        <v>-0.05887679999999996</v>
+      </c>
+      <c r="P26">
+        <v>-0.3336352</v>
+      </c>
+      <c r="Q26">
+        <v>-0.1156352</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1348052212761069</v>
+      </c>
+      <c r="T26">
+        <v>1.043473463206446</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.008303009299370409</v>
+      </c>
+      <c r="W26">
+        <v>0.2368172413793103</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.05535339532913619</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1612881061008758</v>
+      </c>
+      <c r="C27">
+        <v>3.006886514719158</v>
+      </c>
+      <c r="D27">
+        <v>4.032386514719158</v>
+      </c>
+      <c r="E27">
+        <v>0.6125</v>
+      </c>
+      <c r="F27">
+        <v>1.8125</v>
+      </c>
+      <c r="G27">
+        <v>0.787</v>
+      </c>
+      <c r="H27">
+        <v>6.05</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.241</v>
+      </c>
+      <c r="K27">
+        <v>0.218</v>
+      </c>
+      <c r="L27">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M27">
+        <v>0.432825</v>
+      </c>
+      <c r="N27">
+        <v>-0.409825</v>
+      </c>
+      <c r="O27">
+        <v>-0.06147374999999997</v>
+      </c>
+      <c r="P27">
+        <v>-0.34835125</v>
+      </c>
+      <c r="Q27">
+        <v>-0.13035125</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1360852908931217</v>
+      </c>
+      <c r="T27">
+        <v>1.057386442715865</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.007970888927395592</v>
+      </c>
+      <c r="W27">
+        <v>0.2368965517241379</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.05313925951597065</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1632881061008758</v>
+      </c>
+      <c r="C28">
+        <v>2.869603032328453</v>
+      </c>
+      <c r="D28">
+        <v>3.967603032328453</v>
+      </c>
+      <c r="E28">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="F28">
+        <v>1.885</v>
+      </c>
+      <c r="G28">
+        <v>0.787</v>
+      </c>
+      <c r="H28">
+        <v>6.05</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.241</v>
+      </c>
+      <c r="K28">
+        <v>0.218</v>
+      </c>
+      <c r="L28">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M28">
+        <v>0.450138</v>
+      </c>
+      <c r="N28">
+        <v>-0.427138</v>
+      </c>
+      <c r="O28">
+        <v>-0.06407069999999997</v>
+      </c>
+      <c r="P28">
+        <v>-0.3630673</v>
+      </c>
+      <c r="Q28">
+        <v>-0.1450673</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.137399956986272</v>
+      </c>
+      <c r="T28">
+        <v>1.071675448698512</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.007664316276341915</v>
+      </c>
+      <c r="W28">
+        <v>0.2369697612732096</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.05109544184227954</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1652881061008758</v>
+      </c>
+      <c r="C29">
+        <v>2.734368232122586</v>
+      </c>
+      <c r="D29">
+        <v>3.904868232122586</v>
+      </c>
+      <c r="E29">
+        <v>0.7575000000000001</v>
+      </c>
+      <c r="F29">
+        <v>1.9575</v>
+      </c>
+      <c r="G29">
+        <v>0.787</v>
+      </c>
+      <c r="H29">
+        <v>6.05</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.241</v>
+      </c>
+      <c r="K29">
+        <v>0.218</v>
+      </c>
+      <c r="L29">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M29">
+        <v>0.467451</v>
+      </c>
+      <c r="N29">
+        <v>-0.444451</v>
+      </c>
+      <c r="O29">
+        <v>-0.06666764999999997</v>
+      </c>
+      <c r="P29">
+        <v>-0.3777833500000001</v>
+      </c>
+      <c r="Q29">
+        <v>-0.1597833500000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1387506413285498</v>
+      </c>
+      <c r="T29">
+        <v>1.086355934297122</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.007380452710551474</v>
+      </c>
+      <c r="W29">
+        <v>0.2370375478927203</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.04920301807034311</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1672881061008758</v>
+      </c>
+      <c r="C30">
+        <v>2.601086446934517</v>
+      </c>
+      <c r="D30">
+        <v>3.844086446934518</v>
+      </c>
+      <c r="E30">
+        <v>0.8300000000000003</v>
+      </c>
+      <c r="F30">
+        <v>2.03</v>
+      </c>
+      <c r="G30">
+        <v>0.787</v>
+      </c>
+      <c r="H30">
+        <v>6.05</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.241</v>
+      </c>
+      <c r="K30">
+        <v>0.218</v>
+      </c>
+      <c r="L30">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M30">
+        <v>0.4847640000000001</v>
+      </c>
+      <c r="N30">
+        <v>-0.4617640000000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.06926459999999997</v>
+      </c>
+      <c r="P30">
+        <v>-0.3924994000000001</v>
+      </c>
+      <c r="Q30">
+        <v>-0.1744994000000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1401388446803351</v>
+      </c>
+      <c r="T30">
+        <v>1.101444211162359</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.007116865113746063</v>
+      </c>
+      <c r="W30">
+        <v>0.2371004926108374</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.04744576742497386</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1692881061008758</v>
+      </c>
+      <c r="C31">
+        <v>2.469667874785684</v>
+      </c>
+      <c r="D31">
+        <v>3.785167874785684</v>
+      </c>
+      <c r="E31">
+        <v>0.9025000000000001</v>
+      </c>
+      <c r="F31">
+        <v>2.1025</v>
+      </c>
+      <c r="G31">
+        <v>0.787</v>
+      </c>
+      <c r="H31">
+        <v>6.05</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.241</v>
+      </c>
+      <c r="K31">
+        <v>0.218</v>
+      </c>
+      <c r="L31">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M31">
+        <v>0.502077</v>
+      </c>
+      <c r="N31">
+        <v>-0.479077</v>
+      </c>
+      <c r="O31">
+        <v>-0.07186154999999995</v>
+      </c>
+      <c r="P31">
+        <v>-0.40721545</v>
+      </c>
+      <c r="Q31">
+        <v>-0.18921545</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1415661523518892</v>
+      </c>
+      <c r="T31">
+        <v>1.116957509911125</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.006871455971892751</v>
+      </c>
+      <c r="W31">
+        <v>0.237159096313912</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.04580970647928506</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1712881061008758</v>
+      </c>
+      <c r="C32">
+        <v>2.340028136190528</v>
+      </c>
+      <c r="D32">
+        <v>3.728028136190528</v>
+      </c>
+      <c r="E32">
+        <v>0.9749999999999999</v>
+      </c>
+      <c r="F32">
+        <v>2.175</v>
+      </c>
+      <c r="G32">
+        <v>0.787</v>
+      </c>
+      <c r="H32">
+        <v>6.05</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.241</v>
+      </c>
+      <c r="K32">
+        <v>0.218</v>
+      </c>
+      <c r="L32">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M32">
+        <v>0.51939</v>
+      </c>
+      <c r="N32">
+        <v>-0.49639</v>
+      </c>
+      <c r="O32">
+        <v>-0.07445849999999996</v>
+      </c>
+      <c r="P32">
+        <v>-0.4219315</v>
+      </c>
+      <c r="Q32">
+        <v>-0.2039315</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1430342402426305</v>
+      </c>
+      <c r="T32">
+        <v>1.132914045766998</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.006642407439496326</v>
+      </c>
+      <c r="W32">
+        <v>0.2372137931034483</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.04428271626330893</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1732881061008758</v>
+      </c>
+      <c r="C33">
+        <v>2.21208787096151</v>
+      </c>
+      <c r="D33">
+        <v>3.67258787096151</v>
+      </c>
+      <c r="E33">
+        <v>1.0475</v>
+      </c>
+      <c r="F33">
+        <v>2.2475</v>
+      </c>
+      <c r="G33">
+        <v>0.787</v>
+      </c>
+      <c r="H33">
+        <v>6.05</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.241</v>
+      </c>
+      <c r="K33">
+        <v>0.218</v>
+      </c>
+      <c r="L33">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M33">
+        <v>0.536703</v>
+      </c>
+      <c r="N33">
+        <v>-0.513703</v>
+      </c>
+      <c r="O33">
+        <v>-0.07705544999999996</v>
+      </c>
+      <c r="P33">
+        <v>-0.4366475500000001</v>
+      </c>
+      <c r="Q33">
+        <v>-0.2186475500000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1445448814055671</v>
+      </c>
+      <c r="T33">
+        <v>1.149333089908549</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.006428136231770637</v>
+      </c>
+      <c r="W33">
+        <v>0.2372649610678532</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.04285424154513762</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1752881061008758</v>
+      </c>
+      <c r="C34">
+        <v>2.085772370462922</v>
+      </c>
+      <c r="D34">
+        <v>3.618772370462921</v>
+      </c>
+      <c r="E34">
+        <v>1.12</v>
+      </c>
+      <c r="F34">
+        <v>2.32</v>
+      </c>
+      <c r="G34">
+        <v>0.787</v>
+      </c>
+      <c r="H34">
+        <v>6.05</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.241</v>
+      </c>
+      <c r="K34">
+        <v>0.218</v>
+      </c>
+      <c r="L34">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M34">
+        <v>0.554016</v>
+      </c>
+      <c r="N34">
+        <v>-0.5310159999999999</v>
+      </c>
+      <c r="O34">
+        <v>-0.07965239999999994</v>
+      </c>
+      <c r="P34">
+        <v>-0.4513636</v>
+      </c>
+      <c r="Q34">
+        <v>-0.2333636</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1460999531909431</v>
+      </c>
+      <c r="T34">
+        <v>1.166235047113086</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.006227256974527806</v>
+      </c>
+      <c r="W34">
+        <v>0.2373129310344828</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.04151504649685211</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1772881061008758</v>
+      </c>
+      <c r="C35">
+        <v>1.961011241729931</v>
+      </c>
+      <c r="D35">
+        <v>3.566511241729931</v>
+      </c>
+      <c r="E35">
+        <v>1.1925</v>
+      </c>
+      <c r="F35">
+        <v>2.3925</v>
+      </c>
+      <c r="G35">
+        <v>0.787</v>
+      </c>
+      <c r="H35">
+        <v>6.05</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.241</v>
+      </c>
+      <c r="K35">
+        <v>0.218</v>
+      </c>
+      <c r="L35">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M35">
+        <v>0.5713290000000001</v>
+      </c>
+      <c r="N35">
+        <v>-0.5483290000000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.08224934999999996</v>
+      </c>
+      <c r="P35">
+        <v>-0.4660796500000001</v>
+      </c>
+      <c r="Q35">
+        <v>-0.2480796500000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1477014450296139</v>
+      </c>
+      <c r="T35">
+        <v>1.18364154035358</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.006038552217723933</v>
+      </c>
+      <c r="W35">
+        <v>0.2373579937304075</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.04025701478482624</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1792881061008758</v>
+      </c>
+      <c r="C36">
+        <v>1.837738100277387</v>
+      </c>
+      <c r="D36">
+        <v>3.515738100277387</v>
+      </c>
+      <c r="E36">
+        <v>1.265</v>
+      </c>
+      <c r="F36">
+        <v>2.465</v>
+      </c>
+      <c r="G36">
+        <v>0.787</v>
+      </c>
+      <c r="H36">
+        <v>6.05</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.241</v>
+      </c>
+      <c r="K36">
+        <v>0.218</v>
+      </c>
+      <c r="L36">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M36">
+        <v>0.5886420000000001</v>
+      </c>
+      <c r="N36">
+        <v>-0.5656420000000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.08484629999999996</v>
+      </c>
+      <c r="P36">
+        <v>-0.4807957000000002</v>
+      </c>
+      <c r="Q36">
+        <v>-0.2627957000000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.149351466924002</v>
+      </c>
+      <c r="T36">
+        <v>1.20157550308621</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.005860947740732051</v>
+      </c>
+      <c r="W36">
+        <v>0.2374004056795132</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.03907298493821376</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1812881061008758</v>
+      </c>
+      <c r="C37">
+        <v>1.715890288779515</v>
+      </c>
+      <c r="D37">
+        <v>3.466390288779515</v>
+      </c>
+      <c r="E37">
+        <v>1.3375</v>
+      </c>
+      <c r="F37">
+        <v>2.5375</v>
+      </c>
+      <c r="G37">
+        <v>0.787</v>
+      </c>
+      <c r="H37">
+        <v>6.05</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.241</v>
+      </c>
+      <c r="K37">
+        <v>0.218</v>
+      </c>
+      <c r="L37">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M37">
+        <v>0.605955</v>
+      </c>
+      <c r="N37">
+        <v>-0.582955</v>
+      </c>
+      <c r="O37">
+        <v>-0.08744324999999994</v>
+      </c>
+      <c r="P37">
+        <v>-0.49551175</v>
+      </c>
+      <c r="Q37">
+        <v>-0.2775117500000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1510522587228328</v>
+      </c>
+      <c r="T37">
+        <v>1.220061280056767</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.00569349209099685</v>
+      </c>
+      <c r="W37">
+        <v>0.23744039408867</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.03795661393997907</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1832881061008758</v>
+      </c>
+      <c r="C38">
+        <v>1.595408619113786</v>
+      </c>
+      <c r="D38">
+        <v>3.418408619113785</v>
+      </c>
+      <c r="E38">
+        <v>1.41</v>
+      </c>
+      <c r="F38">
+        <v>2.61</v>
+      </c>
+      <c r="G38">
+        <v>0.787</v>
+      </c>
+      <c r="H38">
+        <v>6.05</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.241</v>
+      </c>
+      <c r="K38">
+        <v>0.218</v>
+      </c>
+      <c r="L38">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M38">
+        <v>0.623268</v>
+      </c>
+      <c r="N38">
+        <v>-0.600268</v>
+      </c>
+      <c r="O38">
+        <v>-0.09004019999999995</v>
+      </c>
+      <c r="P38">
+        <v>-0.5102278000000001</v>
+      </c>
+      <c r="Q38">
+        <v>-0.2922278000000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.152806200265377</v>
+      </c>
+      <c r="T38">
+        <v>1.239124737557654</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.005535339532913605</v>
+      </c>
+      <c r="W38">
+        <v>0.2374781609195402</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.03690226355275739</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1852881061008758</v>
+      </c>
+      <c r="C39">
+        <v>1.476237135536003</v>
+      </c>
+      <c r="D39">
+        <v>3.371737135536003</v>
+      </c>
+      <c r="E39">
+        <v>1.4825</v>
+      </c>
+      <c r="F39">
+        <v>2.6825</v>
+      </c>
+      <c r="G39">
+        <v>0.787</v>
+      </c>
+      <c r="H39">
+        <v>6.05</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.241</v>
+      </c>
+      <c r="K39">
+        <v>0.218</v>
+      </c>
+      <c r="L39">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M39">
+        <v>0.6405810000000001</v>
+      </c>
+      <c r="N39">
+        <v>-0.617581</v>
+      </c>
+      <c r="O39">
+        <v>-0.09263714999999995</v>
+      </c>
+      <c r="P39">
+        <v>-0.5249438500000001</v>
+      </c>
+      <c r="Q39">
+        <v>-0.3069438500000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1546158224918116</v>
+      </c>
+      <c r="T39">
+        <v>1.258793384185554</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.005385735761753777</v>
+      </c>
+      <c r="W39">
+        <v>0.2375138863000932</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.03590490507835853</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1872881061008758</v>
+      </c>
+      <c r="C40">
+        <v>1.358322896994292</v>
+      </c>
+      <c r="D40">
+        <v>3.326322896994292</v>
+      </c>
+      <c r="E40">
+        <v>1.555</v>
+      </c>
+      <c r="F40">
+        <v>2.755</v>
+      </c>
+      <c r="G40">
+        <v>0.787</v>
+      </c>
+      <c r="H40">
+        <v>6.05</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.241</v>
+      </c>
+      <c r="K40">
+        <v>0.218</v>
+      </c>
+      <c r="L40">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M40">
+        <v>0.657894</v>
+      </c>
+      <c r="N40">
+        <v>-0.634894</v>
+      </c>
+      <c r="O40">
+        <v>-0.09523409999999993</v>
+      </c>
+      <c r="P40">
+        <v>-0.5396599</v>
+      </c>
+      <c r="Q40">
+        <v>-0.3216599</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1564838196287763</v>
+      </c>
+      <c r="T40">
+        <v>1.279096503285321</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.005244005873286574</v>
+      </c>
+      <c r="W40">
+        <v>0.2375477313974592</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.03496003915524393</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1892881061008758</v>
+      </c>
+      <c r="C41">
+        <v>1.24161577680149</v>
+      </c>
+      <c r="D41">
+        <v>3.282115776801489</v>
+      </c>
+      <c r="E41">
+        <v>1.6275</v>
+      </c>
+      <c r="F41">
+        <v>2.8275</v>
+      </c>
+      <c r="G41">
+        <v>0.787</v>
+      </c>
+      <c r="H41">
+        <v>6.05</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.241</v>
+      </c>
+      <c r="K41">
+        <v>0.218</v>
+      </c>
+      <c r="L41">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M41">
+        <v>0.6752070000000001</v>
+      </c>
+      <c r="N41">
+        <v>-0.6522070000000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.09783104999999996</v>
+      </c>
+      <c r="P41">
+        <v>-0.5543759500000002</v>
+      </c>
+      <c r="Q41">
+        <v>-0.3363759500000002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1584130625735103</v>
+      </c>
+      <c r="T41">
+        <v>1.300065298421146</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.005109544184227943</v>
+      </c>
+      <c r="W41">
+        <v>0.2375798408488064</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.03406362789485307</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1912881061008758</v>
+      </c>
+      <c r="C42">
+        <v>1.12606827807224</v>
+      </c>
+      <c r="D42">
+        <v>3.23906827807224</v>
+      </c>
+      <c r="E42">
+        <v>1.7</v>
+      </c>
+      <c r="F42">
+        <v>2.9</v>
+      </c>
+      <c r="G42">
+        <v>0.787</v>
+      </c>
+      <c r="H42">
+        <v>6.05</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.241</v>
+      </c>
+      <c r="K42">
+        <v>0.218</v>
+      </c>
+      <c r="L42">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M42">
+        <v>0.6925200000000001</v>
+      </c>
+      <c r="N42">
+        <v>-0.6695200000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.100428</v>
+      </c>
+      <c r="P42">
+        <v>-0.5690920000000002</v>
+      </c>
+      <c r="Q42">
+        <v>-0.3510920000000002</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1604066136164022</v>
+      </c>
+      <c r="T42">
+        <v>1.321733053394831</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.004981805579622243</v>
+      </c>
+      <c r="W42">
+        <v>0.2376103448275862</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.03321203719748167</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1932881061008758</v>
+      </c>
+      <c r="C43">
+        <v>1.011635363496186</v>
+      </c>
+      <c r="D43">
+        <v>3.197135363496186</v>
+      </c>
+      <c r="E43">
+        <v>1.7725</v>
+      </c>
+      <c r="F43">
+        <v>2.9725</v>
+      </c>
+      <c r="G43">
+        <v>0.787</v>
+      </c>
+      <c r="H43">
+        <v>6.05</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.241</v>
+      </c>
+      <c r="K43">
+        <v>0.218</v>
+      </c>
+      <c r="L43">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M43">
+        <v>0.709833</v>
+      </c>
+      <c r="N43">
+        <v>-0.686833</v>
+      </c>
+      <c r="O43">
+        <v>-0.1030249499999999</v>
+      </c>
+      <c r="P43">
+        <v>-0.58380805</v>
+      </c>
+      <c r="Q43">
+        <v>-0.3658080500000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.162467742660748</v>
+      </c>
+      <c r="T43">
+        <v>1.344135308537117</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.004860298126460726</v>
+      </c>
+      <c r="W43">
+        <v>0.2376393608074012</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.03240198750973822</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1952881061008758</v>
+      </c>
+      <c r="C44">
+        <v>0.898274298164675</v>
+      </c>
+      <c r="D44">
+        <v>3.156274298164675</v>
+      </c>
+      <c r="E44">
+        <v>1.845</v>
+      </c>
+      <c r="F44">
+        <v>3.045</v>
+      </c>
+      <c r="G44">
+        <v>0.787</v>
+      </c>
+      <c r="H44">
+        <v>6.05</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.241</v>
+      </c>
+      <c r="K44">
+        <v>0.218</v>
+      </c>
+      <c r="L44">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M44">
+        <v>0.7271460000000001</v>
+      </c>
+      <c r="N44">
+        <v>-0.704146</v>
+      </c>
+      <c r="O44">
+        <v>-0.1056218999999999</v>
+      </c>
+      <c r="P44">
+        <v>-0.5985241000000001</v>
+      </c>
+      <c r="Q44">
+        <v>-0.3805241000000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.164599945120416</v>
+      </c>
+      <c r="T44">
+        <v>1.367310055236032</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.004744576742497376</v>
+      </c>
+      <c r="W44">
+        <v>0.2376669950738916</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.0316305116166492</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1972881061008758</v>
+      </c>
+      <c r="C45">
+        <v>0.785944504297925</v>
+      </c>
+      <c r="D45">
+        <v>3.116444504297925</v>
+      </c>
+      <c r="E45">
+        <v>1.9175</v>
+      </c>
+      <c r="F45">
+        <v>3.1175</v>
+      </c>
+      <c r="G45">
+        <v>0.787</v>
+      </c>
+      <c r="H45">
+        <v>6.05</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.241</v>
+      </c>
+      <c r="K45">
+        <v>0.218</v>
+      </c>
+      <c r="L45">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M45">
+        <v>0.7444590000000001</v>
+      </c>
+      <c r="N45">
+        <v>-0.7214590000000001</v>
+      </c>
+      <c r="O45">
+        <v>-0.1082188499999999</v>
+      </c>
+      <c r="P45">
+        <v>-0.6132401500000001</v>
+      </c>
+      <c r="Q45">
+        <v>-0.3952401500000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.166806961701476</v>
+      </c>
+      <c r="T45">
+        <v>1.391297950941928</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.004634237748485808</v>
+      </c>
+      <c r="W45">
+        <v>0.2376933440256616</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.03089491832323876</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1992881061008758</v>
+      </c>
+      <c r="C46">
+        <v>0.6746074268345148</v>
+      </c>
+      <c r="D46">
+        <v>3.077607426834515</v>
+      </c>
+      <c r="E46">
+        <v>1.99</v>
+      </c>
+      <c r="F46">
+        <v>3.19</v>
+      </c>
+      <c r="G46">
+        <v>0.787</v>
+      </c>
+      <c r="H46">
+        <v>6.05</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.241</v>
+      </c>
+      <c r="K46">
+        <v>0.218</v>
+      </c>
+      <c r="L46">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M46">
+        <v>0.761772</v>
+      </c>
+      <c r="N46">
+        <v>-0.738772</v>
+      </c>
+      <c r="O46">
+        <v>-0.1108157999999999</v>
+      </c>
+      <c r="P46">
+        <v>-0.6279562000000001</v>
+      </c>
+      <c r="Q46">
+        <v>-0.4099562000000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.169092800303288</v>
+      </c>
+      <c r="T46">
+        <v>1.416142557208748</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.00452891416329295</v>
+      </c>
+      <c r="W46">
+        <v>0.2377184952978057</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.03019276108861968</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2012881061008758</v>
+      </c>
+      <c r="C47">
+        <v>0.5642264089472859</v>
+      </c>
+      <c r="D47">
+        <v>3.039726408947286</v>
+      </c>
+      <c r="E47">
+        <v>2.0625</v>
+      </c>
+      <c r="F47">
+        <v>3.2625</v>
+      </c>
+      <c r="G47">
+        <v>0.787</v>
+      </c>
+      <c r="H47">
+        <v>6.05</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.241</v>
+      </c>
+      <c r="K47">
+        <v>0.218</v>
+      </c>
+      <c r="L47">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M47">
+        <v>0.779085</v>
+      </c>
+      <c r="N47">
+        <v>-0.756085</v>
+      </c>
+      <c r="O47">
+        <v>-0.1134127499999999</v>
+      </c>
+      <c r="P47">
+        <v>-0.6426722500000001</v>
+      </c>
+      <c r="Q47">
+        <v>-0.4246722500000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1714617603088024</v>
+      </c>
+      <c r="T47">
+        <v>1.441890603703452</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.004428271626330884</v>
+      </c>
+      <c r="W47">
+        <v>0.2377425287356322</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.02952181084220595</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2032881061008758</v>
+      </c>
+      <c r="C48">
+        <v>0.4547665766408331</v>
+      </c>
+      <c r="D48">
+        <v>3.002766576640833</v>
+      </c>
+      <c r="E48">
+        <v>2.135</v>
+      </c>
+      <c r="F48">
+        <v>3.335</v>
+      </c>
+      <c r="G48">
+        <v>0.787</v>
+      </c>
+      <c r="H48">
+        <v>6.05</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.241</v>
+      </c>
+      <c r="K48">
+        <v>0.218</v>
+      </c>
+      <c r="L48">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M48">
+        <v>0.7963980000000001</v>
+      </c>
+      <c r="N48">
+        <v>-0.773398</v>
+      </c>
+      <c r="O48">
+        <v>-0.1160096999999999</v>
+      </c>
+      <c r="P48">
+        <v>-0.6573883</v>
+      </c>
+      <c r="Q48">
+        <v>-0.4393883000000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1739184595737802</v>
+      </c>
+      <c r="T48">
+        <v>1.468592281549812</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.00433200485184543</v>
+      </c>
+      <c r="W48">
+        <v>0.2377655172413793</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.0288800323456363</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2052881061008758</v>
+      </c>
+      <c r="C49">
+        <v>0.346194731666857</v>
+      </c>
+      <c r="D49">
+        <v>2.966694731666857</v>
+      </c>
+      <c r="E49">
+        <v>2.2075</v>
+      </c>
+      <c r="F49">
+        <v>3.4075</v>
+      </c>
+      <c r="G49">
+        <v>0.787</v>
+      </c>
+      <c r="H49">
+        <v>6.05</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.241</v>
+      </c>
+      <c r="K49">
+        <v>0.218</v>
+      </c>
+      <c r="L49">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M49">
+        <v>0.8137110000000001</v>
+      </c>
+      <c r="N49">
+        <v>-0.7907110000000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.1186066499999999</v>
+      </c>
+      <c r="P49">
+        <v>-0.6721043500000001</v>
+      </c>
+      <c r="Q49">
+        <v>-0.4541043500000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1764678644713987</v>
+      </c>
+      <c r="T49">
+        <v>1.496301569880941</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.004239834535848718</v>
+      </c>
+      <c r="W49">
+        <v>0.2377875275128393</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.02826556357232479</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2072881061008758</v>
+      </c>
+      <c r="C50">
+        <v>0.2384792520662891</v>
+      </c>
+      <c r="D50">
+        <v>2.931479252066289</v>
+      </c>
+      <c r="E50">
+        <v>2.28</v>
+      </c>
+      <c r="F50">
+        <v>3.48</v>
+      </c>
+      <c r="G50">
+        <v>0.787</v>
+      </c>
+      <c r="H50">
+        <v>6.05</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.241</v>
+      </c>
+      <c r="K50">
+        <v>0.218</v>
+      </c>
+      <c r="L50">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M50">
+        <v>0.831024</v>
+      </c>
+      <c r="N50">
+        <v>-0.808024</v>
+      </c>
+      <c r="O50">
+        <v>-0.1212035999999999</v>
+      </c>
+      <c r="P50">
+        <v>-0.6868204</v>
+      </c>
+      <c r="Q50">
+        <v>-0.4688204</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1791153234035409</v>
+      </c>
+      <c r="T50">
+        <v>1.525076600070959</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.004151504649685204</v>
+      </c>
+      <c r="W50">
+        <v>0.2378086206896552</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.02767669766456804</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2092881061008758</v>
+      </c>
+      <c r="C51">
+        <v>0.131589999711855</v>
+      </c>
+      <c r="D51">
+        <v>2.897089999711855</v>
+      </c>
+      <c r="E51">
+        <v>2.3525</v>
+      </c>
+      <c r="F51">
+        <v>3.5525</v>
+      </c>
+      <c r="G51">
+        <v>0.787</v>
+      </c>
+      <c r="H51">
+        <v>6.05</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.241</v>
+      </c>
+      <c r="K51">
+        <v>0.218</v>
+      </c>
+      <c r="L51">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M51">
+        <v>0.848337</v>
+      </c>
+      <c r="N51">
+        <v>-0.825337</v>
+      </c>
+      <c r="O51">
+        <v>-0.1238005499999999</v>
+      </c>
+      <c r="P51">
+        <v>-0.7015364500000001</v>
+      </c>
+      <c r="Q51">
+        <v>-0.4835364500000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1818666042545908</v>
+      </c>
+      <c r="T51">
+        <v>1.554980062817449</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.004066780064997751</v>
+      </c>
+      <c r="W51">
+        <v>0.2378288529204786</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.02711186709998503</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2112881061008758</v>
+      </c>
+      <c r="C52">
+        <v>0.02549823428290887</v>
+      </c>
+      <c r="D52">
+        <v>2.863498234282909</v>
+      </c>
+      <c r="E52">
+        <v>2.425</v>
+      </c>
+      <c r="F52">
+        <v>3.625</v>
+      </c>
+      <c r="G52">
+        <v>0.787</v>
+      </c>
+      <c r="H52">
+        <v>6.05</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.241</v>
+      </c>
+      <c r="K52">
+        <v>0.218</v>
+      </c>
+      <c r="L52">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M52">
+        <v>0.86565</v>
+      </c>
+      <c r="N52">
+        <v>-0.84265</v>
+      </c>
+      <c r="O52">
+        <v>-0.1263974999999999</v>
+      </c>
+      <c r="P52">
+        <v>-0.7162525000000001</v>
+      </c>
+      <c r="Q52">
+        <v>-0.4982525000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1847279363396826</v>
+      </c>
+      <c r="T52">
+        <v>1.586079664073798</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.003985444463697796</v>
+      </c>
+      <c r="W52">
+        <v>0.237848275862069</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.02656962975798538</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2132881061008758</v>
+      </c>
+      <c r="C53">
+        <v>-0.07982346684355646</v>
+      </c>
+      <c r="D53">
+        <v>2.830676533156444</v>
+      </c>
+      <c r="E53">
+        <v>2.4975</v>
+      </c>
+      <c r="F53">
+        <v>3.6975</v>
+      </c>
+      <c r="G53">
+        <v>0.787</v>
+      </c>
+      <c r="H53">
+        <v>6.05</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.241</v>
+      </c>
+      <c r="K53">
+        <v>0.218</v>
+      </c>
+      <c r="L53">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M53">
+        <v>0.8829630000000001</v>
+      </c>
+      <c r="N53">
+        <v>-0.859963</v>
+      </c>
+      <c r="O53">
+        <v>-0.1289944499999999</v>
+      </c>
+      <c r="P53">
+        <v>-0.7309685500000001</v>
+      </c>
+      <c r="Q53">
+        <v>-0.5129685500000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.187706057489472</v>
+      </c>
+      <c r="T53">
+        <v>1.618448636809998</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.003907298493821368</v>
+      </c>
+      <c r="W53">
+        <v>0.2378669371196755</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.02604865662547584</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2152881061008758</v>
+      </c>
+      <c r="C54">
+        <v>-0.1844012832550312</v>
+      </c>
+      <c r="D54">
+        <v>2.798598716744969</v>
+      </c>
+      <c r="E54">
+        <v>2.57</v>
+      </c>
+      <c r="F54">
+        <v>3.77</v>
+      </c>
+      <c r="G54">
+        <v>0.787</v>
+      </c>
+      <c r="H54">
+        <v>6.05</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.241</v>
+      </c>
+      <c r="K54">
+        <v>0.218</v>
+      </c>
+      <c r="L54">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M54">
+        <v>0.9002760000000001</v>
+      </c>
+      <c r="N54">
+        <v>-0.8772760000000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.1315913999999999</v>
+      </c>
+      <c r="P54">
+        <v>-0.7456846000000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.5276846000000002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1908082670205027</v>
+      </c>
+      <c r="T54">
+        <v>1.652166316743539</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.003832158138170957</v>
+      </c>
+      <c r="W54">
+        <v>0.2378848806366048</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.02554772092113977</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2172881061008758</v>
+      </c>
+      <c r="C55">
+        <v>-0.2882602211459782</v>
+      </c>
+      <c r="D55">
+        <v>2.767239778854022</v>
+      </c>
+      <c r="E55">
+        <v>2.6425</v>
+      </c>
+      <c r="F55">
+        <v>3.8425</v>
+      </c>
+      <c r="G55">
+        <v>0.787</v>
+      </c>
+      <c r="H55">
+        <v>6.05</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.241</v>
+      </c>
+      <c r="K55">
+        <v>0.218</v>
+      </c>
+      <c r="L55">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M55">
+        <v>0.9175890000000001</v>
+      </c>
+      <c r="N55">
+        <v>-0.8945890000000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.1341883499999999</v>
+      </c>
+      <c r="P55">
+        <v>-0.7604006500000001</v>
+      </c>
+      <c r="Q55">
+        <v>-0.5424006500000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1940424854677475</v>
+      </c>
+      <c r="T55">
+        <v>1.68731879156787</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.00375985326763943</v>
+      </c>
+      <c r="W55">
+        <v>0.2379021470396877</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.0250656884509296</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2192881061008758</v>
+      </c>
+      <c r="C56">
+        <v>-0.391424178330031</v>
+      </c>
+      <c r="D56">
+        <v>2.736575821669969</v>
+      </c>
+      <c r="E56">
+        <v>2.715</v>
+      </c>
+      <c r="F56">
+        <v>3.915</v>
+      </c>
+      <c r="G56">
+        <v>0.787</v>
+      </c>
+      <c r="H56">
+        <v>6.05</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.241</v>
+      </c>
+      <c r="K56">
+        <v>0.218</v>
+      </c>
+      <c r="L56">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M56">
+        <v>0.934902</v>
+      </c>
+      <c r="N56">
+        <v>-0.911902</v>
+      </c>
+      <c r="O56">
+        <v>-0.1367852999999999</v>
+      </c>
+      <c r="P56">
+        <v>-0.7751167000000001</v>
+      </c>
+      <c r="Q56">
+        <v>-0.5571167000000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1974173221083507</v>
+      </c>
+      <c r="T56">
+        <v>1.723999634862824</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.003690226355275737</v>
+      </c>
+      <c r="W56">
+        <v>0.2379187739463602</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.02460150903517166</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2212881061008758</v>
+      </c>
+      <c r="C57">
+        <v>-0.4939160049771569</v>
+      </c>
+      <c r="D57">
+        <v>2.706583995022843</v>
+      </c>
+      <c r="E57">
+        <v>2.787500000000001</v>
+      </c>
+      <c r="F57">
+        <v>3.9875</v>
+      </c>
+      <c r="G57">
+        <v>0.787</v>
+      </c>
+      <c r="H57">
+        <v>6.05</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.241</v>
+      </c>
+      <c r="K57">
+        <v>0.218</v>
+      </c>
+      <c r="L57">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M57">
+        <v>0.9522150000000001</v>
+      </c>
+      <c r="N57">
+        <v>-0.9292150000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.1393822499999999</v>
+      </c>
+      <c r="P57">
+        <v>-0.7898327500000002</v>
+      </c>
+      <c r="Q57">
+        <v>-0.5718327500000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2009421514885362</v>
+      </c>
+      <c r="T57">
+        <v>1.762310737859775</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.003623131330634359</v>
+      </c>
+      <c r="W57">
+        <v>0.2379347962382445</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.02415420887089581</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2232881061008758</v>
+      </c>
+      <c r="C58">
+        <v>-0.595757560400171</v>
+      </c>
+      <c r="D58">
+        <v>2.67724243959983</v>
+      </c>
+      <c r="E58">
+        <v>2.86</v>
+      </c>
+      <c r="F58">
+        <v>4.06</v>
+      </c>
+      <c r="G58">
+        <v>0.787</v>
+      </c>
+      <c r="H58">
+        <v>6.05</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.241</v>
+      </c>
+      <c r="K58">
+        <v>0.218</v>
+      </c>
+      <c r="L58">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M58">
+        <v>0.9695280000000002</v>
+      </c>
+      <c r="N58">
+        <v>-0.9465280000000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.1419791999999999</v>
+      </c>
+      <c r="P58">
+        <v>-0.8045488000000002</v>
+      </c>
+      <c r="Q58">
+        <v>-0.5865488000000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.204627200386003</v>
+      </c>
+      <c r="T58">
+        <v>1.802363254629316</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.003558432556873031</v>
+      </c>
+      <c r="W58">
+        <v>0.2379502463054187</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.02372288371248688</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2252881061008758</v>
+      </c>
+      <c r="C59">
+        <v>-0.696969766187189</v>
+      </c>
+      <c r="D59">
+        <v>2.648530233812811</v>
+      </c>
+      <c r="E59">
+        <v>2.9325</v>
+      </c>
+      <c r="F59">
+        <v>4.1325</v>
+      </c>
+      <c r="G59">
+        <v>0.787</v>
+      </c>
+      <c r="H59">
+        <v>6.05</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.241</v>
+      </c>
+      <c r="K59">
+        <v>0.218</v>
+      </c>
+      <c r="L59">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M59">
+        <v>0.9868410000000001</v>
+      </c>
+      <c r="N59">
+        <v>-0.9638410000000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.1445761499999999</v>
+      </c>
+      <c r="P59">
+        <v>-0.8192648500000002</v>
+      </c>
+      <c r="Q59">
+        <v>-0.6012648500000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2084836469066077</v>
+      </c>
+      <c r="T59">
+        <v>1.844278679155579</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.003496003915524382</v>
+      </c>
+      <c r="W59">
+        <v>0.2379651542649728</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.02330669277016262</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2272881061008758</v>
+      </c>
+      <c r="C60">
+        <v>-0.7975726559514413</v>
+      </c>
+      <c r="D60">
+        <v>2.620427344048559</v>
+      </c>
+      <c r="E60">
+        <v>3.005</v>
+      </c>
+      <c r="F60">
+        <v>4.205</v>
+      </c>
+      <c r="G60">
+        <v>0.787</v>
+      </c>
+      <c r="H60">
+        <v>6.05</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.241</v>
+      </c>
+      <c r="K60">
+        <v>0.218</v>
+      </c>
+      <c r="L60">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M60">
+        <v>1.004154</v>
+      </c>
+      <c r="N60">
+        <v>-0.981154</v>
+      </c>
+      <c r="O60">
+        <v>-0.1471730999999999</v>
+      </c>
+      <c r="P60">
+        <v>-0.8339809</v>
+      </c>
+      <c r="Q60">
+        <v>-0.6159809000000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2125237337377174</v>
+      </c>
+      <c r="T60">
+        <v>1.88819007627833</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.003435727985946376</v>
+      </c>
+      <c r="W60">
+        <v>0.237979548156956</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.02290485323964253</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2292881061008758</v>
+      </c>
+      <c r="C61">
+        <v>-0.8975854219470341</v>
+      </c>
+      <c r="D61">
+        <v>2.592914578052966</v>
+      </c>
+      <c r="E61">
+        <v>3.0775</v>
+      </c>
+      <c r="F61">
+        <v>4.2775</v>
+      </c>
+      <c r="G61">
+        <v>0.787</v>
+      </c>
+      <c r="H61">
+        <v>6.05</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.241</v>
+      </c>
+      <c r="K61">
+        <v>0.218</v>
+      </c>
+      <c r="L61">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M61">
+        <v>1.021467</v>
+      </c>
+      <c r="N61">
+        <v>-0.9984670000000001</v>
+      </c>
+      <c r="O61">
+        <v>-0.1497700499999999</v>
+      </c>
+      <c r="P61">
+        <v>-0.8486969500000001</v>
+      </c>
+      <c r="Q61">
+        <v>-0.6306969500000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2167608979752227</v>
+      </c>
+      <c r="T61">
+        <v>1.934243492772924</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.003377495308218471</v>
+      </c>
+      <c r="W61">
+        <v>0.2379934541203974</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.02251663538812321</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2312881061008758</v>
+      </c>
+      <c r="C62">
+        <v>-0.99702645877862</v>
+      </c>
+      <c r="D62">
+        <v>2.56597354122138</v>
+      </c>
+      <c r="E62">
+        <v>3.149999999999999</v>
+      </c>
+      <c r="F62">
+        <v>4.35</v>
+      </c>
+      <c r="G62">
+        <v>0.787</v>
+      </c>
+      <c r="H62">
+        <v>6.05</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.241</v>
+      </c>
+      <c r="K62">
+        <v>0.218</v>
+      </c>
+      <c r="L62">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M62">
+        <v>1.03878</v>
+      </c>
+      <c r="N62">
+        <v>-1.01578</v>
+      </c>
+      <c r="O62">
+        <v>-0.1523669999999999</v>
+      </c>
+      <c r="P62">
+        <v>-0.8634130000000002</v>
+      </c>
+      <c r="Q62">
+        <v>-0.6454130000000002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2212099204246032</v>
+      </c>
+      <c r="T62">
+        <v>1.982599580092247</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.003321203719748163</v>
+      </c>
+      <c r="W62">
+        <v>0.2380068965517241</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.0221413581316543</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2332881061008758</v>
+      </c>
+      <c r="C63">
+        <v>-1.09591340441416</v>
+      </c>
+      <c r="D63">
+        <v>2.53958659558584</v>
+      </c>
+      <c r="E63">
+        <v>3.2225</v>
+      </c>
+      <c r="F63">
+        <v>4.4225</v>
+      </c>
+      <c r="G63">
+        <v>0.787</v>
+      </c>
+      <c r="H63">
+        <v>6.05</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.241</v>
+      </c>
+      <c r="K63">
+        <v>0.218</v>
+      </c>
+      <c r="L63">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M63">
+        <v>1.056093</v>
+      </c>
+      <c r="N63">
+        <v>-1.033093</v>
+      </c>
+      <c r="O63">
+        <v>-0.1549639499999999</v>
+      </c>
+      <c r="P63">
+        <v>-0.8781290500000003</v>
+      </c>
+      <c r="Q63">
+        <v>-0.6601290500000003</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.225887097871388</v>
+      </c>
+      <c r="T63">
+        <v>2.033435466761279</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.00326675775712934</v>
+      </c>
+      <c r="W63">
+        <v>0.2380198982475975</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.02177838504752883</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2352881061008757</v>
+      </c>
+      <c r="C64">
+        <v>-1.194263178692935</v>
+      </c>
+      <c r="D64">
+        <v>2.513736821307066</v>
+      </c>
+      <c r="E64">
+        <v>3.295</v>
+      </c>
+      <c r="F64">
+        <v>4.495</v>
+      </c>
+      <c r="G64">
+        <v>0.787</v>
+      </c>
+      <c r="H64">
+        <v>6.05</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.241</v>
+      </c>
+      <c r="K64">
+        <v>0.218</v>
+      </c>
+      <c r="L64">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M64">
+        <v>1.073406</v>
+      </c>
+      <c r="N64">
+        <v>-1.050406</v>
+      </c>
+      <c r="O64">
+        <v>-0.1575608999999999</v>
+      </c>
+      <c r="P64">
+        <v>-0.8928451000000003</v>
+      </c>
+      <c r="Q64">
+        <v>-0.6748451000000003</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2308104425522139</v>
+      </c>
+      <c r="T64">
+        <v>2.086946926412891</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.003214068115885319</v>
+      </c>
+      <c r="W64">
+        <v>0.2380324805339266</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.0214271207725687</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2372881061008758</v>
+      </c>
+      <c r="C65">
+        <v>-1.292092019505487</v>
+      </c>
+      <c r="D65">
+        <v>2.488407980494513</v>
+      </c>
+      <c r="E65">
+        <v>3.3675</v>
+      </c>
+      <c r="F65">
+        <v>4.5675</v>
+      </c>
+      <c r="G65">
+        <v>0.787</v>
+      </c>
+      <c r="H65">
+        <v>6.05</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.241</v>
+      </c>
+      <c r="K65">
+        <v>0.218</v>
+      </c>
+      <c r="L65">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M65">
+        <v>1.090719</v>
+      </c>
+      <c r="N65">
+        <v>-1.067719</v>
+      </c>
+      <c r="O65">
+        <v>-0.1601578499999999</v>
+      </c>
+      <c r="P65">
+        <v>-0.9075611500000001</v>
+      </c>
+      <c r="Q65">
+        <v>-0.6895611500000002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.235999913972544</v>
+      </c>
+      <c r="T65">
+        <v>2.143350897397024</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.003163051161664917</v>
+      </c>
+      <c r="W65">
+        <v>0.2380446633825944</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.02108700774443273</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2392881061008758</v>
+      </c>
+      <c r="C66">
+        <v>-1.38941551680804</v>
+      </c>
+      <c r="D66">
+        <v>2.46358448319196</v>
+      </c>
+      <c r="E66">
+        <v>3.44</v>
+      </c>
+      <c r="F66">
+        <v>4.64</v>
+      </c>
+      <c r="G66">
+        <v>0.787</v>
+      </c>
+      <c r="H66">
+        <v>6.05</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.241</v>
+      </c>
+      <c r="K66">
+        <v>0.218</v>
+      </c>
+      <c r="L66">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M66">
+        <v>1.108032</v>
+      </c>
+      <c r="N66">
+        <v>-1.085032</v>
+      </c>
+      <c r="O66">
+        <v>-0.1627547999999999</v>
+      </c>
+      <c r="P66">
+        <v>-0.9222772000000001</v>
+      </c>
+      <c r="Q66">
+        <v>-0.7042772000000002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2414776893606703</v>
+      </c>
+      <c r="T66">
+        <v>2.202888422324719</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.003113628487263903</v>
+      </c>
+      <c r="W66">
+        <v>0.2380564655172414</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.02075752324842595</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2412881061008758</v>
+      </c>
+      <c r="C67">
+        <v>-1.486248644621134</v>
+      </c>
+      <c r="D67">
+        <v>2.439251355378866</v>
+      </c>
+      <c r="E67">
+        <v>3.5125</v>
+      </c>
+      <c r="F67">
+        <v>4.7125</v>
+      </c>
+      <c r="G67">
+        <v>0.787</v>
+      </c>
+      <c r="H67">
+        <v>6.05</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.241</v>
+      </c>
+      <c r="K67">
+        <v>0.218</v>
+      </c>
+      <c r="L67">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M67">
+        <v>1.125345</v>
+      </c>
+      <c r="N67">
+        <v>-1.102345</v>
+      </c>
+      <c r="O67">
+        <v>-0.1653517499999999</v>
+      </c>
+      <c r="P67">
+        <v>-0.9369932500000002</v>
+      </c>
+      <c r="Q67">
+        <v>-0.7189932500000003</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2472684804852609</v>
+      </c>
+      <c r="T67">
+        <v>2.265828091533997</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.003065726510536766</v>
+      </c>
+      <c r="W67">
+        <v>0.2380679045092838</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.02043817673691173</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2432881061008758</v>
+      </c>
+      <c r="C68">
+        <v>-1.582605791150483</v>
+      </c>
+      <c r="D68">
+        <v>2.415394208849517</v>
+      </c>
+      <c r="E68">
+        <v>3.585</v>
+      </c>
+      <c r="F68">
+        <v>4.785</v>
+      </c>
+      <c r="G68">
+        <v>0.787</v>
+      </c>
+      <c r="H68">
+        <v>6.05</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.241</v>
+      </c>
+      <c r="K68">
+        <v>0.218</v>
+      </c>
+      <c r="L68">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M68">
+        <v>1.142658</v>
+      </c>
+      <c r="N68">
+        <v>-1.119658</v>
+      </c>
+      <c r="O68">
+        <v>-0.1679487</v>
+      </c>
+      <c r="P68">
+        <v>-0.9517093000000003</v>
+      </c>
+      <c r="Q68">
+        <v>-0.7337093000000003</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2533999063818861</v>
+      </c>
+      <c r="T68">
+        <v>2.332470094226173</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.003019276108861966</v>
+      </c>
+      <c r="W68">
+        <v>0.2380789968652038</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.02012850739241301</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2452881061008758</v>
+      </c>
+      <c r="C69">
+        <v>-1.678500787157367</v>
+      </c>
+      <c r="D69">
+        <v>2.391999212842633</v>
+      </c>
+      <c r="E69">
+        <v>3.6575</v>
+      </c>
+      <c r="F69">
+        <v>4.8575</v>
+      </c>
+      <c r="G69">
+        <v>0.787</v>
+      </c>
+      <c r="H69">
+        <v>6.05</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.241</v>
+      </c>
+      <c r="K69">
+        <v>0.218</v>
+      </c>
+      <c r="L69">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M69">
+        <v>1.159971</v>
+      </c>
+      <c r="N69">
+        <v>-1.136971</v>
+      </c>
+      <c r="O69">
+        <v>-0.1705456499999999</v>
+      </c>
+      <c r="P69">
+        <v>-0.9664253500000002</v>
+      </c>
+      <c r="Q69">
+        <v>-0.7484253500000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.259902933848004</v>
+      </c>
+      <c r="T69">
+        <v>2.403151006172421</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.002974212286341638</v>
+      </c>
+      <c r="W69">
+        <v>0.2380897581060216</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.01982808190894425</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2472881061008758</v>
+      </c>
+      <c r="C70">
+        <v>-1.7739469326961</v>
+      </c>
+      <c r="D70">
+        <v>2.3690530673039</v>
+      </c>
+      <c r="E70">
+        <v>3.73</v>
+      </c>
+      <c r="F70">
+        <v>4.930000000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.787</v>
+      </c>
+      <c r="H70">
+        <v>6.05</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.241</v>
+      </c>
+      <c r="K70">
+        <v>0.218</v>
+      </c>
+      <c r="L70">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M70">
+        <v>1.177284</v>
+      </c>
+      <c r="N70">
+        <v>-1.154284</v>
+      </c>
+      <c r="O70">
+        <v>-0.1731426</v>
+      </c>
+      <c r="P70">
+        <v>-0.9811414000000004</v>
+      </c>
+      <c r="Q70">
+        <v>-0.7631414000000004</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2668124005307541</v>
+      </c>
+      <c r="T70">
+        <v>2.478249475115309</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.002930473870366026</v>
+      </c>
+      <c r="W70">
+        <v>0.2381002028397566</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.01953649246910683</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2492881061008758</v>
+      </c>
+      <c r="C71">
+        <v>-1.868957022327184</v>
+      </c>
+      <c r="D71">
+        <v>2.346542977672817</v>
+      </c>
+      <c r="E71">
+        <v>3.8025</v>
+      </c>
+      <c r="F71">
+        <v>5.0025</v>
+      </c>
+      <c r="G71">
+        <v>0.787</v>
+      </c>
+      <c r="H71">
+        <v>6.05</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.241</v>
+      </c>
+      <c r="K71">
+        <v>0.218</v>
+      </c>
+      <c r="L71">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M71">
+        <v>1.194597</v>
+      </c>
+      <c r="N71">
+        <v>-1.171597</v>
+      </c>
+      <c r="O71">
+        <v>-0.1757395499999999</v>
+      </c>
+      <c r="P71">
+        <v>-0.9958574500000003</v>
+      </c>
+      <c r="Q71">
+        <v>-0.7778574500000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2741676392575526</v>
+      </c>
+      <c r="T71">
+        <v>2.558193006570642</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.002888003234563619</v>
+      </c>
+      <c r="W71">
+        <v>0.2381103448275862</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.01925335489709079</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2512881061008758</v>
+      </c>
+      <c r="C72">
+        <v>-1.96354336890659</v>
+      </c>
+      <c r="D72">
+        <v>2.32445663109341</v>
+      </c>
+      <c r="E72">
+        <v>3.875</v>
+      </c>
+      <c r="F72">
+        <v>5.075</v>
+      </c>
+      <c r="G72">
+        <v>0.787</v>
+      </c>
+      <c r="H72">
+        <v>6.05</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.241</v>
+      </c>
+      <c r="K72">
+        <v>0.218</v>
+      </c>
+      <c r="L72">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M72">
+        <v>1.21191</v>
+      </c>
+      <c r="N72">
+        <v>-1.18891</v>
+      </c>
+      <c r="O72">
+        <v>-0.1783364999999999</v>
+      </c>
+      <c r="P72">
+        <v>-1.0105735</v>
+      </c>
+      <c r="Q72">
+        <v>-0.7925735000000003</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2820132272328044</v>
+      </c>
+      <c r="T72">
+        <v>2.643466106789663</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.002846746045498425</v>
+      </c>
+      <c r="W72">
+        <v>0.238120197044335</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.01897830696998948</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2532881061008758</v>
+      </c>
+      <c r="C73">
+        <v>-2.057717826044088</v>
+      </c>
+      <c r="D73">
+        <v>2.302782173955912</v>
+      </c>
+      <c r="E73">
+        <v>3.9475</v>
+      </c>
+      <c r="F73">
+        <v>5.1475</v>
+      </c>
+      <c r="G73">
+        <v>0.787</v>
+      </c>
+      <c r="H73">
+        <v>6.05</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.241</v>
+      </c>
+      <c r="K73">
+        <v>0.218</v>
+      </c>
+      <c r="L73">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M73">
+        <v>1.229223</v>
+      </c>
+      <c r="N73">
+        <v>-1.206223</v>
+      </c>
+      <c r="O73">
+        <v>-0.1809334499999999</v>
+      </c>
+      <c r="P73">
+        <v>-1.02528955</v>
+      </c>
+      <c r="Q73">
+        <v>-0.8072895500000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2903998902408321</v>
+      </c>
+      <c r="T73">
+        <v>2.734620110472065</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.002806651030773096</v>
+      </c>
+      <c r="W73">
+        <v>0.2381297717338514</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.01871100687182059</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2552881061008758</v>
+      </c>
+      <c r="C74">
+        <v>-2.151491809316711</v>
+      </c>
+      <c r="D74">
+        <v>2.281508190683289</v>
+      </c>
+      <c r="E74">
+        <v>4.02</v>
+      </c>
+      <c r="F74">
+        <v>5.22</v>
+      </c>
+      <c r="G74">
+        <v>0.787</v>
+      </c>
+      <c r="H74">
+        <v>6.05</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.241</v>
+      </c>
+      <c r="K74">
+        <v>0.218</v>
+      </c>
+      <c r="L74">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M74">
+        <v>1.246536</v>
+      </c>
+      <c r="N74">
+        <v>-1.223536</v>
+      </c>
+      <c r="O74">
+        <v>-0.1835303999999999</v>
+      </c>
+      <c r="P74">
+        <v>-1.0400056</v>
+      </c>
+      <c r="Q74">
+        <v>-0.8220056000000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.299385600606576</v>
+      </c>
+      <c r="T74">
+        <v>2.832285114417496</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.002767669766456802</v>
+      </c>
+      <c r="W74">
+        <v>0.2381390804597701</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.01845113177637858</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2572881061008758</v>
+      </c>
+      <c r="C75">
+        <v>-2.244876316317104</v>
+      </c>
+      <c r="D75">
+        <v>2.260623683682895</v>
+      </c>
+      <c r="E75">
+        <v>4.092499999999999</v>
+      </c>
+      <c r="F75">
+        <v>5.2925</v>
+      </c>
+      <c r="G75">
+        <v>0.787</v>
+      </c>
+      <c r="H75">
+        <v>6.05</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.241</v>
+      </c>
+      <c r="K75">
+        <v>0.218</v>
+      </c>
+      <c r="L75">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M75">
+        <v>1.263849</v>
+      </c>
+      <c r="N75">
+        <v>-1.240849</v>
+      </c>
+      <c r="O75">
+        <v>-0.1861273499999999</v>
+      </c>
+      <c r="P75">
+        <v>-1.05472165</v>
+      </c>
+      <c r="Q75">
+        <v>-0.8367216500000003</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3090369191475603</v>
+      </c>
+      <c r="T75">
+        <v>2.937184563099625</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.002729756481984792</v>
+      </c>
+      <c r="W75">
+        <v>0.238148134152102</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.0181983765465652</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2592881061008758</v>
+      </c>
+      <c r="C76">
+        <v>-2.337881945610766</v>
+      </c>
+      <c r="D76">
+        <v>2.240118054389235</v>
+      </c>
+      <c r="E76">
+        <v>4.165</v>
+      </c>
+      <c r="F76">
+        <v>5.365</v>
+      </c>
+      <c r="G76">
+        <v>0.787</v>
+      </c>
+      <c r="H76">
+        <v>6.05</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.241</v>
+      </c>
+      <c r="K76">
+        <v>0.218</v>
+      </c>
+      <c r="L76">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M76">
+        <v>1.281162</v>
+      </c>
+      <c r="N76">
+        <v>-1.258162</v>
+      </c>
+      <c r="O76">
+        <v>-0.1887242999999999</v>
+      </c>
+      <c r="P76">
+        <v>-1.0694377</v>
+      </c>
+      <c r="Q76">
+        <v>-0.8514377000000004</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3194306468070819</v>
+      </c>
+      <c r="T76">
+        <v>3.050153200141918</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.002692867880876889</v>
+      </c>
+      <c r="W76">
+        <v>0.2381569431500466</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.01795245253917921</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2612881061008758</v>
+      </c>
+      <c r="C77">
+        <v>-2.430518914670797</v>
+      </c>
+      <c r="D77">
+        <v>2.219981085329203</v>
+      </c>
+      <c r="E77">
+        <v>4.2375</v>
+      </c>
+      <c r="F77">
+        <v>5.4375</v>
+      </c>
+      <c r="G77">
+        <v>0.787</v>
+      </c>
+      <c r="H77">
+        <v>6.05</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.241</v>
+      </c>
+      <c r="K77">
+        <v>0.218</v>
+      </c>
+      <c r="L77">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M77">
+        <v>1.298475</v>
+      </c>
+      <c r="N77">
+        <v>-1.275475</v>
+      </c>
+      <c r="O77">
+        <v>-0.1913212499999999</v>
+      </c>
+      <c r="P77">
+        <v>-1.08415375</v>
+      </c>
+      <c r="Q77">
+        <v>-0.8661537500000003</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3306558726793652</v>
+      </c>
+      <c r="T77">
+        <v>3.172159328147595</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.00265696297579853</v>
+      </c>
+      <c r="W77">
+        <v>0.2381655172413793</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.01771308650532344</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2632881061008758</v>
+      </c>
+      <c r="C78">
+        <v>-2.522797076853979</v>
+      </c>
+      <c r="D78">
+        <v>2.200202923146021</v>
+      </c>
+      <c r="E78">
+        <v>4.31</v>
+      </c>
+      <c r="F78">
+        <v>5.51</v>
+      </c>
+      <c r="G78">
+        <v>0.787</v>
+      </c>
+      <c r="H78">
+        <v>6.05</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.241</v>
+      </c>
+      <c r="K78">
+        <v>0.218</v>
+      </c>
+      <c r="L78">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M78">
+        <v>1.315788</v>
+      </c>
+      <c r="N78">
+        <v>-1.292788</v>
+      </c>
+      <c r="O78">
+        <v>-0.1939181999999999</v>
+      </c>
+      <c r="P78">
+        <v>-1.0988698</v>
+      </c>
+      <c r="Q78">
+        <v>-0.8808698000000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3428165340410054</v>
+      </c>
+      <c r="T78">
+        <v>3.304332633487078</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.002622002936643287</v>
+      </c>
+      <c r="W78">
+        <v>0.2381738656987296</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.01748001957762191</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2652881061008758</v>
+      </c>
+      <c r="C79">
+        <v>-2.614725937477381</v>
+      </c>
+      <c r="D79">
+        <v>2.18077406252262</v>
+      </c>
+      <c r="E79">
+        <v>4.3825</v>
+      </c>
+      <c r="F79">
+        <v>5.5825</v>
+      </c>
+      <c r="G79">
+        <v>0.787</v>
+      </c>
+      <c r="H79">
+        <v>6.05</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.241</v>
+      </c>
+      <c r="K79">
+        <v>0.218</v>
+      </c>
+      <c r="L79">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M79">
+        <v>1.333101</v>
+      </c>
+      <c r="N79">
+        <v>-1.310101</v>
+      </c>
+      <c r="O79">
+        <v>-0.1965151499999999</v>
+      </c>
+      <c r="P79">
+        <v>-1.11358585</v>
+      </c>
+      <c r="Q79">
+        <v>-0.8955858500000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3560346442167013</v>
+      </c>
+      <c r="T79">
+        <v>3.447999269725647</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.002587950950453114</v>
+      </c>
+      <c r="W79">
+        <v>0.2381819973130318</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.01725300633635407</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2672881061008758</v>
+      </c>
+      <c r="C80">
+        <v>-2.706314669050655</v>
+      </c>
+      <c r="D80">
+        <v>2.161685330949346</v>
+      </c>
+      <c r="E80">
+        <v>4.455</v>
+      </c>
+      <c r="F80">
+        <v>5.655</v>
+      </c>
+      <c r="G80">
+        <v>0.787</v>
+      </c>
+      <c r="H80">
+        <v>6.05</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.241</v>
+      </c>
+      <c r="K80">
+        <v>0.218</v>
+      </c>
+      <c r="L80">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M80">
+        <v>1.350414</v>
+      </c>
+      <c r="N80">
+        <v>-1.327414</v>
+      </c>
+      <c r="O80">
+        <v>-0.1991120999999999</v>
+      </c>
+      <c r="P80">
+        <v>-1.1283019</v>
+      </c>
+      <c r="Q80">
+        <v>-0.9103019000000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.370454400772006</v>
+      </c>
+      <c r="T80">
+        <v>3.604726509258632</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.002554772092113971</v>
+      </c>
+      <c r="W80">
+        <v>0.2381899204244032</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.01703181394742648</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2692881061008758</v>
+      </c>
+      <c r="C81">
+        <v>-2.797572125715279</v>
+      </c>
+      <c r="D81">
+        <v>2.142927874284721</v>
+      </c>
+      <c r="E81">
+        <v>4.5275</v>
+      </c>
+      <c r="F81">
+        <v>5.7275</v>
+      </c>
+      <c r="G81">
+        <v>0.787</v>
+      </c>
+      <c r="H81">
+        <v>6.05</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.241</v>
+      </c>
+      <c r="K81">
+        <v>0.218</v>
+      </c>
+      <c r="L81">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M81">
+        <v>1.367727</v>
+      </c>
+      <c r="N81">
+        <v>-1.344727</v>
+      </c>
+      <c r="O81">
+        <v>-0.2017090499999999</v>
+      </c>
+      <c r="P81">
+        <v>-1.14301795</v>
+      </c>
+      <c r="Q81">
+        <v>-0.9250179500000004</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3862474674754348</v>
+      </c>
+      <c r="T81">
+        <v>3.776380152556662</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.002522433204872023</v>
+      </c>
+      <c r="W81">
+        <v>0.2381976429506766</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.0168162213658134</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2712881061008758</v>
+      </c>
+      <c r="C82">
+        <v>-2.888506856938519</v>
+      </c>
+      <c r="D82">
+        <v>2.124493143061482</v>
+      </c>
+      <c r="E82">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="F82">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="G82">
+        <v>0.787</v>
+      </c>
+      <c r="H82">
+        <v>6.05</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.241</v>
+      </c>
+      <c r="K82">
+        <v>0.218</v>
+      </c>
+      <c r="L82">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M82">
+        <v>1.38504</v>
+      </c>
+      <c r="N82">
+        <v>-1.36204</v>
+      </c>
+      <c r="O82">
+        <v>-0.2043059999999999</v>
+      </c>
+      <c r="P82">
+        <v>-1.157734</v>
+      </c>
+      <c r="Q82">
+        <v>-0.9397340000000005</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4036198408492066</v>
+      </c>
+      <c r="T82">
+        <v>3.965199160184495</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.002490902789811122</v>
+      </c>
+      <c r="W82">
+        <v>0.2382051724137931</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.01660601859874078</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2732881061008758</v>
+      </c>
+      <c r="C83">
+        <v>-2.979127120506578</v>
+      </c>
+      <c r="D83">
+        <v>2.106372879493423</v>
+      </c>
+      <c r="E83">
+        <v>4.6725</v>
+      </c>
+      <c r="F83">
+        <v>5.8725</v>
+      </c>
+      <c r="G83">
+        <v>0.787</v>
+      </c>
+      <c r="H83">
+        <v>6.05</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.241</v>
+      </c>
+      <c r="K83">
+        <v>0.218</v>
+      </c>
+      <c r="L83">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M83">
+        <v>1.402353</v>
+      </c>
+      <c r="N83">
+        <v>-1.379353</v>
+      </c>
+      <c r="O83">
+        <v>-0.2069029499999999</v>
+      </c>
+      <c r="P83">
+        <v>-1.17245005</v>
+      </c>
+      <c r="Q83">
+        <v>-0.9544500500000004</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4228208851044279</v>
+      </c>
+      <c r="T83">
+        <v>4.173893852825784</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.002460150903517157</v>
+      </c>
+      <c r="W83">
+        <v>0.2382125159642401</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.01640100602344763</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2752881061008758</v>
+      </c>
+      <c r="C84">
+        <v>-3.069440894858467</v>
+      </c>
+      <c r="D84">
+        <v>2.088559105141533</v>
+      </c>
+      <c r="E84">
+        <v>4.745</v>
+      </c>
+      <c r="F84">
+        <v>5.945</v>
+      </c>
+      <c r="G84">
+        <v>0.787</v>
+      </c>
+      <c r="H84">
+        <v>6.05</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.241</v>
+      </c>
+      <c r="K84">
+        <v>0.218</v>
+      </c>
+      <c r="L84">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M84">
+        <v>1.419666</v>
+      </c>
+      <c r="N84">
+        <v>-1.396666</v>
+      </c>
+      <c r="O84">
+        <v>-0.2094998999999999</v>
+      </c>
+      <c r="P84">
+        <v>-1.1871661</v>
+      </c>
+      <c r="Q84">
+        <v>-0.9691661000000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4441553787213407</v>
+      </c>
+      <c r="T84">
+        <v>4.40577684464944</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.002430149063230363</v>
+      </c>
+      <c r="W84">
+        <v>0.2382196804037006</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.01620099375486905</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2772881061008758</v>
+      </c>
+      <c r="C85">
+        <v>-3.159455890799256</v>
+      </c>
+      <c r="D85">
+        <v>2.071044109200745</v>
+      </c>
+      <c r="E85">
+        <v>4.8175</v>
+      </c>
+      <c r="F85">
+        <v>6.0175</v>
+      </c>
+      <c r="G85">
+        <v>0.787</v>
+      </c>
+      <c r="H85">
+        <v>6.05</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.241</v>
+      </c>
+      <c r="K85">
+        <v>0.218</v>
+      </c>
+      <c r="L85">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M85">
+        <v>1.436979</v>
+      </c>
+      <c r="N85">
+        <v>-1.413979</v>
+      </c>
+      <c r="O85">
+        <v>-0.2120968499999999</v>
+      </c>
+      <c r="P85">
+        <v>-1.20188215</v>
+      </c>
+      <c r="Q85">
+        <v>-0.9838821500000003</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4679998127637725</v>
+      </c>
+      <c r="T85">
+        <v>4.664940188452348</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.002400870158854094</v>
+      </c>
+      <c r="W85">
+        <v>0.2382266722060657</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.01600580105902727</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2792881061008758</v>
+      </c>
+      <c r="C86">
+        <v>-3.249179562628847</v>
+      </c>
+      <c r="D86">
+        <v>2.053820437371153</v>
+      </c>
+      <c r="E86">
+        <v>4.89</v>
+      </c>
+      <c r="F86">
+        <v>6.09</v>
+      </c>
+      <c r="G86">
+        <v>0.787</v>
+      </c>
+      <c r="H86">
+        <v>6.05</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.241</v>
+      </c>
+      <c r="K86">
+        <v>0.218</v>
+      </c>
+      <c r="L86">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M86">
+        <v>1.454292</v>
+      </c>
+      <c r="N86">
+        <v>-1.431292</v>
+      </c>
+      <c r="O86">
+        <v>-0.2146937999999999</v>
+      </c>
+      <c r="P86">
+        <v>-1.2165982</v>
+      </c>
+      <c r="Q86">
+        <v>-0.9985982000000004</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4948248010615081</v>
+      </c>
+      <c r="T86">
+        <v>4.956498950230617</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.002372288371248688</v>
+      </c>
+      <c r="W86">
+        <v>0.2382334975369458</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.01581525580832455</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2812881061008758</v>
+      </c>
+      <c r="C87">
+        <v>-3.338619118720036</v>
+      </c>
+      <c r="D87">
+        <v>2.036880881279963</v>
+      </c>
+      <c r="E87">
+        <v>4.962499999999999</v>
+      </c>
+      <c r="F87">
+        <v>6.1625</v>
+      </c>
+      <c r="G87">
+        <v>0.787</v>
+      </c>
+      <c r="H87">
+        <v>6.05</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.241</v>
+      </c>
+      <c r="K87">
+        <v>0.218</v>
+      </c>
+      <c r="L87">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M87">
+        <v>1.471605</v>
+      </c>
+      <c r="N87">
+        <v>-1.448605</v>
+      </c>
+      <c r="O87">
+        <v>-0.2172907499999999</v>
+      </c>
+      <c r="P87">
+        <v>-1.23131425</v>
+      </c>
+      <c r="Q87">
+        <v>-1.01331425</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5252264544656087</v>
+      </c>
+      <c r="T87">
+        <v>5.286932213579325</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.002344379096292821</v>
+      </c>
+      <c r="W87">
+        <v>0.2382401622718053</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.01562919397528539</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2832881061008758</v>
+      </c>
+      <c r="C88">
+        <v>-3.427781531577369</v>
+      </c>
+      <c r="D88">
+        <v>2.020218468422631</v>
+      </c>
+      <c r="E88">
+        <v>5.035</v>
+      </c>
+      <c r="F88">
+        <v>6.235</v>
+      </c>
+      <c r="G88">
+        <v>0.787</v>
+      </c>
+      <c r="H88">
+        <v>6.05</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.241</v>
+      </c>
+      <c r="K88">
+        <v>0.218</v>
+      </c>
+      <c r="L88">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M88">
+        <v>1.488918</v>
+      </c>
+      <c r="N88">
+        <v>-1.465918</v>
+      </c>
+      <c r="O88">
+        <v>-0.2198876999999999</v>
+      </c>
+      <c r="P88">
+        <v>-1.2460303</v>
+      </c>
+      <c r="Q88">
+        <v>-1.0280303</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5599712012131521</v>
+      </c>
+      <c r="T88">
+        <v>5.664570228834991</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.002317118874242904</v>
+      </c>
+      <c r="W88">
+        <v>0.2382466720128308</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.01544745916161927</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2852881061008758</v>
+      </c>
+      <c r="C89">
+        <v>-3.516673547406286</v>
+      </c>
+      <c r="D89">
+        <v>2.003826452593714</v>
+      </c>
+      <c r="E89">
+        <v>5.1075</v>
+      </c>
+      <c r="F89">
+        <v>6.3075</v>
+      </c>
+      <c r="G89">
+        <v>0.787</v>
+      </c>
+      <c r="H89">
+        <v>6.05</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.241</v>
+      </c>
+      <c r="K89">
+        <v>0.218</v>
+      </c>
+      <c r="L89">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M89">
+        <v>1.506231</v>
+      </c>
+      <c r="N89">
+        <v>-1.483231</v>
+      </c>
+      <c r="O89">
+        <v>-0.2224846499999999</v>
+      </c>
+      <c r="P89">
+        <v>-1.26074635</v>
+      </c>
+      <c r="Q89">
+        <v>-1.04274635</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6000612936141638</v>
+      </c>
+      <c r="T89">
+        <v>6.100306400283836</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.00229048532396425</v>
+      </c>
+      <c r="W89">
+        <v>0.2382530321046374</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.01526990215976165</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2872881061008758</v>
+      </c>
+      <c r="C90">
+        <v>-3.605301695220172</v>
+      </c>
+      <c r="D90">
+        <v>1.987698304779828</v>
+      </c>
+      <c r="E90">
+        <v>5.18</v>
+      </c>
+      <c r="F90">
+        <v>6.38</v>
+      </c>
+      <c r="G90">
+        <v>0.787</v>
+      </c>
+      <c r="H90">
+        <v>6.05</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.241</v>
+      </c>
+      <c r="K90">
+        <v>0.218</v>
+      </c>
+      <c r="L90">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M90">
+        <v>1.523544</v>
+      </c>
+      <c r="N90">
+        <v>-1.500544</v>
+      </c>
+      <c r="O90">
+        <v>-0.2250815999999999</v>
+      </c>
+      <c r="P90">
+        <v>-1.2754624</v>
+      </c>
+      <c r="Q90">
+        <v>-1.0574624</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6468330680820109</v>
+      </c>
+      <c r="T90">
+        <v>6.608665266974157</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.002264457081646475</v>
+      </c>
+      <c r="W90">
+        <v>0.2382592476489028</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.01509638054430984</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2892881061008758</v>
+      </c>
+      <c r="C91">
+        <v>-3.693672295511103</v>
+      </c>
+      <c r="D91">
+        <v>1.971827704488896</v>
+      </c>
+      <c r="E91">
+        <v>5.2525</v>
+      </c>
+      <c r="F91">
+        <v>6.4525</v>
+      </c>
+      <c r="G91">
+        <v>0.787</v>
+      </c>
+      <c r="H91">
+        <v>6.05</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.241</v>
+      </c>
+      <c r="K91">
+        <v>0.218</v>
+      </c>
+      <c r="L91">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M91">
+        <v>1.540857</v>
+      </c>
+      <c r="N91">
+        <v>-1.517857</v>
+      </c>
+      <c r="O91">
+        <v>-0.2276785499999999</v>
+      </c>
+      <c r="P91">
+        <v>-1.29017845</v>
+      </c>
+      <c r="Q91">
+        <v>-1.07217845</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.702108801544012</v>
+      </c>
+      <c r="T91">
+        <v>7.209453018517263</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.002239013743650447</v>
+      </c>
+      <c r="W91">
+        <v>0.2382653235180163</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.01492675829100298</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2912881061008758</v>
+      </c>
+      <c r="C92">
+        <v>-3.781791468508513</v>
+      </c>
+      <c r="D92">
+        <v>1.956208531491487</v>
+      </c>
+      <c r="E92">
+        <v>5.325</v>
+      </c>
+      <c r="F92">
+        <v>6.525</v>
+      </c>
+      <c r="G92">
+        <v>0.787</v>
+      </c>
+      <c r="H92">
+        <v>6.05</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.241</v>
+      </c>
+      <c r="K92">
+        <v>0.218</v>
+      </c>
+      <c r="L92">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M92">
+        <v>1.55817</v>
+      </c>
+      <c r="N92">
+        <v>-1.53517</v>
+      </c>
+      <c r="O92">
+        <v>-0.2302754999999999</v>
+      </c>
+      <c r="P92">
+        <v>-1.3048945</v>
+      </c>
+      <c r="Q92">
+        <v>-1.0868945</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7684396816984131</v>
+      </c>
+      <c r="T92">
+        <v>7.93039832036899</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.002214135813165442</v>
+      </c>
+      <c r="W92">
+        <v>0.2382712643678161</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.01476090542110287</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2932881061008757</v>
+      </c>
+      <c r="C93">
+        <v>-3.869665142048416</v>
+      </c>
+      <c r="D93">
+        <v>1.940834857951585</v>
+      </c>
+      <c r="E93">
+        <v>5.3975</v>
+      </c>
+      <c r="F93">
+        <v>6.5975</v>
+      </c>
+      <c r="G93">
+        <v>0.787</v>
+      </c>
+      <c r="H93">
+        <v>6.05</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.241</v>
+      </c>
+      <c r="K93">
+        <v>0.218</v>
+      </c>
+      <c r="L93">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M93">
+        <v>1.575483</v>
+      </c>
+      <c r="N93">
+        <v>-1.552483</v>
+      </c>
+      <c r="O93">
+        <v>-0.2328724499999999</v>
+      </c>
+      <c r="P93">
+        <v>-1.31961055</v>
+      </c>
+      <c r="Q93">
+        <v>-1.10161055</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8495107574426812</v>
+      </c>
+      <c r="T93">
+        <v>8.811553689298878</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.002189804650383404</v>
+      </c>
+      <c r="W93">
+        <v>0.2382770746494884</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.01459869766922262</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2952881061008758</v>
+      </c>
+      <c r="C94">
+        <v>-3.95729905907448</v>
+      </c>
+      <c r="D94">
+        <v>1.92570094092552</v>
+      </c>
+      <c r="E94">
+        <v>5.47</v>
+      </c>
+      <c r="F94">
+        <v>6.67</v>
+      </c>
+      <c r="G94">
+        <v>0.787</v>
+      </c>
+      <c r="H94">
+        <v>6.05</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.241</v>
+      </c>
+      <c r="K94">
+        <v>0.218</v>
+      </c>
+      <c r="L94">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M94">
+        <v>1.592796</v>
+      </c>
+      <c r="N94">
+        <v>-1.569796</v>
+      </c>
+      <c r="O94">
+        <v>-0.2354693999999999</v>
+      </c>
+      <c r="P94">
+        <v>-1.3343266</v>
+      </c>
+      <c r="Q94">
+        <v>-1.1163266</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9508496021230166</v>
+      </c>
+      <c r="T94">
+        <v>9.912997900461241</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.002166002425922715</v>
+      </c>
+      <c r="W94">
+        <v>0.2382827586206897</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.01444001617281809</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2972881061008758</v>
+      </c>
+      <c r="C95">
+        <v>-4.044698784790867</v>
+      </c>
+      <c r="D95">
+        <v>1.910801215209134</v>
+      </c>
+      <c r="E95">
+        <v>5.5425</v>
+      </c>
+      <c r="F95">
+        <v>6.742500000000001</v>
+      </c>
+      <c r="G95">
+        <v>0.787</v>
+      </c>
+      <c r="H95">
+        <v>6.05</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.241</v>
+      </c>
+      <c r="K95">
+        <v>0.218</v>
+      </c>
+      <c r="L95">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M95">
+        <v>1.610109</v>
+      </c>
+      <c r="N95">
+        <v>-1.587109</v>
+      </c>
+      <c r="O95">
+        <v>-0.2380663499999999</v>
+      </c>
+      <c r="P95">
+        <v>-1.34904265</v>
+      </c>
+      <c r="Q95">
+        <v>-1.13104265</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.081142402426305</v>
+      </c>
+      <c r="T95">
+        <v>11.32914045766999</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.002142712077256879</v>
+      </c>
+      <c r="W95">
+        <v>0.2382883203559511</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.01428474718171246</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2992881061008758</v>
+      </c>
+      <c r="C96">
+        <v>-4.131869713485547</v>
+      </c>
+      <c r="D96">
+        <v>1.896130286514453</v>
+      </c>
+      <c r="E96">
+        <v>5.615</v>
+      </c>
+      <c r="F96">
+        <v>6.815</v>
+      </c>
+      <c r="G96">
+        <v>0.787</v>
+      </c>
+      <c r="H96">
+        <v>6.05</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.241</v>
+      </c>
+      <c r="K96">
+        <v>0.218</v>
+      </c>
+      <c r="L96">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M96">
+        <v>1.627422</v>
+      </c>
+      <c r="N96">
+        <v>-1.604422</v>
+      </c>
+      <c r="O96">
+        <v>-0.2406632999999999</v>
+      </c>
+      <c r="P96">
+        <v>-1.3637587</v>
+      </c>
+      <c r="Q96">
+        <v>-1.1457587</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.254866136164023</v>
+      </c>
+      <c r="T96">
+        <v>13.21733053394832</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.002119917267924359</v>
+      </c>
+      <c r="W96">
+        <v>0.2382937637564197</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.0141327817861624</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3012881061008758</v>
+      </c>
+      <c r="C97">
+        <v>-4.218817075041699</v>
+      </c>
+      <c r="D97">
+        <v>1.881682924958301</v>
+      </c>
+      <c r="E97">
+        <v>5.6875</v>
+      </c>
+      <c r="F97">
+        <v>6.8875</v>
+      </c>
+      <c r="G97">
+        <v>0.787</v>
+      </c>
+      <c r="H97">
+        <v>6.05</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.241</v>
+      </c>
+      <c r="K97">
+        <v>0.218</v>
+      </c>
+      <c r="L97">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M97">
+        <v>1.644735</v>
+      </c>
+      <c r="N97">
+        <v>-1.621735</v>
+      </c>
+      <c r="O97">
+        <v>-0.2432602499999999</v>
+      </c>
+      <c r="P97">
+        <v>-1.37847475</v>
+      </c>
+      <c r="Q97">
+        <v>-1.16047475</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.498079363396828</v>
+      </c>
+      <c r="T97">
+        <v>15.860796640738</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.002097602349314629</v>
+      </c>
+      <c r="W97">
+        <v>0.2382990925589837</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.0139840156620975</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3032881061008758</v>
+      </c>
+      <c r="C98">
+        <v>-4.305545941153663</v>
+      </c>
+      <c r="D98">
+        <v>1.867454058846337</v>
+      </c>
+      <c r="E98">
+        <v>5.76</v>
+      </c>
+      <c r="F98">
+        <v>6.96</v>
+      </c>
+      <c r="G98">
+        <v>0.787</v>
+      </c>
+      <c r="H98">
+        <v>6.05</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.241</v>
+      </c>
+      <c r="K98">
+        <v>0.218</v>
+      </c>
+      <c r="L98">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M98">
+        <v>1.662048</v>
+      </c>
+      <c r="N98">
+        <v>-1.639048</v>
+      </c>
+      <c r="O98">
+        <v>-0.2458571999999999</v>
+      </c>
+      <c r="P98">
+        <v>-1.3931908</v>
+      </c>
+      <c r="Q98">
+        <v>-1.1751908</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.862899204246031</v>
+      </c>
+      <c r="T98">
+        <v>19.82599580092245</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.002075752324842602</v>
+      </c>
+      <c r="W98">
+        <v>0.2383043103448276</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.01383834883228396</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3052881061008758</v>
+      </c>
+      <c r="C99">
+        <v>-4.392061231263005</v>
+      </c>
+      <c r="D99">
+        <v>1.853438768736995</v>
+      </c>
+      <c r="E99">
+        <v>5.8325</v>
+      </c>
+      <c r="F99">
+        <v>7.0325</v>
+      </c>
+      <c r="G99">
+        <v>0.787</v>
+      </c>
+      <c r="H99">
+        <v>6.05</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.241</v>
+      </c>
+      <c r="K99">
+        <v>0.218</v>
+      </c>
+      <c r="L99">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M99">
+        <v>1.679361</v>
+      </c>
+      <c r="N99">
+        <v>-1.656361</v>
+      </c>
+      <c r="O99">
+        <v>-0.2484541499999999</v>
+      </c>
+      <c r="P99">
+        <v>-1.40790685</v>
+      </c>
+      <c r="Q99">
+        <v>-1.18990685</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.470932272328042</v>
+      </c>
+      <c r="T99">
+        <v>26.43466106789661</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.00205435281633907</v>
+      </c>
+      <c r="W99">
+        <v>0.2383094205474582</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.01369568544226041</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3072881061008758</v>
+      </c>
+      <c r="C100">
+        <v>-4.478367718229251</v>
+      </c>
+      <c r="D100">
+        <v>1.839632281770749</v>
+      </c>
+      <c r="E100">
+        <v>5.904999999999999</v>
+      </c>
+      <c r="F100">
+        <v>7.105</v>
+      </c>
+      <c r="G100">
+        <v>0.787</v>
+      </c>
+      <c r="H100">
+        <v>6.05</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.241</v>
+      </c>
+      <c r="K100">
+        <v>0.218</v>
+      </c>
+      <c r="L100">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M100">
+        <v>1.696674</v>
+      </c>
+      <c r="N100">
+        <v>-1.673674</v>
+      </c>
+      <c r="O100">
+        <v>-0.2510510999999999</v>
+      </c>
+      <c r="P100">
+        <v>-1.4226229</v>
+      </c>
+      <c r="Q100">
+        <v>-1.2046229</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.686998408492062</v>
+      </c>
+      <c r="T100">
+        <v>39.65199160184491</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.002033390032498875</v>
+      </c>
+      <c r="W100">
+        <v>0.2383144264602393</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.01355593354999252</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3092881061008758</v>
+      </c>
+      <c r="C101">
+        <v>-4.564470033749068</v>
+      </c>
+      <c r="D101">
+        <v>1.826029966250933</v>
+      </c>
+      <c r="E101">
+        <v>5.9775</v>
+      </c>
+      <c r="F101">
+        <v>7.1775</v>
+      </c>
+      <c r="G101">
+        <v>0.787</v>
+      </c>
+      <c r="H101">
+        <v>6.05</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.241</v>
+      </c>
+      <c r="K101">
+        <v>0.218</v>
+      </c>
+      <c r="L101">
+        <v>0.02299999999999999</v>
+      </c>
+      <c r="M101">
+        <v>1.713987</v>
+      </c>
+      <c r="N101">
+        <v>-1.690987</v>
+      </c>
+      <c r="O101">
+        <v>-0.2536480499999999</v>
+      </c>
+      <c r="P101">
+        <v>-1.43733895</v>
+      </c>
+      <c r="Q101">
+        <v>-1.21933895</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.335196816984124</v>
+      </c>
+      <c r="T101">
+        <v>79.30398320368981</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.002012850739241311</v>
+      </c>
+      <c r="W101">
+        <v>0.2383193312434692</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.01341900492827541</v>
+      </c>
+      <c r="Z101">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/indonesia/indonesia_education.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_education.xlsx
@@ -1385,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1522,22 +1522,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09746149650817788</v>
+        <v>0.09728218121585988</v>
       </c>
       <c r="C2">
-        <v>3.176212333803373</v>
+        <v>3.155448528079642</v>
       </c>
       <c r="D2">
-        <v>3.042212333803373</v>
+        <v>3.052808528079642</v>
       </c>
       <c r="E2">
-        <v>-0.8259999999999998</v>
+        <v>-0.7946399999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.03136</v>
       </c>
       <c r="G2">
         <v>0.134</v>
@@ -1558,28 +1558,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001577408</v>
       </c>
       <c r="N2">
-        <v>0.3136666666666666</v>
+        <v>0.3120892586666666</v>
       </c>
       <c r="O2">
-        <v>0.06900666666666666</v>
+        <v>0.06865963690666667</v>
       </c>
       <c r="P2">
-        <v>0.24466</v>
+        <v>0.24342962176</v>
       </c>
       <c r="Q2">
-        <v>0.53766</v>
+        <v>0.53642962176</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09746149650817788</v>
+        <v>0.09786852648066655</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129923</v>
+        <v>0.75766050386364</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>198.8494204838993</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1604,22 +1604,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09728218121585988</v>
+        <v>0.09710286592354189</v>
       </c>
       <c r="C3">
-        <v>3.155448528079642</v>
+        <v>3.134758794618344</v>
       </c>
       <c r="D3">
-        <v>3.052808528079642</v>
+        <v>3.063478794618344</v>
       </c>
       <c r="E3">
-        <v>-0.7946399999999998</v>
+        <v>-0.7632799999999998</v>
       </c>
       <c r="F3">
-        <v>0.03136</v>
+        <v>0.06272</v>
       </c>
       <c r="G3">
         <v>0.134</v>
@@ -1640,28 +1640,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M3">
-        <v>0.001577408</v>
+        <v>0.003154816</v>
       </c>
       <c r="N3">
-        <v>0.3120892586666666</v>
+        <v>0.3105118506666666</v>
       </c>
       <c r="O3">
-        <v>0.06865963690666667</v>
+        <v>0.06831260714666666</v>
       </c>
       <c r="P3">
-        <v>0.24342962176</v>
+        <v>0.24219924352</v>
       </c>
       <c r="Q3">
-        <v>0.53642962176</v>
+        <v>0.53519924352</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09786852648066655</v>
+        <v>0.09828386318728766</v>
       </c>
       <c r="T3">
-        <v>0.75766050386364</v>
+        <v>0.7637041590173623</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>198.8494204838993</v>
+        <v>99.42471024194965</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1686,22 +1686,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09710286592354189</v>
+        <v>0.0969235506312239</v>
       </c>
       <c r="C4">
-        <v>3.134758794618344</v>
+        <v>3.114143912842418</v>
       </c>
       <c r="D4">
-        <v>3.063478794618344</v>
+        <v>3.074223912842418</v>
       </c>
       <c r="E4">
-        <v>-0.7632799999999998</v>
+        <v>-0.7319199999999999</v>
       </c>
       <c r="F4">
-        <v>0.06272</v>
+        <v>0.09408</v>
       </c>
       <c r="G4">
         <v>0.134</v>
@@ -1722,28 +1722,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M4">
-        <v>0.003154816</v>
+        <v>0.004732223999999999</v>
       </c>
       <c r="N4">
-        <v>0.3105118506666666</v>
+        <v>0.3089344426666666</v>
       </c>
       <c r="O4">
-        <v>0.06831260714666666</v>
+        <v>0.06796557738666666</v>
       </c>
       <c r="P4">
-        <v>0.24219924352</v>
+        <v>0.24096886528</v>
       </c>
       <c r="Q4">
-        <v>0.53519924352</v>
+        <v>0.5339688652800001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09828386318728766</v>
+        <v>0.09870776353734423</v>
       </c>
       <c r="T4">
-        <v>0.7637041590173623</v>
+        <v>0.7698724256175531</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.42471024194965</v>
+        <v>66.28314016129978</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1768,22 +1768,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0969235506312239</v>
+        <v>0.09674423533890593</v>
       </c>
       <c r="C5">
-        <v>3.114143912842418</v>
+        <v>3.093604673148565</v>
       </c>
       <c r="D5">
-        <v>3.074223912842418</v>
+        <v>3.085044673148565</v>
       </c>
       <c r="E5">
-        <v>-0.7319199999999999</v>
+        <v>-0.7005599999999998</v>
       </c>
       <c r="F5">
-        <v>0.09408</v>
+        <v>0.12544</v>
       </c>
       <c r="G5">
         <v>0.134</v>
@@ -1804,28 +1804,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M5">
-        <v>0.004732223999999999</v>
+        <v>0.006309632</v>
       </c>
       <c r="N5">
-        <v>0.3089344426666666</v>
+        <v>0.3073570346666666</v>
       </c>
       <c r="O5">
-        <v>0.06796557738666666</v>
+        <v>0.06761854762666666</v>
       </c>
       <c r="P5">
-        <v>0.24096886528</v>
+        <v>0.23973848704</v>
       </c>
       <c r="Q5">
-        <v>0.5339688652800001</v>
+        <v>0.53273848704</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09870776353734423</v>
+        <v>0.09914049514469367</v>
       </c>
       <c r="T5">
-        <v>0.7698724256175531</v>
+        <v>0.7761691977719145</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.28314016129978</v>
+        <v>49.71235512097483</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1850,22 +1850,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09674423533890593</v>
+        <v>0.09656492004658791</v>
       </c>
       <c r="C6">
-        <v>3.093604673148565</v>
+        <v>3.073141877101061</v>
       </c>
       <c r="D6">
-        <v>3.085044673148565</v>
+        <v>3.095941877101061</v>
       </c>
       <c r="E6">
-        <v>-0.7005599999999998</v>
+        <v>-0.6691999999999998</v>
       </c>
       <c r="F6">
-        <v>0.12544</v>
+        <v>0.1568</v>
       </c>
       <c r="G6">
         <v>0.134</v>
@@ -1886,28 +1886,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M6">
-        <v>0.006309632</v>
+        <v>0.007887040000000001</v>
       </c>
       <c r="N6">
-        <v>0.3073570346666666</v>
+        <v>0.3057796266666666</v>
       </c>
       <c r="O6">
-        <v>0.06761854762666666</v>
+        <v>0.06727151786666666</v>
       </c>
       <c r="P6">
-        <v>0.23973848704</v>
+        <v>0.2385081088</v>
       </c>
       <c r="Q6">
-        <v>0.53273848704</v>
+        <v>0.5315081088</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09914049514469367</v>
+        <v>0.09958233689114518</v>
       </c>
       <c r="T6">
-        <v>0.7761691977719145</v>
+        <v>0.7825985335505783</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.71235512097483</v>
+        <v>39.76988409677985</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1932,22 +1932,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09656492004658791</v>
+        <v>0.09638560475426992</v>
       </c>
       <c r="C7">
-        <v>3.073141877101061</v>
+        <v>3.052756337629676</v>
       </c>
       <c r="D7">
-        <v>3.095941877101061</v>
+        <v>3.106916337629676</v>
       </c>
       <c r="E7">
-        <v>-0.6691999999999998</v>
+        <v>-0.6378399999999999</v>
       </c>
       <c r="F7">
-        <v>0.1568</v>
+        <v>0.18816</v>
       </c>
       <c r="G7">
         <v>0.134</v>
@@ -1968,28 +1968,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M7">
-        <v>0.007887040000000001</v>
+        <v>0.009464448</v>
       </c>
       <c r="N7">
-        <v>0.3057796266666666</v>
+        <v>0.3042022186666666</v>
       </c>
       <c r="O7">
-        <v>0.06727151786666666</v>
+        <v>0.06692448810666667</v>
       </c>
       <c r="P7">
-        <v>0.2385081088</v>
+        <v>0.23727773056</v>
       </c>
       <c r="Q7">
-        <v>0.5315081088</v>
+        <v>0.5302777305599999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09958233689114518</v>
+        <v>0.1000335795258191</v>
       </c>
       <c r="T7">
-        <v>0.7825985335505783</v>
+        <v>0.7891646637075114</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.76988409677985</v>
+        <v>33.14157008064988</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2014,22 +2014,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09638560475426992</v>
+        <v>0.09620628946195195</v>
       </c>
       <c r="C8">
-        <v>3.052756337629676</v>
+        <v>3.032448879231852</v>
       </c>
       <c r="D8">
-        <v>3.106916337629676</v>
+        <v>3.117968879231853</v>
       </c>
       <c r="E8">
-        <v>-0.6378399999999999</v>
+        <v>-0.6064799999999999</v>
       </c>
       <c r="F8">
-        <v>0.18816</v>
+        <v>0.21952</v>
       </c>
       <c r="G8">
         <v>0.134</v>
@@ -2050,28 +2050,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M8">
-        <v>0.009464447999999999</v>
+        <v>0.011041856</v>
       </c>
       <c r="N8">
-        <v>0.3042022186666666</v>
+        <v>0.3026248106666666</v>
       </c>
       <c r="O8">
-        <v>0.06692448810666667</v>
+        <v>0.06657745834666666</v>
       </c>
       <c r="P8">
-        <v>0.23727773056</v>
+        <v>0.23604735232</v>
       </c>
       <c r="Q8">
-        <v>0.5302777305599999</v>
+        <v>0.52904735232</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1000335795258191</v>
+        <v>0.1004945263031741</v>
       </c>
       <c r="T8">
-        <v>0.7891646637075114</v>
+        <v>0.7958720009645937</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.14157008064989</v>
+        <v>28.40706006912847</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2096,22 +2096,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09620628946195195</v>
+        <v>0.09602697416963395</v>
       </c>
       <c r="C9">
-        <v>3.032448879231852</v>
+        <v>3.012220338179182</v>
       </c>
       <c r="D9">
-        <v>3.117968879231853</v>
+        <v>3.129100338179182</v>
       </c>
       <c r="E9">
-        <v>-0.6064799999999998</v>
+        <v>-0.5751199999999999</v>
       </c>
       <c r="F9">
-        <v>0.21952</v>
+        <v>0.25088</v>
       </c>
       <c r="G9">
         <v>0.134</v>
@@ -2132,28 +2132,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M9">
-        <v>0.011041856</v>
+        <v>0.012619264</v>
       </c>
       <c r="N9">
-        <v>0.3026248106666666</v>
+        <v>0.3010474026666666</v>
       </c>
       <c r="O9">
-        <v>0.06657745834666666</v>
+        <v>0.06623042858666665</v>
       </c>
       <c r="P9">
-        <v>0.23604735232</v>
+        <v>0.23481697408</v>
       </c>
       <c r="Q9">
-        <v>0.52904735232</v>
+        <v>0.5278169740800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1004945263031741</v>
+        <v>0.1009654936626456</v>
       </c>
       <c r="T9">
-        <v>0.7958720009645939</v>
+        <v>0.8027251499011778</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.40706006912847</v>
+        <v>24.85617756048741</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2178,22 +2178,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09602697416963395</v>
+        <v>0.09584765887731597</v>
       </c>
       <c r="C10">
-        <v>3.012220338179182</v>
+        <v>2.992071562728333</v>
       </c>
       <c r="D10">
-        <v>3.129100338179182</v>
+        <v>3.140311562728333</v>
       </c>
       <c r="E10">
-        <v>-0.5751199999999999</v>
+        <v>-0.5437599999999998</v>
       </c>
       <c r="F10">
-        <v>0.25088</v>
+        <v>0.28224</v>
       </c>
       <c r="G10">
         <v>0.134</v>
@@ -2214,28 +2214,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M10">
-        <v>0.012619264</v>
+        <v>0.014196672</v>
       </c>
       <c r="N10">
-        <v>0.3010474026666666</v>
+        <v>0.2994699946666666</v>
       </c>
       <c r="O10">
-        <v>0.06623042858666665</v>
+        <v>0.06588339882666666</v>
       </c>
       <c r="P10">
-        <v>0.23481697408</v>
+        <v>0.23358659584</v>
       </c>
       <c r="Q10">
-        <v>0.5278169740800001</v>
+        <v>0.52658659584</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1009654936626456</v>
+        <v>0.1014468119530945</v>
       </c>
       <c r="T10">
-        <v>0.8027251499011778</v>
+        <v>0.8097289174957089</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.85617756048741</v>
+        <v>22.09438005376659</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2260,22 +2260,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09584765887731597</v>
+        <v>0.09566834358499797</v>
       </c>
       <c r="C11">
-        <v>2.992071562728333</v>
+        <v>2.972003413336534</v>
       </c>
       <c r="D11">
-        <v>3.140311562728333</v>
+        <v>3.151603413336534</v>
       </c>
       <c r="E11">
-        <v>-0.5437599999999998</v>
+        <v>-0.5123999999999999</v>
       </c>
       <c r="F11">
-        <v>0.28224</v>
+        <v>0.3136</v>
       </c>
       <c r="G11">
         <v>0.134</v>
@@ -2296,28 +2296,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M11">
-        <v>0.014196672</v>
+        <v>0.01577408</v>
       </c>
       <c r="N11">
-        <v>0.2994699946666666</v>
+        <v>0.2978925866666666</v>
       </c>
       <c r="O11">
-        <v>0.06588339882666666</v>
+        <v>0.06553636906666666</v>
       </c>
       <c r="P11">
-        <v>0.23358659584</v>
+        <v>0.2323562176</v>
       </c>
       <c r="Q11">
-        <v>0.52658659584</v>
+        <v>0.5253562176</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1014468119530945</v>
+        <v>0.1019388262055533</v>
       </c>
       <c r="T11">
-        <v>0.8097289174957089</v>
+        <v>0.8168883243701183</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.09438005376659</v>
+        <v>19.88494204838993</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2342,22 +2342,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09566834358499797</v>
+        <v>0.09548902829267998</v>
       </c>
       <c r="C12">
-        <v>2.972003413336534</v>
+        <v>2.952016762881711</v>
       </c>
       <c r="D12">
-        <v>3.151603413336534</v>
+        <v>3.162976762881711</v>
       </c>
       <c r="E12">
-        <v>-0.5123999999999997</v>
+        <v>-0.4810399999999999</v>
       </c>
       <c r="F12">
-        <v>0.3136</v>
+        <v>0.34496</v>
       </c>
       <c r="G12">
         <v>0.134</v>
@@ -2378,28 +2378,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M12">
-        <v>0.01577408</v>
+        <v>0.017351488</v>
       </c>
       <c r="N12">
-        <v>0.2978925866666666</v>
+        <v>0.2963151786666667</v>
       </c>
       <c r="O12">
-        <v>0.06553636906666666</v>
+        <v>0.06518933930666666</v>
       </c>
       <c r="P12">
-        <v>0.2323562176</v>
+        <v>0.23112583936</v>
       </c>
       <c r="Q12">
-        <v>0.5253562176</v>
+        <v>0.5241258393600001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1019388262055533</v>
+        <v>0.1024418969580674</v>
       </c>
       <c r="T12">
-        <v>0.8168883243701183</v>
+        <v>0.8242086167922673</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.88494204838993</v>
+        <v>18.07722004399085</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09548902829267998</v>
+        <v>0.09530971300036199</v>
       </c>
       <c r="C13">
-        <v>2.952016762881711</v>
+        <v>2.932112496887419</v>
       </c>
       <c r="D13">
-        <v>3.162976762881711</v>
+        <v>3.17443249688742</v>
       </c>
       <c r="E13">
-        <v>-0.4810399999999999</v>
+        <v>-0.4496799999999999</v>
       </c>
       <c r="F13">
-        <v>0.34496</v>
+        <v>0.37632</v>
       </c>
       <c r="G13">
         <v>0.134</v>
@@ -2460,28 +2460,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M13">
-        <v>0.017351488</v>
+        <v>0.018928896</v>
       </c>
       <c r="N13">
-        <v>0.2963151786666667</v>
+        <v>0.2947377706666667</v>
       </c>
       <c r="O13">
-        <v>0.06518933930666666</v>
+        <v>0.06484230954666667</v>
       </c>
       <c r="P13">
-        <v>0.23112583936</v>
+        <v>0.22989546112</v>
       </c>
       <c r="Q13">
-        <v>0.5241258393600001</v>
+        <v>0.5228954611200001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1024418969580674</v>
+        <v>0.102956401136775</v>
       </c>
       <c r="T13">
-        <v>0.8242086167922673</v>
+        <v>0.8316952794967378</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.07722004399085</v>
+        <v>16.57078504032495</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2506,22 +2506,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09530971300036199</v>
+        <v>0.09513039770804398</v>
       </c>
       <c r="C14">
-        <v>2.932112496887419</v>
+        <v>2.912291513752681</v>
       </c>
       <c r="D14">
-        <v>3.17443249688742</v>
+        <v>3.185971513752681</v>
       </c>
       <c r="E14">
-        <v>-0.4496799999999999</v>
+        <v>-0.4183199999999998</v>
       </c>
       <c r="F14">
-        <v>0.37632</v>
+        <v>0.40768</v>
       </c>
       <c r="G14">
         <v>0.134</v>
@@ -2542,28 +2542,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M14">
-        <v>0.018928896</v>
+        <v>0.020506304</v>
       </c>
       <c r="N14">
-        <v>0.2947377706666667</v>
+        <v>0.2931603626666667</v>
       </c>
       <c r="O14">
-        <v>0.06484230954666667</v>
+        <v>0.06449527978666666</v>
       </c>
       <c r="P14">
-        <v>0.22989546112</v>
+        <v>0.22866508288</v>
       </c>
       <c r="Q14">
-        <v>0.5228954611200001</v>
+        <v>0.52166508288</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.102956401136775</v>
+        <v>0.1034827329977517</v>
       </c>
       <c r="T14">
-        <v>0.8316952794967378</v>
+        <v>0.8393540493898168</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.57078504032495</v>
+        <v>15.29610926799226</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2588,22 +2588,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09513039770804398</v>
+        <v>0.094951082415726</v>
       </c>
       <c r="C15">
-        <v>2.912291513752681</v>
+        <v>2.892554724986835</v>
       </c>
       <c r="D15">
-        <v>3.185971513752681</v>
+        <v>3.197594724986835</v>
       </c>
       <c r="E15">
-        <v>-0.4183199999999998</v>
+        <v>-0.3869599999999998</v>
       </c>
       <c r="F15">
-        <v>0.40768</v>
+        <v>0.43904</v>
       </c>
       <c r="G15">
         <v>0.134</v>
@@ -2624,28 +2624,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M15">
-        <v>0.020506304</v>
+        <v>0.022083712</v>
       </c>
       <c r="N15">
-        <v>0.2931603626666667</v>
+        <v>0.2915829546666667</v>
       </c>
       <c r="O15">
-        <v>0.06449527978666666</v>
+        <v>0.06414825002666667</v>
       </c>
       <c r="P15">
-        <v>0.22866508288</v>
+        <v>0.22743470464</v>
       </c>
       <c r="Q15">
-        <v>0.52166508288</v>
+        <v>0.52043470464</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1034827329977517</v>
+        <v>0.1040213051345651</v>
       </c>
       <c r="T15">
-        <v>0.8393540493898168</v>
+        <v>0.847190930210642</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.29610926799226</v>
+        <v>14.20353003456424</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2670,22 +2670,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.094951082415726</v>
+        <v>0.09477176712340803</v>
       </c>
       <c r="C16">
-        <v>2.892554724986835</v>
+        <v>2.872903055449579</v>
       </c>
       <c r="D16">
-        <v>3.197594724986835</v>
+        <v>3.209303055449579</v>
       </c>
       <c r="E16">
-        <v>-0.3869599999999998</v>
+        <v>-0.3555999999999997</v>
       </c>
       <c r="F16">
-        <v>0.43904</v>
+        <v>0.4704000000000001</v>
       </c>
       <c r="G16">
         <v>0.134</v>
@@ -2706,28 +2706,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M16">
-        <v>0.022083712</v>
+        <v>0.02366112</v>
       </c>
       <c r="N16">
-        <v>0.2915829546666667</v>
+        <v>0.2900055466666667</v>
       </c>
       <c r="O16">
-        <v>0.06414825002666667</v>
+        <v>0.06380122026666667</v>
       </c>
       <c r="P16">
-        <v>0.22743470464</v>
+        <v>0.2262043264</v>
       </c>
       <c r="Q16">
-        <v>0.52043470464</v>
+        <v>0.5192043264</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1040213051345651</v>
+        <v>0.1045725495569506</v>
       </c>
       <c r="T16">
-        <v>0.847190930210642</v>
+        <v>0.8552122082272512</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.20353003456424</v>
+        <v>13.25662803225995</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2752,22 +2752,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09477176712340803</v>
+        <v>0.09477965183109002</v>
       </c>
       <c r="C17">
-        <v>2.872903055449579</v>
+        <v>2.841026424246433</v>
       </c>
       <c r="D17">
-        <v>3.209303055449579</v>
+        <v>3.208786424246433</v>
       </c>
       <c r="E17">
-        <v>-0.3555999999999999</v>
+        <v>-0.3242399999999999</v>
       </c>
       <c r="F17">
-        <v>0.4704</v>
+        <v>0.50176</v>
       </c>
       <c r="G17">
         <v>0.134</v>
@@ -2788,45 +2788,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M17">
-        <v>0.02366112</v>
+        <v>0.025991168</v>
       </c>
       <c r="N17">
-        <v>0.2900055466666667</v>
+        <v>0.2876754986666666</v>
       </c>
       <c r="O17">
-        <v>0.06380122026666667</v>
+        <v>0.06328860970666667</v>
       </c>
       <c r="P17">
-        <v>0.2262043264</v>
+        <v>0.22438688896</v>
       </c>
       <c r="Q17">
-        <v>0.5192043264</v>
+        <v>0.51738688896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1045725495569506</v>
+        <v>0.1051369188465357</v>
       </c>
       <c r="T17">
-        <v>0.8552122082272512</v>
+        <v>0.8634244690537797</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.25662803225996</v>
+        <v>12.06820203950306</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2834,22 +2834,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09477965183109002</v>
+        <v>0.09461203653877202</v>
       </c>
       <c r="C18">
-        <v>2.841026424246433</v>
+        <v>2.820685052286239</v>
       </c>
       <c r="D18">
-        <v>3.208786424246433</v>
+        <v>3.219805052286239</v>
       </c>
       <c r="E18">
-        <v>-0.3242399999999999</v>
+        <v>-0.2928799999999998</v>
       </c>
       <c r="F18">
-        <v>0.50176</v>
+        <v>0.53312</v>
       </c>
       <c r="G18">
         <v>0.134</v>
@@ -2870,28 +2870,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M18">
-        <v>0.025991168</v>
+        <v>0.027615616</v>
       </c>
       <c r="N18">
-        <v>0.2876754986666666</v>
+        <v>0.2860510506666666</v>
       </c>
       <c r="O18">
-        <v>0.06328860970666667</v>
+        <v>0.06293123114666666</v>
       </c>
       <c r="P18">
-        <v>0.22438688896</v>
+        <v>0.22311981952</v>
       </c>
       <c r="Q18">
-        <v>0.51738688896</v>
+        <v>0.5161198195200001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1051369188465357</v>
+        <v>0.1057148873961109</v>
       </c>
       <c r="T18">
-        <v>0.8634244690537797</v>
+        <v>0.8718346156833571</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.06820203950306</v>
+        <v>11.35830780188523</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2916,22 +2916,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09461203653877202</v>
+        <v>0.09444442124645404</v>
       </c>
       <c r="C19">
-        <v>2.820685052286239</v>
+        <v>2.800419614647492</v>
       </c>
       <c r="D19">
-        <v>3.219805052286239</v>
+        <v>3.230899614647492</v>
       </c>
       <c r="E19">
-        <v>-0.2928799999999998</v>
+        <v>-0.2615199999999998</v>
       </c>
       <c r="F19">
-        <v>0.53312</v>
+        <v>0.5644800000000001</v>
       </c>
       <c r="G19">
         <v>0.134</v>
@@ -2952,28 +2952,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M19">
-        <v>0.027615616</v>
+        <v>0.029240064</v>
       </c>
       <c r="N19">
-        <v>0.2860510506666666</v>
+        <v>0.2844266026666666</v>
       </c>
       <c r="O19">
-        <v>0.06293123114666666</v>
+        <v>0.06257385258666666</v>
       </c>
       <c r="P19">
-        <v>0.22311981952</v>
+        <v>0.22185275008</v>
       </c>
       <c r="Q19">
-        <v>0.5161198195200001</v>
+        <v>0.51485275008</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1057148873961109</v>
+        <v>0.1063069527395781</v>
       </c>
       <c r="T19">
-        <v>0.8718346156833571</v>
+        <v>0.8804498878404852</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.35830780188523</v>
+        <v>10.7272907017805</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2998,22 +2998,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09444442124645405</v>
+        <v>0.09427680595413607</v>
       </c>
       <c r="C20">
-        <v>2.800419614647491</v>
+        <v>2.780230898990597</v>
       </c>
       <c r="D20">
-        <v>3.230899614647491</v>
+        <v>3.242070898990597</v>
       </c>
       <c r="E20">
-        <v>-0.2615199999999999</v>
+        <v>-0.2301599999999998</v>
       </c>
       <c r="F20">
-        <v>0.56448</v>
+        <v>0.59584</v>
       </c>
       <c r="G20">
         <v>0.134</v>
@@ -3034,28 +3034,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M20">
-        <v>0.029240064</v>
+        <v>0.030864512</v>
       </c>
       <c r="N20">
-        <v>0.2844266026666666</v>
+        <v>0.2828021546666666</v>
       </c>
       <c r="O20">
-        <v>0.06257385258666666</v>
+        <v>0.06221647402666666</v>
       </c>
       <c r="P20">
-        <v>0.22185275008</v>
+        <v>0.22058568064</v>
       </c>
       <c r="Q20">
-        <v>0.51485275008</v>
+        <v>0.51358568064</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1063069527395781</v>
+        <v>0.1069136369804149</v>
       </c>
       <c r="T20">
-        <v>0.8804498878404851</v>
+        <v>0.889277882766925</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.7272907017805</v>
+        <v>10.16269645431836</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3080,22 +3080,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09427680595413607</v>
+        <v>0.09437439066181808</v>
       </c>
       <c r="C21">
-        <v>2.780230898990597</v>
+        <v>2.742357661528391</v>
       </c>
       <c r="D21">
-        <v>3.242070898990597</v>
+        <v>3.235557661528392</v>
       </c>
       <c r="E21">
-        <v>-0.2301599999999998</v>
+        <v>-0.1987999999999998</v>
       </c>
       <c r="F21">
-        <v>0.59584</v>
+        <v>0.6272000000000001</v>
       </c>
       <c r="G21">
         <v>0.134</v>
@@ -3116,45 +3116,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M21">
-        <v>0.030864512</v>
+        <v>0.03355520000000001</v>
       </c>
       <c r="N21">
-        <v>0.2828021546666666</v>
+        <v>0.2801114666666666</v>
       </c>
       <c r="O21">
-        <v>0.06221647402666666</v>
+        <v>0.06162452266666666</v>
       </c>
       <c r="P21">
-        <v>0.22058568064</v>
+        <v>0.218486944</v>
       </c>
       <c r="Q21">
-        <v>0.51358568064</v>
+        <v>0.5114869440000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1069136369804149</v>
+        <v>0.1075354883272726</v>
       </c>
       <c r="T21">
-        <v>0.889277882766925</v>
+        <v>0.8983265775665258</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.16269645431836</v>
+        <v>9.347781168542181</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3162,22 +3162,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09437439066181808</v>
+        <v>0.09422003536950008</v>
       </c>
       <c r="C22">
-        <v>2.742357661528391</v>
+        <v>2.721312099443312</v>
       </c>
       <c r="D22">
-        <v>3.235557661528392</v>
+        <v>3.245872099443312</v>
       </c>
       <c r="E22">
-        <v>-0.1987999999999998</v>
+        <v>-0.1674399999999998</v>
       </c>
       <c r="F22">
-        <v>0.6272000000000001</v>
+        <v>0.65856</v>
       </c>
       <c r="G22">
         <v>0.134</v>
@@ -3198,28 +3198,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M22">
-        <v>0.03355520000000001</v>
+        <v>0.03523296</v>
       </c>
       <c r="N22">
-        <v>0.2801114666666666</v>
+        <v>0.2784337066666667</v>
       </c>
       <c r="O22">
-        <v>0.06162452266666666</v>
+        <v>0.06125541546666666</v>
       </c>
       <c r="P22">
-        <v>0.218486944</v>
+        <v>0.2171782912</v>
       </c>
       <c r="Q22">
-        <v>0.5114869440000001</v>
+        <v>0.5101782912</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1075354883272726</v>
+        <v>0.1081730827462026</v>
       </c>
       <c r="T22">
-        <v>0.8983265775665258</v>
+        <v>0.9076043532471292</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.347781168542181</v>
+        <v>8.902648731944936</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3244,22 +3244,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09422003536950006</v>
+        <v>0.09406568007718208</v>
       </c>
       <c r="C23">
-        <v>2.721312099443313</v>
+        <v>2.700332509207252</v>
       </c>
       <c r="D23">
-        <v>3.245872099443313</v>
+        <v>3.256252509207252</v>
       </c>
       <c r="E23">
-        <v>-0.1674399999999998</v>
+        <v>-0.1360799999999999</v>
       </c>
       <c r="F23">
-        <v>0.65856</v>
+        <v>0.68992</v>
       </c>
       <c r="G23">
         <v>0.134</v>
@@ -3280,28 +3280,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M23">
-        <v>0.03523296</v>
+        <v>0.03691072</v>
       </c>
       <c r="N23">
-        <v>0.2784337066666667</v>
+        <v>0.2767559466666666</v>
       </c>
       <c r="O23">
-        <v>0.06125541546666666</v>
+        <v>0.06088630826666666</v>
       </c>
       <c r="P23">
-        <v>0.2171782912</v>
+        <v>0.2158696384</v>
       </c>
       <c r="Q23">
-        <v>0.5101782912</v>
+        <v>0.5088696384</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1081730827462026</v>
+        <v>0.108827025739977</v>
       </c>
       <c r="T23">
-        <v>0.9076043532471291</v>
+        <v>0.9171200206118505</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.902648731944936</v>
+        <v>8.497982880492893</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3326,22 +3326,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09406568007718208</v>
+        <v>0.09391132478486408</v>
       </c>
       <c r="C24">
-        <v>2.700332509207252</v>
+        <v>2.679419525791548</v>
       </c>
       <c r="D24">
-        <v>3.256252509207252</v>
+        <v>3.266699525791548</v>
       </c>
       <c r="E24">
-        <v>-0.1360799999999999</v>
+        <v>-0.1047199999999998</v>
       </c>
       <c r="F24">
-        <v>0.68992</v>
+        <v>0.72128</v>
       </c>
       <c r="G24">
         <v>0.134</v>
@@ -3362,28 +3362,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M24">
-        <v>0.03691072</v>
+        <v>0.03858848</v>
       </c>
       <c r="N24">
-        <v>0.2767559466666666</v>
+        <v>0.2750781866666667</v>
       </c>
       <c r="O24">
-        <v>0.06088630826666666</v>
+        <v>0.06051720106666666</v>
       </c>
       <c r="P24">
-        <v>0.2158696384</v>
+        <v>0.2145609856</v>
       </c>
       <c r="Q24">
-        <v>0.5088696384</v>
+        <v>0.5075609856000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.108827025739977</v>
+        <v>0.1094979542660572</v>
       </c>
       <c r="T24">
-        <v>0.9171200206118505</v>
+        <v>0.9268828481678635</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.497982880492893</v>
+        <v>8.128505363949724</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3408,22 +3408,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09391132478486408</v>
+        <v>0.0937569694925461</v>
       </c>
       <c r="C25">
-        <v>2.679419525791548</v>
+        <v>2.658573792342459</v>
       </c>
       <c r="D25">
-        <v>3.266699525791548</v>
+        <v>3.277213792342459</v>
       </c>
       <c r="E25">
-        <v>-0.1047199999999998</v>
+        <v>-0.07335999999999976</v>
       </c>
       <c r="F25">
-        <v>0.72128</v>
+        <v>0.7526400000000001</v>
       </c>
       <c r="G25">
         <v>0.134</v>
@@ -3444,28 +3444,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M25">
-        <v>0.03858848</v>
+        <v>0.04026624</v>
       </c>
       <c r="N25">
-        <v>0.2750781866666667</v>
+        <v>0.2734004266666666</v>
       </c>
       <c r="O25">
-        <v>0.06051720106666666</v>
+        <v>0.06014809386666666</v>
       </c>
       <c r="P25">
-        <v>0.2145609856</v>
+        <v>0.2132523328</v>
       </c>
       <c r="Q25">
-        <v>0.5075609856000001</v>
+        <v>0.5062523328</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1094979542660572</v>
+        <v>0.1101865388059817</v>
       </c>
       <c r="T25">
-        <v>0.9268828481678635</v>
+        <v>0.9369025922385082</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.128505363949724</v>
+        <v>7.789817640451818</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3490,22 +3490,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0937569694925461</v>
+        <v>0.0937586142002281</v>
       </c>
       <c r="C26">
-        <v>2.658573792342459</v>
+        <v>2.627101402549933</v>
       </c>
       <c r="D26">
-        <v>3.277213792342459</v>
+        <v>3.277101402549933</v>
       </c>
       <c r="E26">
-        <v>-0.07335999999999987</v>
+        <v>-0.04199999999999982</v>
       </c>
       <c r="F26">
-        <v>0.75264</v>
+        <v>0.784</v>
       </c>
       <c r="G26">
         <v>0.134</v>
@@ -3526,45 +3526,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M26">
-        <v>0.04026623999999999</v>
+        <v>0.0425712</v>
       </c>
       <c r="N26">
-        <v>0.2734004266666666</v>
+        <v>0.2710954666666666</v>
       </c>
       <c r="O26">
-        <v>0.06014809386666666</v>
+        <v>0.05964100266666666</v>
       </c>
       <c r="P26">
-        <v>0.2132523328</v>
+        <v>0.211454464</v>
       </c>
       <c r="Q26">
-        <v>0.5062523328</v>
+        <v>0.5044544639999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1101865388059817</v>
+        <v>0.1108934856003041</v>
       </c>
       <c r="T26">
-        <v>0.9369025922385082</v>
+        <v>0.9471895294843703</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.78981764045182</v>
+        <v>7.368048508537852</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3572,22 +3572,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0937586142002281</v>
+        <v>0.09361049890791011</v>
       </c>
       <c r="C27">
-        <v>2.627101402549933</v>
+        <v>2.605893750742938</v>
       </c>
       <c r="D27">
-        <v>3.277101402549933</v>
+        <v>3.287253750742938</v>
       </c>
       <c r="E27">
-        <v>-0.04199999999999982</v>
+        <v>-0.01063999999999976</v>
       </c>
       <c r="F27">
-        <v>0.784</v>
+        <v>0.8153600000000001</v>
       </c>
       <c r="G27">
         <v>0.134</v>
@@ -3608,28 +3608,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M27">
-        <v>0.0425712</v>
+        <v>0.044274048</v>
       </c>
       <c r="N27">
-        <v>0.2710954666666666</v>
+        <v>0.2693926186666666</v>
       </c>
       <c r="O27">
-        <v>0.05964100266666666</v>
+        <v>0.05926637610666666</v>
       </c>
       <c r="P27">
-        <v>0.211454464</v>
+        <v>0.21012624256</v>
       </c>
       <c r="Q27">
-        <v>0.5044544639999999</v>
+        <v>0.50312624256</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1108934856003041</v>
+        <v>0.1116195390647434</v>
       </c>
       <c r="T27">
-        <v>0.9471895294843703</v>
+        <v>0.9577544920612016</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.368048508537852</v>
+        <v>7.084662027440243</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09361049890791011</v>
+        <v>0.09346238361559213</v>
       </c>
       <c r="C28">
-        <v>2.605893750742938</v>
+        <v>2.584749197669419</v>
       </c>
       <c r="D28">
-        <v>3.287253750742938</v>
+        <v>3.297469197669419</v>
       </c>
       <c r="E28">
-        <v>-0.01063999999999976</v>
+        <v>0.02072000000000029</v>
       </c>
       <c r="F28">
-        <v>0.8153600000000001</v>
+        <v>0.8467200000000001</v>
       </c>
       <c r="G28">
         <v>0.134</v>
@@ -3690,28 +3690,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M28">
-        <v>0.044274048</v>
+        <v>0.04597689600000001</v>
       </c>
       <c r="N28">
-        <v>0.2693926186666666</v>
+        <v>0.2676897706666667</v>
       </c>
       <c r="O28">
-        <v>0.05926637610666666</v>
+        <v>0.05889174954666666</v>
       </c>
       <c r="P28">
-        <v>0.21012624256</v>
+        <v>0.20879802112</v>
       </c>
       <c r="Q28">
-        <v>0.50312624256</v>
+        <v>0.50179802112</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1116195390647434</v>
+        <v>0.1123654844049207</v>
       </c>
       <c r="T28">
-        <v>0.9577544920612016</v>
+        <v>0.968608905667535</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.084662027440243</v>
+        <v>6.822267137535048</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3736,22 +3736,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09346238361559213</v>
+        <v>0.09331426832327414</v>
       </c>
       <c r="C29">
-        <v>2.584749197669419</v>
+        <v>2.563668333418693</v>
       </c>
       <c r="D29">
-        <v>3.297469197669419</v>
+        <v>3.307748333418694</v>
       </c>
       <c r="E29">
-        <v>0.02072000000000029</v>
+        <v>0.05208000000000024</v>
       </c>
       <c r="F29">
-        <v>0.8467200000000001</v>
+        <v>0.8780800000000001</v>
       </c>
       <c r="G29">
         <v>0.134</v>
@@ -3772,28 +3772,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M29">
-        <v>0.04597689600000001</v>
+        <v>0.047679744</v>
       </c>
       <c r="N29">
-        <v>0.2676897706666667</v>
+        <v>0.2659869226666666</v>
       </c>
       <c r="O29">
-        <v>0.05889174954666666</v>
+        <v>0.05851712298666666</v>
       </c>
       <c r="P29">
-        <v>0.20879802112</v>
+        <v>0.20746979968</v>
       </c>
       <c r="Q29">
-        <v>0.50179802112</v>
+        <v>0.50046979968</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1123654844049207</v>
+        <v>0.1131321504489919</v>
       </c>
       <c r="T29">
-        <v>0.968608905667535</v>
+        <v>0.9797648307629333</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.822267137535048</v>
+        <v>6.578614739765939</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3818,22 +3818,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09331426832327414</v>
+        <v>0.09316615303095613</v>
       </c>
       <c r="C30">
-        <v>2.563668333418693</v>
+        <v>2.54265175546098</v>
       </c>
       <c r="D30">
-        <v>3.307748333418694</v>
+        <v>3.31809175546098</v>
       </c>
       <c r="E30">
-        <v>0.05208000000000024</v>
+        <v>0.08344000000000029</v>
       </c>
       <c r="F30">
-        <v>0.8780800000000001</v>
+        <v>0.9094400000000001</v>
       </c>
       <c r="G30">
         <v>0.134</v>
@@ -3854,28 +3854,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M30">
-        <v>0.047679744</v>
+        <v>0.04938259200000001</v>
       </c>
       <c r="N30">
-        <v>0.2659869226666666</v>
+        <v>0.2642840746666666</v>
       </c>
       <c r="O30">
-        <v>0.05851712298666666</v>
+        <v>0.05814249642666666</v>
       </c>
       <c r="P30">
-        <v>0.20746979968</v>
+        <v>0.20614157824</v>
       </c>
       <c r="Q30">
-        <v>0.50046979968</v>
+        <v>0.4991415782400001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1131321504489919</v>
+        <v>0.1139204127196565</v>
       </c>
       <c r="T30">
-        <v>0.9797648307629333</v>
+        <v>0.9912350072694696</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.578614739765939</v>
+        <v>6.351765955636079</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3900,22 +3900,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09316615303095613</v>
+        <v>0.09301803773863815</v>
       </c>
       <c r="C31">
-        <v>2.54265175546098</v>
+        <v>2.521700068763162</v>
       </c>
       <c r="D31">
-        <v>3.31809175546098</v>
+        <v>3.328500068763162</v>
       </c>
       <c r="E31">
-        <v>0.08344000000000018</v>
+        <v>0.1148000000000001</v>
       </c>
       <c r="F31">
-        <v>0.90944</v>
+        <v>0.9408</v>
       </c>
       <c r="G31">
         <v>0.134</v>
@@ -3936,28 +3936,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M31">
-        <v>0.049382592</v>
+        <v>0.05108544</v>
       </c>
       <c r="N31">
-        <v>0.2642840746666666</v>
+        <v>0.2625812266666667</v>
       </c>
       <c r="O31">
-        <v>0.05814249642666666</v>
+        <v>0.05776786986666667</v>
       </c>
       <c r="P31">
-        <v>0.20614157824</v>
+        <v>0.2048133568</v>
       </c>
       <c r="Q31">
-        <v>0.4991415782400001</v>
+        <v>0.4978133568000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1139204127196565</v>
+        <v>0.1147311967694831</v>
       </c>
       <c r="T31">
-        <v>0.9912350072694696</v>
+        <v>1.003032903104764</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.35176595563608</v>
+        <v>6.140040423781544</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3982,22 +3982,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09301803773863815</v>
+        <v>0.09311172244632014</v>
       </c>
       <c r="C32">
-        <v>2.521700068763162</v>
+        <v>2.483749111177219</v>
       </c>
       <c r="D32">
-        <v>3.328500068763162</v>
+        <v>3.32190911117722</v>
       </c>
       <c r="E32">
-        <v>0.1148000000000001</v>
+        <v>0.1461600000000002</v>
       </c>
       <c r="F32">
-        <v>0.9408</v>
+        <v>0.97216</v>
       </c>
       <c r="G32">
         <v>0.134</v>
@@ -4018,45 +4018,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M32">
-        <v>0.05108544</v>
+        <v>0.053760448</v>
       </c>
       <c r="N32">
-        <v>0.2625812266666667</v>
+        <v>0.2599062186666666</v>
       </c>
       <c r="O32">
-        <v>0.05776786986666667</v>
+        <v>0.05717936810666666</v>
       </c>
       <c r="P32">
-        <v>0.2048133568</v>
+        <v>0.20272685056</v>
       </c>
       <c r="Q32">
-        <v>0.4978133568000001</v>
+        <v>0.49572685056</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1147311967694831</v>
+        <v>0.1155654818062611</v>
       </c>
       <c r="T32">
-        <v>1.003032903104764</v>
+        <v>1.015172766935284</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.140040423781544</v>
+        <v>5.834524791658481</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4064,22 +4064,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09311172244632014</v>
+        <v>0.09297140715400215</v>
       </c>
       <c r="C33">
-        <v>2.483749111177219</v>
+        <v>2.462270407413876</v>
       </c>
       <c r="D33">
-        <v>3.32190911117722</v>
+        <v>3.331790407413876</v>
       </c>
       <c r="E33">
-        <v>0.1461600000000002</v>
+        <v>0.1775200000000001</v>
       </c>
       <c r="F33">
-        <v>0.97216</v>
+        <v>1.00352</v>
       </c>
       <c r="G33">
         <v>0.134</v>
@@ -4100,28 +4100,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M33">
-        <v>0.053760448</v>
+        <v>0.055494656</v>
       </c>
       <c r="N33">
-        <v>0.2599062186666666</v>
+        <v>0.2581720106666666</v>
       </c>
       <c r="O33">
-        <v>0.05717936810666666</v>
+        <v>0.05679784234666665</v>
       </c>
       <c r="P33">
-        <v>0.20272685056</v>
+        <v>0.20137416832</v>
       </c>
       <c r="Q33">
-        <v>0.49572685056</v>
+        <v>0.49437416832</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1155654818062611</v>
+        <v>0.1164243046382385</v>
       </c>
       <c r="T33">
-        <v>1.015172766935284</v>
+        <v>1.027669685584349</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.834524791658481</v>
+        <v>5.652195891919154</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4146,22 +4146,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09297140715400215</v>
+        <v>0.09283109186168416</v>
       </c>
       <c r="C34">
-        <v>2.462270407413876</v>
+        <v>2.440850664517272</v>
       </c>
       <c r="D34">
-        <v>3.331790407413876</v>
+        <v>3.341730664517272</v>
       </c>
       <c r="E34">
-        <v>0.1775200000000001</v>
+        <v>0.2088800000000002</v>
       </c>
       <c r="F34">
-        <v>1.00352</v>
+        <v>1.03488</v>
       </c>
       <c r="G34">
         <v>0.134</v>
@@ -4182,28 +4182,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M34">
-        <v>0.055494656</v>
+        <v>0.057228864</v>
       </c>
       <c r="N34">
-        <v>0.2581720106666666</v>
+        <v>0.2564378026666667</v>
       </c>
       <c r="O34">
-        <v>0.05679784234666665</v>
+        <v>0.05641631658666667</v>
       </c>
       <c r="P34">
-        <v>0.20137416832</v>
+        <v>0.20002148608</v>
       </c>
       <c r="Q34">
-        <v>0.49437416832</v>
+        <v>0.49302148608</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1164243046382385</v>
+        <v>0.1173087639726629</v>
       </c>
       <c r="T34">
-        <v>1.027669685584349</v>
+        <v>1.040539646581148</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.652195891919154</v>
+        <v>5.480917228527665</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4228,22 +4228,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09283109186168416</v>
+        <v>0.09269077656936618</v>
       </c>
       <c r="C35">
-        <v>2.440850664517272</v>
+        <v>2.41949041178838</v>
       </c>
       <c r="D35">
-        <v>3.341730664517272</v>
+        <v>3.351730411788381</v>
       </c>
       <c r="E35">
-        <v>0.2088800000000002</v>
+        <v>0.2402400000000002</v>
       </c>
       <c r="F35">
-        <v>1.03488</v>
+        <v>1.06624</v>
       </c>
       <c r="G35">
         <v>0.134</v>
@@ -4264,28 +4264,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M35">
-        <v>0.057228864</v>
+        <v>0.05896307200000001</v>
       </c>
       <c r="N35">
-        <v>0.2564378026666667</v>
+        <v>0.2547035946666666</v>
       </c>
       <c r="O35">
-        <v>0.05641631658666667</v>
+        <v>0.05603479082666666</v>
       </c>
       <c r="P35">
-        <v>0.20002148608</v>
+        <v>0.19866880384</v>
       </c>
       <c r="Q35">
-        <v>0.49302148608</v>
+        <v>0.49166880384</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1173087639726629</v>
+        <v>0.1182200251051003</v>
       </c>
       <c r="T35">
-        <v>1.040539646581148</v>
+        <v>1.053799606396031</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.480917228527665</v>
+        <v>5.319713780629792</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4310,22 +4310,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09269077656936618</v>
+        <v>0.09255046127704819</v>
       </c>
       <c r="C36">
-        <v>2.41949041178838</v>
+        <v>2.398190184882685</v>
       </c>
       <c r="D36">
-        <v>3.351730411788381</v>
+        <v>3.361790184882685</v>
       </c>
       <c r="E36">
-        <v>0.2402400000000002</v>
+        <v>0.2716000000000003</v>
       </c>
       <c r="F36">
-        <v>1.06624</v>
+        <v>1.0976</v>
       </c>
       <c r="G36">
         <v>0.134</v>
@@ -4346,28 +4346,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M36">
-        <v>0.05896307200000001</v>
+        <v>0.06069728000000001</v>
       </c>
       <c r="N36">
-        <v>0.2547035946666666</v>
+        <v>0.2529693866666666</v>
       </c>
       <c r="O36">
-        <v>0.05603479082666666</v>
+        <v>0.05565326506666666</v>
       </c>
       <c r="P36">
-        <v>0.19866880384</v>
+        <v>0.1973161216</v>
       </c>
       <c r="Q36">
-        <v>0.49166880384</v>
+        <v>0.4903161216</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1182200251051003</v>
+        <v>0.1191593250416126</v>
       </c>
       <c r="T36">
-        <v>1.053799606396031</v>
+        <v>1.067467564974449</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.319713780629792</v>
+        <v>5.167721958326084</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4392,22 +4392,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09255046127704819</v>
+        <v>0.0924101459847302</v>
       </c>
       <c r="C37">
-        <v>2.398190184882685</v>
+        <v>2.376950525905819</v>
       </c>
       <c r="D37">
-        <v>3.361790184882685</v>
+        <v>3.37191052590582</v>
       </c>
       <c r="E37">
-        <v>0.2716000000000003</v>
+        <v>0.3029600000000003</v>
       </c>
       <c r="F37">
-        <v>1.0976</v>
+        <v>1.12896</v>
       </c>
       <c r="G37">
         <v>0.134</v>
@@ -4428,28 +4428,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M37">
-        <v>0.06069728000000001</v>
+        <v>0.06243148800000001</v>
       </c>
       <c r="N37">
-        <v>0.2529693866666666</v>
+        <v>0.2512351786666666</v>
       </c>
       <c r="O37">
-        <v>0.05565326506666666</v>
+        <v>0.05527173930666666</v>
       </c>
       <c r="P37">
-        <v>0.1973161216</v>
+        <v>0.19596343936</v>
       </c>
       <c r="Q37">
-        <v>0.4903161216</v>
+        <v>0.48896343936</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1191593250416126</v>
+        <v>0.120127978101141</v>
       </c>
       <c r="T37">
-        <v>1.067467564974449</v>
+        <v>1.081562647258443</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.167721958326084</v>
+        <v>5.024174126150358</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4474,22 +4474,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0924101459847302</v>
+        <v>0.09226983069241219</v>
       </c>
       <c r="C38">
-        <v>2.376950525905819</v>
+        <v>2.355771983510955</v>
       </c>
       <c r="D38">
-        <v>3.37191052590582</v>
+        <v>3.382091983510955</v>
       </c>
       <c r="E38">
-        <v>0.3029600000000001</v>
+        <v>0.3343200000000002</v>
       </c>
       <c r="F38">
-        <v>1.12896</v>
+        <v>1.16032</v>
       </c>
       <c r="G38">
         <v>0.134</v>
@@ -4510,28 +4510,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M38">
-        <v>0.062431488</v>
+        <v>0.06416569600000001</v>
       </c>
       <c r="N38">
-        <v>0.2512351786666667</v>
+        <v>0.2495009706666667</v>
       </c>
       <c r="O38">
-        <v>0.05527173930666666</v>
+        <v>0.05489021354666666</v>
       </c>
       <c r="P38">
-        <v>0.19596343936</v>
+        <v>0.19461075712</v>
       </c>
       <c r="Q38">
-        <v>0.48896343936</v>
+        <v>0.48761075712</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1201279781011409</v>
+        <v>0.1211273820514479</v>
       </c>
       <c r="T38">
-        <v>1.081562647258443</v>
+        <v>1.096105192472087</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.02417412615036</v>
+        <v>4.888385636254403</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4556,22 +4556,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09226983069241219</v>
+        <v>0.0921295154000942</v>
       </c>
       <c r="C39">
-        <v>2.355771983510955</v>
+        <v>2.334655112997946</v>
       </c>
       <c r="D39">
-        <v>3.382091983510955</v>
+        <v>3.392335112997946</v>
       </c>
       <c r="E39">
-        <v>0.3343200000000002</v>
+        <v>0.3656800000000002</v>
       </c>
       <c r="F39">
-        <v>1.16032</v>
+        <v>1.19168</v>
       </c>
       <c r="G39">
         <v>0.134</v>
@@ -4592,28 +4592,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M39">
-        <v>0.06416569600000001</v>
+        <v>0.06589990400000001</v>
       </c>
       <c r="N39">
-        <v>0.2495009706666667</v>
+        <v>0.2477667626666666</v>
       </c>
       <c r="O39">
-        <v>0.05489021354666666</v>
+        <v>0.05450868778666666</v>
       </c>
       <c r="P39">
-        <v>0.19461075712</v>
+        <v>0.19325807488</v>
       </c>
       <c r="Q39">
-        <v>0.48761075712</v>
+        <v>0.48625807488</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1211273820514479</v>
+        <v>0.1221590248388616</v>
       </c>
       <c r="T39">
-        <v>1.096105192472087</v>
+        <v>1.111116852047461</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.888385636254403</v>
+        <v>4.75974390898455</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4638,22 +4638,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0921295154000942</v>
+        <v>0.09198920010777623</v>
       </c>
       <c r="C40">
-        <v>2.334655112997946</v>
+        <v>2.313600476414289</v>
       </c>
       <c r="D40">
-        <v>3.392335112997946</v>
+        <v>3.402640476414289</v>
       </c>
       <c r="E40">
-        <v>0.3656800000000002</v>
+        <v>0.3970400000000003</v>
       </c>
       <c r="F40">
-        <v>1.19168</v>
+        <v>1.22304</v>
       </c>
       <c r="G40">
         <v>0.134</v>
@@ -4674,28 +4674,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M40">
-        <v>0.06589990400000001</v>
+        <v>0.06763411200000001</v>
       </c>
       <c r="N40">
-        <v>0.2477667626666666</v>
+        <v>0.2460325546666666</v>
       </c>
       <c r="O40">
-        <v>0.05450868778666666</v>
+        <v>0.05412716202666665</v>
       </c>
       <c r="P40">
-        <v>0.19325807488</v>
+        <v>0.19190539264</v>
       </c>
       <c r="Q40">
-        <v>0.48625807488</v>
+        <v>0.48490539264</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1221590248388616</v>
+        <v>0.123224491979961</v>
       </c>
       <c r="T40">
-        <v>1.111116852047461</v>
+        <v>1.126620697182684</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.75974390898455</v>
+        <v>4.637699193369562</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4720,22 +4720,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09198920010777623</v>
+        <v>0.09184888481545823</v>
       </c>
       <c r="C41">
-        <v>2.313600476414289</v>
+        <v>2.292608642657934</v>
       </c>
       <c r="D41">
-        <v>3.402640476414289</v>
+        <v>3.413008642657934</v>
       </c>
       <c r="E41">
-        <v>0.3970400000000003</v>
+        <v>0.4284000000000003</v>
       </c>
       <c r="F41">
-        <v>1.22304</v>
+        <v>1.2544</v>
       </c>
       <c r="G41">
         <v>0.134</v>
@@ -4756,28 +4756,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M41">
-        <v>0.06763411200000001</v>
+        <v>0.06936832000000001</v>
       </c>
       <c r="N41">
-        <v>0.2460325546666666</v>
+        <v>0.2442983466666666</v>
       </c>
       <c r="O41">
-        <v>0.05412716202666665</v>
+        <v>0.05374563626666666</v>
       </c>
       <c r="P41">
-        <v>0.19190539264</v>
+        <v>0.1905527104</v>
       </c>
       <c r="Q41">
-        <v>0.48490539264</v>
+        <v>0.4835527104</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.123224491979961</v>
+        <v>0.1243254746924304</v>
       </c>
       <c r="T41">
-        <v>1.126620697182684</v>
+        <v>1.142641337155748</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.637699193369562</v>
+        <v>4.521756713535323</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4802,22 +4802,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09184888481545823</v>
+        <v>0.09250806952314024</v>
       </c>
       <c r="C42">
-        <v>2.292608642657934</v>
+        <v>2.213081310387607</v>
       </c>
       <c r="D42">
-        <v>3.413008642657934</v>
+        <v>3.364841310387607</v>
       </c>
       <c r="E42">
-        <v>0.4284000000000003</v>
+        <v>0.4597600000000004</v>
       </c>
       <c r="F42">
-        <v>1.2544</v>
+        <v>1.28576</v>
       </c>
       <c r="G42">
         <v>0.134</v>
@@ -4838,45 +4838,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M42">
-        <v>0.06936832000000001</v>
+        <v>0.07431692800000002</v>
       </c>
       <c r="N42">
-        <v>0.2442983466666666</v>
+        <v>0.2393497386666666</v>
       </c>
       <c r="O42">
-        <v>0.05374563626666666</v>
+        <v>0.05265694250666667</v>
       </c>
       <c r="P42">
-        <v>0.1905527104</v>
+        <v>0.18669279616</v>
       </c>
       <c r="Q42">
-        <v>0.4835527104</v>
+        <v>0.47969279616</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1243254746924304</v>
+        <v>0.1254637788527801</v>
       </c>
       <c r="T42">
-        <v>1.142641337155748</v>
+        <v>1.159205049670272</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.521756713535323</v>
+        <v>4.220662440011871</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4884,22 +4884,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09250806952314024</v>
+        <v>0.09238725423082225</v>
       </c>
       <c r="C43">
-        <v>2.213081310387607</v>
+        <v>2.190447394232427</v>
       </c>
       <c r="D43">
-        <v>3.364841310387607</v>
+        <v>3.373567394232427</v>
       </c>
       <c r="E43">
-        <v>0.4597600000000004</v>
+        <v>0.4911200000000002</v>
       </c>
       <c r="F43">
-        <v>1.28576</v>
+        <v>1.31712</v>
       </c>
       <c r="G43">
         <v>0.134</v>
@@ -4920,28 +4920,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M43">
-        <v>0.07431692800000002</v>
+        <v>0.07612953600000001</v>
       </c>
       <c r="N43">
-        <v>0.2393497386666666</v>
+        <v>0.2375371306666667</v>
       </c>
       <c r="O43">
-        <v>0.05265694250666667</v>
+        <v>0.05225816874666667</v>
       </c>
       <c r="P43">
-        <v>0.18669279616</v>
+        <v>0.18527896192</v>
       </c>
       <c r="Q43">
-        <v>0.47969279616</v>
+        <v>0.47827896192</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1254637788527801</v>
+        <v>0.126641334880728</v>
       </c>
       <c r="T43">
-        <v>1.159205049670272</v>
+        <v>1.176339924685296</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.220662440011871</v>
+        <v>4.120170477154447</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4966,22 +4966,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09238725423082225</v>
+        <v>0.09226643893850427</v>
       </c>
       <c r="C44">
-        <v>2.190447394232427</v>
+        <v>2.167858854671391</v>
       </c>
       <c r="D44">
-        <v>3.373567394232427</v>
+        <v>3.382338854671391</v>
       </c>
       <c r="E44">
-        <v>0.4911200000000002</v>
+        <v>0.5224800000000003</v>
       </c>
       <c r="F44">
-        <v>1.31712</v>
+        <v>1.34848</v>
       </c>
       <c r="G44">
         <v>0.134</v>
@@ -5002,28 +5002,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M44">
-        <v>0.07612953600000001</v>
+        <v>0.07794214400000002</v>
       </c>
       <c r="N44">
-        <v>0.2375371306666667</v>
+        <v>0.2357245226666666</v>
       </c>
       <c r="O44">
-        <v>0.05225816874666667</v>
+        <v>0.05185939498666666</v>
       </c>
       <c r="P44">
-        <v>0.18527896192</v>
+        <v>0.18386512768</v>
       </c>
       <c r="Q44">
-        <v>0.47827896192</v>
+        <v>0.47686512768</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.126641334880728</v>
+        <v>0.1278602086640425</v>
       </c>
       <c r="T44">
-        <v>1.176339924685296</v>
+        <v>1.194076023385058</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.120170477154447</v>
+        <v>4.024352559081087</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5048,22 +5048,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09226643893850427</v>
+        <v>0.09334682364618627</v>
       </c>
       <c r="C45">
-        <v>2.167858854671391</v>
+        <v>2.059643517247001</v>
       </c>
       <c r="D45">
-        <v>3.382338854671391</v>
+        <v>3.305483517247001</v>
       </c>
       <c r="E45">
-        <v>0.5224800000000003</v>
+        <v>0.5538400000000001</v>
       </c>
       <c r="F45">
-        <v>1.34848</v>
+        <v>1.37984</v>
       </c>
       <c r="G45">
         <v>0.134</v>
@@ -5084,45 +5084,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M45">
-        <v>0.07794214400000002</v>
+        <v>0.084584192</v>
       </c>
       <c r="N45">
-        <v>0.2357245226666666</v>
+        <v>0.2290824746666666</v>
       </c>
       <c r="O45">
-        <v>0.05185939498666666</v>
+        <v>0.05039814442666666</v>
       </c>
       <c r="P45">
-        <v>0.18386512768</v>
+        <v>0.17868433024</v>
       </c>
       <c r="Q45">
-        <v>0.47686512768</v>
+        <v>0.47168433024</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1278602086640425</v>
+        <v>0.129122613653904</v>
       </c>
       <c r="T45">
-        <v>1.194076023385058</v>
+        <v>1.21244555418124</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.024352559081087</v>
+        <v>3.708336738224876</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5130,22 +5130,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09334682364618627</v>
+        <v>0.09325330835386827</v>
       </c>
       <c r="C46">
-        <v>2.059643517247001</v>
+        <v>2.034797567965289</v>
       </c>
       <c r="D46">
-        <v>3.305483517247001</v>
+        <v>3.311997567965289</v>
       </c>
       <c r="E46">
-        <v>0.5538400000000001</v>
+        <v>0.5852000000000002</v>
       </c>
       <c r="F46">
-        <v>1.37984</v>
+        <v>1.4112</v>
       </c>
       <c r="G46">
         <v>0.134</v>
@@ -5166,28 +5166,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M46">
-        <v>0.084584192</v>
+        <v>0.08650656</v>
       </c>
       <c r="N46">
-        <v>0.2290824746666666</v>
+        <v>0.2271601066666666</v>
       </c>
       <c r="O46">
-        <v>0.05039814442666666</v>
+        <v>0.04997522346666666</v>
       </c>
       <c r="P46">
-        <v>0.17868433024</v>
+        <v>0.1771848832</v>
       </c>
       <c r="Q46">
-        <v>0.47168433024</v>
+        <v>0.4701848832</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.129122613653904</v>
+        <v>0.1304309242797605</v>
       </c>
       <c r="T46">
-        <v>1.21244555418124</v>
+        <v>1.231483067915466</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.708336738224876</v>
+        <v>3.625929255153212</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5212,22 +5212,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09325330835386827</v>
+        <v>0.0931597930615503</v>
       </c>
       <c r="C47">
-        <v>2.034797567965289</v>
+        <v>2.009977343599911</v>
       </c>
       <c r="D47">
-        <v>3.311997567965289</v>
+        <v>3.318537343599911</v>
       </c>
       <c r="E47">
-        <v>0.5852000000000002</v>
+        <v>0.6165600000000002</v>
       </c>
       <c r="F47">
-        <v>1.4112</v>
+        <v>1.44256</v>
       </c>
       <c r="G47">
         <v>0.134</v>
@@ -5248,28 +5248,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M47">
-        <v>0.08650656</v>
+        <v>0.088428928</v>
       </c>
       <c r="N47">
-        <v>0.2271601066666666</v>
+        <v>0.2252377386666666</v>
       </c>
       <c r="O47">
-        <v>0.04997522346666666</v>
+        <v>0.04955230250666666</v>
       </c>
       <c r="P47">
-        <v>0.1771848832</v>
+        <v>0.17568543616</v>
       </c>
       <c r="Q47">
-        <v>0.4701848832</v>
+        <v>0.46868543616</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1304309242797605</v>
+        <v>0.1317876908547227</v>
       </c>
       <c r="T47">
-        <v>1.231483067915466</v>
+        <v>1.251225674750958</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.625929255153212</v>
+        <v>3.547104706128142</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5294,22 +5294,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0931597930615503</v>
+        <v>0.0940927577692323</v>
       </c>
       <c r="C48">
-        <v>2.009977343599911</v>
+        <v>1.914506732284273</v>
       </c>
       <c r="D48">
-        <v>3.318537343599911</v>
+        <v>3.254426732284273</v>
       </c>
       <c r="E48">
-        <v>0.6165600000000002</v>
+        <v>0.6479200000000003</v>
       </c>
       <c r="F48">
-        <v>1.44256</v>
+        <v>1.47392</v>
       </c>
       <c r="G48">
         <v>0.134</v>
@@ -5330,45 +5330,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M48">
-        <v>0.088428928</v>
+        <v>0.09447827200000002</v>
       </c>
       <c r="N48">
-        <v>0.2252377386666666</v>
+        <v>0.2191883946666666</v>
       </c>
       <c r="O48">
-        <v>0.04955230250666666</v>
+        <v>0.04822144682666666</v>
       </c>
       <c r="P48">
-        <v>0.17568543616</v>
+        <v>0.17096694784</v>
       </c>
       <c r="Q48">
-        <v>0.46868543616</v>
+        <v>0.46396694784</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1317876908547227</v>
+        <v>0.1331956561683628</v>
       </c>
       <c r="T48">
-        <v>1.251225674750958</v>
+        <v>1.271713285617979</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.547104706128142</v>
+        <v>3.319987337053186</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5376,22 +5376,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0940927577692323</v>
+        <v>0.09402108247691432</v>
       </c>
       <c r="C49">
-        <v>1.914506732284273</v>
+        <v>1.887984076768931</v>
       </c>
       <c r="D49">
-        <v>3.254426732284273</v>
+        <v>3.259264076768932</v>
       </c>
       <c r="E49">
-        <v>0.6479200000000003</v>
+        <v>0.6792800000000003</v>
       </c>
       <c r="F49">
-        <v>1.47392</v>
+        <v>1.50528</v>
       </c>
       <c r="G49">
         <v>0.134</v>
@@ -5412,28 +5412,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M49">
-        <v>0.09447827200000002</v>
+        <v>0.09648844800000002</v>
       </c>
       <c r="N49">
-        <v>0.2191883946666666</v>
+        <v>0.2171782186666666</v>
       </c>
       <c r="O49">
-        <v>0.04822144682666666</v>
+        <v>0.04777920810666667</v>
       </c>
       <c r="P49">
-        <v>0.17096694784</v>
+        <v>0.16939901056</v>
       </c>
       <c r="Q49">
-        <v>0.46396694784</v>
+        <v>0.46239901056</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1331956561683628</v>
+        <v>0.134657773994066</v>
       </c>
       <c r="T49">
-        <v>1.271713285617979</v>
+        <v>1.292988881518347</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.319987337053186</v>
+        <v>3.250820934197912</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5458,22 +5458,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09402108247691429</v>
+        <v>0.09394940718459632</v>
       </c>
       <c r="C50">
-        <v>1.887984076768933</v>
+        <v>1.861475823012625</v>
       </c>
       <c r="D50">
-        <v>3.259264076768933</v>
+        <v>3.264115823012625</v>
       </c>
       <c r="E50">
-        <v>0.6792800000000001</v>
+        <v>0.7106400000000002</v>
       </c>
       <c r="F50">
-        <v>1.50528</v>
+        <v>1.53664</v>
       </c>
       <c r="G50">
         <v>0.134</v>
@@ -5494,28 +5494,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M50">
-        <v>0.096488448</v>
+        <v>0.09849862400000001</v>
       </c>
       <c r="N50">
-        <v>0.2171782186666666</v>
+        <v>0.2151680426666666</v>
       </c>
       <c r="O50">
-        <v>0.04777920810666667</v>
+        <v>0.04733696938666666</v>
       </c>
       <c r="P50">
-        <v>0.16939901056</v>
+        <v>0.16783107328</v>
       </c>
       <c r="Q50">
-        <v>0.46239901056</v>
+        <v>0.46083107328</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1346577739940659</v>
+        <v>0.1361772297737183</v>
       </c>
       <c r="T50">
-        <v>1.292988881518347</v>
+        <v>1.315098814512847</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.250820934197912</v>
+        <v>3.184477649826526</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5540,22 +5540,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09394940718459632</v>
+        <v>0.09387773189227833</v>
       </c>
       <c r="C51">
-        <v>1.861475823012625</v>
+        <v>1.834982035426689</v>
       </c>
       <c r="D51">
-        <v>3.264115823012625</v>
+        <v>3.268982035426689</v>
       </c>
       <c r="E51">
-        <v>0.7106400000000002</v>
+        <v>0.7420000000000002</v>
       </c>
       <c r="F51">
-        <v>1.53664</v>
+        <v>1.568</v>
       </c>
       <c r="G51">
         <v>0.134</v>
@@ -5576,28 +5576,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M51">
-        <v>0.09849862400000001</v>
+        <v>0.1005088</v>
       </c>
       <c r="N51">
-        <v>0.2151680426666666</v>
+        <v>0.2131578666666666</v>
       </c>
       <c r="O51">
-        <v>0.04733696938666666</v>
+        <v>0.04689473066666666</v>
       </c>
       <c r="P51">
-        <v>0.16783107328</v>
+        <v>0.166263136</v>
       </c>
       <c r="Q51">
-        <v>0.46083107328</v>
+        <v>0.459263136</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1361772297737183</v>
+        <v>0.1377574637845566</v>
       </c>
       <c r="T51">
-        <v>1.315098814512847</v>
+        <v>1.338093144827126</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.184477649826526</v>
+        <v>3.120788096829995</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5622,22 +5622,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09387773189227833</v>
+        <v>0.09380605659996033</v>
       </c>
       <c r="C52">
-        <v>1.834982035426689</v>
+        <v>1.808502778807133</v>
       </c>
       <c r="D52">
-        <v>3.268982035426689</v>
+        <v>3.273862778807133</v>
       </c>
       <c r="E52">
-        <v>0.7420000000000002</v>
+        <v>0.7733600000000003</v>
       </c>
       <c r="F52">
-        <v>1.568</v>
+        <v>1.59936</v>
       </c>
       <c r="G52">
         <v>0.134</v>
@@ -5658,28 +5658,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M52">
-        <v>0.1005088</v>
+        <v>0.102518976</v>
       </c>
       <c r="N52">
-        <v>0.2131578666666666</v>
+        <v>0.2111476906666666</v>
       </c>
       <c r="O52">
-        <v>0.04689473066666666</v>
+        <v>0.04645249194666666</v>
       </c>
       <c r="P52">
-        <v>0.166263136</v>
+        <v>0.16469519872</v>
       </c>
       <c r="Q52">
-        <v>0.459263136</v>
+        <v>0.45769519872</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1377574637845566</v>
+        <v>0.1394021971427762</v>
       </c>
       <c r="T52">
-        <v>1.338093144827126</v>
+        <v>1.362026019235866</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.120788096829995</v>
+        <v>3.05959617336274</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5704,22 +5704,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09380605659996033</v>
+        <v>0.09373438130764233</v>
       </c>
       <c r="C53">
-        <v>1.808502778807133</v>
+        <v>1.782038118337521</v>
       </c>
       <c r="D53">
-        <v>3.273862778807133</v>
+        <v>3.278758118337521</v>
       </c>
       <c r="E53">
-        <v>0.7733600000000003</v>
+        <v>0.8047200000000003</v>
       </c>
       <c r="F53">
-        <v>1.59936</v>
+        <v>1.63072</v>
       </c>
       <c r="G53">
         <v>0.134</v>
@@ -5740,28 +5740,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M53">
-        <v>0.102518976</v>
+        <v>0.104529152</v>
       </c>
       <c r="N53">
-        <v>0.2111476906666666</v>
+        <v>0.2091375146666666</v>
       </c>
       <c r="O53">
-        <v>0.04645249194666666</v>
+        <v>0.04601025322666666</v>
       </c>
       <c r="P53">
-        <v>0.16469519872</v>
+        <v>0.16312726144</v>
       </c>
       <c r="Q53">
-        <v>0.45769519872</v>
+        <v>0.45612726144</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1394021971427762</v>
+        <v>0.1411154610575882</v>
       </c>
       <c r="T53">
-        <v>1.362026019235866</v>
+        <v>1.386956096744971</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.05959617336274</v>
+        <v>3.000757785413457</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5786,22 +5786,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09373438130764233</v>
+        <v>0.09688722601532435</v>
       </c>
       <c r="C54">
-        <v>1.782038118337521</v>
+        <v>1.548329782217861</v>
       </c>
       <c r="D54">
-        <v>3.278758118337521</v>
+        <v>3.076409782217862</v>
       </c>
       <c r="E54">
-        <v>0.8047200000000003</v>
+        <v>0.8360800000000004</v>
       </c>
       <c r="F54">
-        <v>1.63072</v>
+        <v>1.66208</v>
       </c>
       <c r="G54">
         <v>0.134</v>
@@ -5822,45 +5822,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M54">
-        <v>0.104529152</v>
+        <v>0.119503552</v>
       </c>
       <c r="N54">
-        <v>0.2091375146666666</v>
+        <v>0.1941631146666666</v>
       </c>
       <c r="O54">
-        <v>0.04601025322666666</v>
+        <v>0.04271588522666666</v>
       </c>
       <c r="P54">
-        <v>0.16312726144</v>
+        <v>0.15144722944</v>
       </c>
       <c r="Q54">
-        <v>0.45612726144</v>
+        <v>0.44444722944</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1411154610575882</v>
+        <v>0.142901629819839</v>
       </c>
       <c r="T54">
-        <v>1.386956096744971</v>
+        <v>1.412947028616165</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.000757785413457</v>
+        <v>2.624747644878929</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5868,22 +5868,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09688722601532435</v>
+        <v>0.09687639072300636</v>
       </c>
       <c r="C55">
-        <v>1.548329782217861</v>
+        <v>1.517622408584141</v>
       </c>
       <c r="D55">
-        <v>3.076409782217862</v>
+        <v>3.077062408584142</v>
       </c>
       <c r="E55">
-        <v>0.8360800000000004</v>
+        <v>0.8674400000000004</v>
       </c>
       <c r="F55">
-        <v>1.66208</v>
+        <v>1.69344</v>
       </c>
       <c r="G55">
         <v>0.134</v>
@@ -5904,28 +5904,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M55">
-        <v>0.119503552</v>
+        <v>0.121758336</v>
       </c>
       <c r="N55">
-        <v>0.1941631146666666</v>
+        <v>0.1919083306666666</v>
       </c>
       <c r="O55">
-        <v>0.04271588522666666</v>
+        <v>0.04221983274666666</v>
       </c>
       <c r="P55">
-        <v>0.15144722944</v>
+        <v>0.14968849792</v>
       </c>
       <c r="Q55">
-        <v>0.44444722944</v>
+        <v>0.44268849792</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.142901629819839</v>
+        <v>0.1447654580934921</v>
       </c>
       <c r="T55">
-        <v>1.412947028616165</v>
+        <v>1.440068001003497</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.624747644878929</v>
+        <v>2.5761412070108</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5950,22 +5950,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09687639072300636</v>
+        <v>0.09686555543068837</v>
       </c>
       <c r="C56">
-        <v>1.517622408584141</v>
+        <v>1.486915311904129</v>
       </c>
       <c r="D56">
-        <v>3.077062408584142</v>
+        <v>3.077715311904129</v>
       </c>
       <c r="E56">
-        <v>0.8674400000000004</v>
+        <v>0.8988000000000003</v>
       </c>
       <c r="F56">
-        <v>1.69344</v>
+        <v>1.7248</v>
       </c>
       <c r="G56">
         <v>0.134</v>
@@ -5986,28 +5986,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M56">
-        <v>0.121758336</v>
+        <v>0.12401312</v>
       </c>
       <c r="N56">
-        <v>0.1919083306666666</v>
+        <v>0.1896535466666666</v>
       </c>
       <c r="O56">
-        <v>0.04221983274666666</v>
+        <v>0.04172378026666666</v>
       </c>
       <c r="P56">
-        <v>0.14968849792</v>
+        <v>0.1479297664</v>
       </c>
       <c r="Q56">
-        <v>0.44268849792</v>
+        <v>0.4409297664</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1447654580934921</v>
+        <v>0.1467121231793075</v>
       </c>
       <c r="T56">
-        <v>1.440068001003497</v>
+        <v>1.468394349941378</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.5761412070108</v>
+        <v>2.52930227597424</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6032,22 +6032,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09686555543068837</v>
+        <v>0.09855824013837036</v>
       </c>
       <c r="C57">
-        <v>1.486915311904129</v>
+        <v>1.356810516221113</v>
       </c>
       <c r="D57">
-        <v>3.077715311904129</v>
+        <v>2.978970516221114</v>
       </c>
       <c r="E57">
-        <v>0.8988000000000003</v>
+        <v>0.9301600000000003</v>
       </c>
       <c r="F57">
-        <v>1.7248</v>
+        <v>1.75616</v>
       </c>
       <c r="G57">
         <v>0.134</v>
@@ -6068,45 +6068,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M57">
-        <v>0.12401312</v>
+        <v>0.133116928</v>
       </c>
       <c r="N57">
-        <v>0.1896535466666666</v>
+        <v>0.1805497386666666</v>
       </c>
       <c r="O57">
-        <v>0.04172378026666666</v>
+        <v>0.03972094250666666</v>
       </c>
       <c r="P57">
-        <v>0.1479297664</v>
+        <v>0.14082879616</v>
       </c>
       <c r="Q57">
-        <v>0.4409297664</v>
+        <v>0.43382879616</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1467121231793075</v>
+        <v>0.1487472730417508</v>
       </c>
       <c r="T57">
-        <v>1.468394349941378</v>
+        <v>1.498008260194617</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.22</v>
       </c>
       <c r="W57">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.52930227597424</v>
+        <v>2.356324408768407</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6114,22 +6114,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09855824013837036</v>
+        <v>0.09857782484605239</v>
       </c>
       <c r="C58">
-        <v>1.356810516221113</v>
+        <v>1.32434508478426</v>
       </c>
       <c r="D58">
-        <v>2.978970516221114</v>
+        <v>2.97786508478426</v>
       </c>
       <c r="E58">
-        <v>0.9301600000000003</v>
+        <v>0.9615200000000004</v>
       </c>
       <c r="F58">
-        <v>1.75616</v>
+        <v>1.78752</v>
       </c>
       <c r="G58">
         <v>0.134</v>
@@ -6150,28 +6150,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M58">
-        <v>0.133116928</v>
+        <v>0.135494016</v>
       </c>
       <c r="N58">
-        <v>0.1805497386666666</v>
+        <v>0.1781726506666666</v>
       </c>
       <c r="O58">
-        <v>0.03972094250666666</v>
+        <v>0.03919798314666666</v>
       </c>
       <c r="P58">
-        <v>0.14082879616</v>
+        <v>0.13897466752</v>
       </c>
       <c r="Q58">
-        <v>0.43382879616</v>
+        <v>0.43197466752</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1487472730417508</v>
+        <v>0.1508770810373311</v>
       </c>
       <c r="T58">
-        <v>1.498008260194617</v>
+        <v>1.528999561622426</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.356324408768407</v>
+        <v>2.314985384053172</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6196,22 +6196,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09857782484605239</v>
+        <v>0.09859740955373439</v>
       </c>
       <c r="C59">
-        <v>1.32434508478426</v>
+        <v>1.291880473446414</v>
       </c>
       <c r="D59">
-        <v>2.97786508478426</v>
+        <v>2.976760473446415</v>
       </c>
       <c r="E59">
-        <v>0.9615200000000004</v>
+        <v>0.9928800000000004</v>
       </c>
       <c r="F59">
-        <v>1.78752</v>
+        <v>1.81888</v>
       </c>
       <c r="G59">
         <v>0.134</v>
@@ -6232,28 +6232,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M59">
-        <v>0.135494016</v>
+        <v>0.137871104</v>
       </c>
       <c r="N59">
-        <v>0.1781726506666666</v>
+        <v>0.1757955626666666</v>
       </c>
       <c r="O59">
-        <v>0.03919798314666666</v>
+        <v>0.03867502378666666</v>
       </c>
       <c r="P59">
-        <v>0.13897466752</v>
+        <v>0.13712053888</v>
       </c>
       <c r="Q59">
-        <v>0.43197466752</v>
+        <v>0.43012053888</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1508770810373311</v>
+        <v>0.1531083084612724</v>
       </c>
       <c r="T59">
-        <v>1.528999561622426</v>
+        <v>1.561466639308701</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.314985384053172</v>
+        <v>2.275071842948807</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6278,22 +6278,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09859740955373439</v>
+        <v>0.0986169942614164</v>
       </c>
       <c r="C60">
-        <v>1.291880473446414</v>
+        <v>1.259416681295288</v>
       </c>
       <c r="D60">
-        <v>2.976760473446415</v>
+        <v>2.975656681295288</v>
       </c>
       <c r="E60">
-        <v>0.9928800000000002</v>
+        <v>1.02424</v>
       </c>
       <c r="F60">
-        <v>1.81888</v>
+        <v>1.85024</v>
       </c>
       <c r="G60">
         <v>0.134</v>
@@ -6314,28 +6314,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M60">
-        <v>0.137871104</v>
+        <v>0.140248192</v>
       </c>
       <c r="N60">
-        <v>0.1757955626666666</v>
+        <v>0.1734184746666667</v>
       </c>
       <c r="O60">
-        <v>0.03867502378666666</v>
+        <v>0.03815206442666667</v>
       </c>
       <c r="P60">
-        <v>0.13712053888</v>
+        <v>0.13526641024</v>
       </c>
       <c r="Q60">
-        <v>0.43012053888</v>
+        <v>0.42826641024</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1531083084612723</v>
+        <v>0.1554483762473571</v>
       </c>
       <c r="T60">
-        <v>1.561466639308701</v>
+        <v>1.595517476882112</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.275071842948807</v>
+        <v>2.236511303237811</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6360,22 +6360,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0986169942614164</v>
+        <v>0.09863657896909842</v>
       </c>
       <c r="C61">
-        <v>1.259416681295288</v>
+        <v>1.22695370741995</v>
       </c>
       <c r="D61">
-        <v>2.975656681295288</v>
+        <v>2.97455370741995</v>
       </c>
       <c r="E61">
-        <v>1.02424</v>
+        <v>1.0556</v>
       </c>
       <c r="F61">
-        <v>1.85024</v>
+        <v>1.8816</v>
       </c>
       <c r="G61">
         <v>0.134</v>
@@ -6396,28 +6396,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M61">
-        <v>0.140248192</v>
+        <v>0.14262528</v>
       </c>
       <c r="N61">
-        <v>0.1734184746666667</v>
+        <v>0.1710413866666666</v>
       </c>
       <c r="O61">
-        <v>0.03815206442666667</v>
+        <v>0.03762910506666666</v>
       </c>
       <c r="P61">
-        <v>0.13526641024</v>
+        <v>0.1334122816</v>
       </c>
       <c r="Q61">
-        <v>0.42826641024</v>
+        <v>0.4264122816</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1554483762473571</v>
+        <v>0.157905447422746</v>
       </c>
       <c r="T61">
-        <v>1.595517476882112</v>
+        <v>1.631270856334193</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.236511303237811</v>
+        <v>2.199236114850513</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6442,22 +6442,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09863657896909842</v>
+        <v>0.0986561636767804</v>
       </c>
       <c r="C62">
-        <v>1.22695370741995</v>
+        <v>1.194491550910816</v>
       </c>
       <c r="D62">
-        <v>2.97455370741995</v>
+        <v>2.973451550910816</v>
       </c>
       <c r="E62">
-        <v>1.0556</v>
+        <v>1.08696</v>
       </c>
       <c r="F62">
-        <v>1.8816</v>
+        <v>1.91296</v>
       </c>
       <c r="G62">
         <v>0.134</v>
@@ -6478,28 +6478,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M62">
-        <v>0.14262528</v>
+        <v>0.145002368</v>
       </c>
       <c r="N62">
-        <v>0.1710413866666666</v>
+        <v>0.1686642986666666</v>
       </c>
       <c r="O62">
-        <v>0.03762910506666666</v>
+        <v>0.03710614570666666</v>
       </c>
       <c r="P62">
-        <v>0.1334122816</v>
+        <v>0.13155815296</v>
       </c>
       <c r="Q62">
-        <v>0.4264122816</v>
+        <v>0.42455815296</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.157905447422746</v>
+        <v>0.1604885222481549</v>
       </c>
       <c r="T62">
-        <v>1.631270856334193</v>
+        <v>1.668857742424843</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.199236114850513</v>
+        <v>2.16318306378739</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6524,22 +6524,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0986561636767804</v>
+        <v>0.09867574838446241</v>
       </c>
       <c r="C63">
-        <v>1.194491550910816</v>
+        <v>1.16203021085965</v>
       </c>
       <c r="D63">
-        <v>2.973451550910816</v>
+        <v>2.97235021085965</v>
       </c>
       <c r="E63">
-        <v>1.08696</v>
+        <v>1.11832</v>
       </c>
       <c r="F63">
-        <v>1.91296</v>
+        <v>1.94432</v>
       </c>
       <c r="G63">
         <v>0.134</v>
@@ -6560,28 +6560,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M63">
-        <v>0.145002368</v>
+        <v>0.147379456</v>
       </c>
       <c r="N63">
-        <v>0.1686642986666666</v>
+        <v>0.1662872106666666</v>
       </c>
       <c r="O63">
-        <v>0.03710614570666666</v>
+        <v>0.03658318634666666</v>
       </c>
       <c r="P63">
-        <v>0.13155815296</v>
+        <v>0.12970402432</v>
       </c>
       <c r="Q63">
-        <v>0.42455815296</v>
+        <v>0.42270402432</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1604885222481549</v>
+        <v>0.1632075483801642</v>
       </c>
       <c r="T63">
-        <v>1.668857742424843</v>
+        <v>1.708422885678158</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.16318306378739</v>
+        <v>2.128293014371464</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6606,22 +6606,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09867574838446241</v>
+        <v>0.09869533309214443</v>
       </c>
       <c r="C64">
-        <v>1.16203021085965</v>
+        <v>1.129569686359561</v>
       </c>
       <c r="D64">
-        <v>2.97235021085965</v>
+        <v>2.971249686359561</v>
       </c>
       <c r="E64">
-        <v>1.11832</v>
+        <v>1.14968</v>
       </c>
       <c r="F64">
-        <v>1.94432</v>
+        <v>1.97568</v>
       </c>
       <c r="G64">
         <v>0.134</v>
@@ -6642,28 +6642,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M64">
-        <v>0.147379456</v>
+        <v>0.149756544</v>
       </c>
       <c r="N64">
-        <v>0.1662872106666666</v>
+        <v>0.1639101226666666</v>
       </c>
       <c r="O64">
-        <v>0.03658318634666666</v>
+        <v>0.03606022698666666</v>
       </c>
       <c r="P64">
-        <v>0.12970402432</v>
+        <v>0.12784989568</v>
       </c>
       <c r="Q64">
-        <v>0.42270402432</v>
+        <v>0.42084989568</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1632075483801642</v>
+        <v>0.1660735488976876</v>
       </c>
       <c r="T64">
-        <v>1.708422885678158</v>
+        <v>1.750126685323545</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.128293014371464</v>
+        <v>2.094510585571917</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6688,22 +6688,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09869533309214443</v>
+        <v>0.09871491779982644</v>
       </c>
       <c r="C65">
-        <v>1.129569686359561</v>
+        <v>1.097109976505002</v>
       </c>
       <c r="D65">
-        <v>2.971249686359561</v>
+        <v>2.970149976505002</v>
       </c>
       <c r="E65">
-        <v>1.14968</v>
+        <v>1.18104</v>
       </c>
       <c r="F65">
-        <v>1.97568</v>
+        <v>2.00704</v>
       </c>
       <c r="G65">
         <v>0.134</v>
@@ -6724,28 +6724,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M65">
-        <v>0.149756544</v>
+        <v>0.152133632</v>
       </c>
       <c r="N65">
-        <v>0.1639101226666666</v>
+        <v>0.1615330346666666</v>
       </c>
       <c r="O65">
-        <v>0.03606022698666666</v>
+        <v>0.03553726762666666</v>
       </c>
       <c r="P65">
-        <v>0.12784989568</v>
+        <v>0.12599576704</v>
       </c>
       <c r="Q65">
-        <v>0.42084989568</v>
+        <v>0.41899576704</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1660735488976876</v>
+        <v>0.1690987716661845</v>
       </c>
       <c r="T65">
-        <v>1.750126685323545</v>
+        <v>1.794147362727008</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.094510585571917</v>
+        <v>2.061783857672356</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6770,22 +6770,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09871491779982644</v>
+        <v>0.09873450250750845</v>
       </c>
       <c r="C66">
-        <v>1.097109976505002</v>
+        <v>1.064651080391766</v>
       </c>
       <c r="D66">
-        <v>2.970149976505002</v>
+        <v>2.969051080391766</v>
       </c>
       <c r="E66">
-        <v>1.18104</v>
+        <v>1.2124</v>
       </c>
       <c r="F66">
-        <v>2.00704</v>
+        <v>2.0384</v>
       </c>
       <c r="G66">
         <v>0.134</v>
@@ -6806,28 +6806,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M66">
-        <v>0.152133632</v>
+        <v>0.15451072</v>
       </c>
       <c r="N66">
-        <v>0.1615330346666666</v>
+        <v>0.1591559466666666</v>
       </c>
       <c r="O66">
-        <v>0.03553726762666666</v>
+        <v>0.03501430826666666</v>
       </c>
       <c r="P66">
-        <v>0.12599576704</v>
+        <v>0.1241416384</v>
       </c>
       <c r="Q66">
-        <v>0.41899576704</v>
+        <v>0.4171416384</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1690987716661845</v>
+        <v>0.172296864307167</v>
       </c>
       <c r="T66">
-        <v>1.794147362727008</v>
+        <v>1.84068350741067</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.061783857672356</v>
+        <v>2.030064106015859</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6852,22 +6852,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09873450250750845</v>
+        <v>0.1060642472151904</v>
       </c>
       <c r="C67">
-        <v>1.064651080391766</v>
+        <v>0.6721750381448541</v>
       </c>
       <c r="D67">
-        <v>2.969051080391766</v>
+        <v>2.607935038144854</v>
       </c>
       <c r="E67">
-        <v>1.2124</v>
+        <v>1.24376</v>
       </c>
       <c r="F67">
-        <v>2.0384</v>
+        <v>2.06976</v>
       </c>
       <c r="G67">
         <v>0.134</v>
@@ -6888,45 +6888,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M67">
-        <v>0.15451072</v>
+        <v>0.1862784</v>
       </c>
       <c r="N67">
-        <v>0.1591559466666666</v>
+        <v>0.1273882666666666</v>
       </c>
       <c r="O67">
-        <v>0.03501430826666666</v>
+        <v>0.02802541866666666</v>
       </c>
       <c r="P67">
-        <v>0.1241416384</v>
+        <v>0.09936284799999998</v>
       </c>
       <c r="Q67">
-        <v>0.4171416384</v>
+        <v>0.392362848</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.172296864307167</v>
+        <v>0.1756830800446778</v>
       </c>
       <c r="T67">
-        <v>1.84068350741067</v>
+        <v>1.889957072369841</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.030064106015859</v>
+        <v>1.683859570764332</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6934,22 +6934,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1060642472151904</v>
+        <v>0.1061945919228725</v>
       </c>
       <c r="C68">
-        <v>0.6721750381448541</v>
+        <v>0.6351865452719361</v>
       </c>
       <c r="D68">
-        <v>2.607935038144854</v>
+        <v>2.602306545271936</v>
       </c>
       <c r="E68">
-        <v>1.24376</v>
+        <v>1.27512</v>
       </c>
       <c r="F68">
-        <v>2.06976</v>
+        <v>2.10112</v>
       </c>
       <c r="G68">
         <v>0.134</v>
@@ -6970,28 +6970,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M68">
-        <v>0.1862784</v>
+        <v>0.1891008</v>
       </c>
       <c r="N68">
-        <v>0.1273882666666666</v>
+        <v>0.1245658666666666</v>
       </c>
       <c r="O68">
-        <v>0.02802541866666666</v>
+        <v>0.02740449066666666</v>
       </c>
       <c r="P68">
-        <v>0.09936284799999998</v>
+        <v>0.09716137599999998</v>
       </c>
       <c r="Q68">
-        <v>0.392362848</v>
+        <v>0.390161376</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1756830800446778</v>
+        <v>0.1792745209784014</v>
       </c>
       <c r="T68">
-        <v>1.889957072369841</v>
+        <v>1.942216913993204</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.683859570764332</v>
+        <v>1.658727338364865</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7016,22 +7016,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1061945919228725</v>
+        <v>0.1063249366305545</v>
       </c>
       <c r="C69">
-        <v>0.6351865452719361</v>
+        <v>0.5982222951095126</v>
       </c>
       <c r="D69">
-        <v>2.602306545271936</v>
+        <v>2.596702295109513</v>
       </c>
       <c r="E69">
-        <v>1.27512</v>
+        <v>1.30648</v>
       </c>
       <c r="F69">
-        <v>2.10112</v>
+        <v>2.13248</v>
       </c>
       <c r="G69">
         <v>0.134</v>
@@ -7052,28 +7052,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M69">
-        <v>0.1891008</v>
+        <v>0.1919232</v>
       </c>
       <c r="N69">
-        <v>0.1245658666666666</v>
+        <v>0.1217434666666666</v>
       </c>
       <c r="O69">
-        <v>0.02740449066666666</v>
+        <v>0.02678356266666666</v>
       </c>
       <c r="P69">
-        <v>0.09716137599999998</v>
+        <v>0.09495990399999997</v>
       </c>
       <c r="Q69">
-        <v>0.390161376</v>
+        <v>0.387959904</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1792745209784014</v>
+        <v>0.1830904269704828</v>
       </c>
       <c r="T69">
-        <v>1.942216913993204</v>
+        <v>1.997742995718027</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.658727338364865</v>
+        <v>1.634334289271264</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7098,22 +7098,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1063249366305545</v>
+        <v>0.1064552813382365</v>
       </c>
       <c r="C70">
-        <v>0.5982222951095126</v>
+        <v>0.5612821313690159</v>
       </c>
       <c r="D70">
-        <v>2.596702295109513</v>
+        <v>2.591122131369016</v>
       </c>
       <c r="E70">
-        <v>1.30648</v>
+        <v>1.337840000000001</v>
       </c>
       <c r="F70">
-        <v>2.13248</v>
+        <v>2.16384</v>
       </c>
       <c r="G70">
         <v>0.134</v>
@@ -7134,28 +7134,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M70">
-        <v>0.1919232</v>
+        <v>0.1947456</v>
       </c>
       <c r="N70">
-        <v>0.1217434666666666</v>
+        <v>0.1189210666666666</v>
       </c>
       <c r="O70">
-        <v>0.02678356266666666</v>
+        <v>0.02616263466666666</v>
       </c>
       <c r="P70">
-        <v>0.09495990399999997</v>
+        <v>0.09275843199999997</v>
       </c>
       <c r="Q70">
-        <v>0.387959904</v>
+        <v>0.385758432</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1830904269704828</v>
+        <v>0.1871525204459242</v>
       </c>
       <c r="T70">
-        <v>1.997742995718027</v>
+        <v>2.056851405296065</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.634334289271264</v>
+        <v>1.610648285078927</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7180,22 +7180,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1064552813382365</v>
+        <v>0.1065856260459185</v>
       </c>
       <c r="C71">
-        <v>0.5612821313690159</v>
+        <v>0.5243658991024187</v>
       </c>
       <c r="D71">
-        <v>2.591122131369016</v>
+        <v>2.585565899102419</v>
       </c>
       <c r="E71">
-        <v>1.337840000000001</v>
+        <v>1.3692</v>
       </c>
       <c r="F71">
-        <v>2.16384</v>
+        <v>2.1952</v>
       </c>
       <c r="G71">
         <v>0.134</v>
@@ -7216,28 +7216,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M71">
-        <v>0.1947456</v>
+        <v>0.197568</v>
       </c>
       <c r="N71">
-        <v>0.1189210666666666</v>
+        <v>0.1160986666666666</v>
       </c>
       <c r="O71">
-        <v>0.02616263466666666</v>
+        <v>0.02554170666666666</v>
       </c>
       <c r="P71">
-        <v>0.09275843199999997</v>
+        <v>0.09055695999999996</v>
       </c>
       <c r="Q71">
-        <v>0.385758432</v>
+        <v>0.38355696</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1871525204459242</v>
+        <v>0.1914854201530616</v>
       </c>
       <c r="T71">
-        <v>2.056851405296065</v>
+        <v>2.119900375512638</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.610648285078927</v>
+        <v>1.587639023863513</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7262,22 +7262,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1065856260459185</v>
+        <v>0.1067159707536005</v>
       </c>
       <c r="C72">
-        <v>0.5243658991024187</v>
+        <v>0.4874734446878883</v>
       </c>
       <c r="D72">
-        <v>2.585565899102419</v>
+        <v>2.580033444687889</v>
       </c>
       <c r="E72">
-        <v>1.3692</v>
+        <v>1.400560000000001</v>
       </c>
       <c r="F72">
-        <v>2.1952</v>
+        <v>2.226560000000001</v>
       </c>
       <c r="G72">
         <v>0.134</v>
@@ -7298,28 +7298,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M72">
-        <v>0.197568</v>
+        <v>0.2003904000000001</v>
       </c>
       <c r="N72">
-        <v>0.1160986666666666</v>
+        <v>0.1132762666666666</v>
       </c>
       <c r="O72">
-        <v>0.02554170666666666</v>
+        <v>0.02492077866666665</v>
       </c>
       <c r="P72">
-        <v>0.09055695999999996</v>
+        <v>0.08835548799999995</v>
       </c>
       <c r="Q72">
-        <v>0.38355696</v>
+        <v>0.381355488</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1914854201530616</v>
+        <v>0.196117140529657</v>
       </c>
       <c r="T72">
-        <v>2.119900375512638</v>
+        <v>2.187297550571735</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.587639023863513</v>
+        <v>1.565277910851351</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7344,22 +7344,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1067159707536005</v>
+        <v>0.1068463154612825</v>
       </c>
       <c r="C73">
-        <v>0.4874734446878888</v>
+        <v>0.4506046158156387</v>
       </c>
       <c r="D73">
-        <v>2.580033444687889</v>
+        <v>2.574524615815639</v>
       </c>
       <c r="E73">
-        <v>1.40056</v>
+        <v>1.43192</v>
       </c>
       <c r="F73">
-        <v>2.22656</v>
+        <v>2.25792</v>
       </c>
       <c r="G73">
         <v>0.134</v>
@@ -7380,28 +7380,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M73">
-        <v>0.2003904</v>
+        <v>0.2032128</v>
       </c>
       <c r="N73">
-        <v>0.1132762666666667</v>
+        <v>0.1104538666666667</v>
       </c>
       <c r="O73">
-        <v>0.02492077866666666</v>
+        <v>0.02429985066666666</v>
       </c>
       <c r="P73">
-        <v>0.08835548799999998</v>
+        <v>0.08615401599999999</v>
       </c>
       <c r="Q73">
-        <v>0.381355488</v>
+        <v>0.379154016</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1961171405296569</v>
+        <v>0.201079698076009</v>
       </c>
       <c r="T73">
-        <v>2.187297550571734</v>
+        <v>2.259508809563623</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.565277910851351</v>
+        <v>1.543537939867305</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7426,22 +7426,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1068463154612825</v>
+        <v>0.1069766601689645</v>
       </c>
       <c r="C74">
-        <v>0.4506046158156387</v>
+        <v>0.4137592614739374</v>
       </c>
       <c r="D74">
-        <v>2.574524615815639</v>
+        <v>2.569039261473938</v>
       </c>
       <c r="E74">
-        <v>1.43192</v>
+        <v>1.46328</v>
       </c>
       <c r="F74">
-        <v>2.25792</v>
+        <v>2.28928</v>
       </c>
       <c r="G74">
         <v>0.134</v>
@@ -7462,28 +7462,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M74">
-        <v>0.2032128</v>
+        <v>0.2060352</v>
       </c>
       <c r="N74">
-        <v>0.1104538666666667</v>
+        <v>0.1076314666666666</v>
       </c>
       <c r="O74">
-        <v>0.02429985066666666</v>
+        <v>0.02367892266666666</v>
       </c>
       <c r="P74">
-        <v>0.08615401599999999</v>
+        <v>0.08395254399999999</v>
       </c>
       <c r="Q74">
-        <v>0.379154016</v>
+        <v>0.376952544</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.201079698076009</v>
+        <v>0.2064098524776463</v>
       </c>
       <c r="T74">
-        <v>2.259508809563623</v>
+        <v>2.337069050703058</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.543537939867305</v>
+        <v>1.522393584526657</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7508,22 +7508,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1069766601689645</v>
+        <v>0.1071070048766465</v>
       </c>
       <c r="C75">
-        <v>0.4137592614739374</v>
+        <v>0.3769372319353197</v>
       </c>
       <c r="D75">
-        <v>2.569039261473938</v>
+        <v>2.56357723193532</v>
       </c>
       <c r="E75">
-        <v>1.46328</v>
+        <v>1.49464</v>
       </c>
       <c r="F75">
-        <v>2.28928</v>
+        <v>2.32064</v>
       </c>
       <c r="G75">
         <v>0.134</v>
@@ -7544,28 +7544,28 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M75">
-        <v>0.2060352</v>
+        <v>0.2088576</v>
       </c>
       <c r="N75">
-        <v>0.1076314666666666</v>
+        <v>0.1048090666666666</v>
       </c>
       <c r="O75">
-        <v>0.02367892266666666</v>
+        <v>0.02305799466666666</v>
       </c>
       <c r="P75">
-        <v>0.08395254399999999</v>
+        <v>0.08175107199999998</v>
       </c>
       <c r="Q75">
-        <v>0.376952544</v>
+        <v>0.374751072</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2064098524776463</v>
+        <v>0.2121500187563328</v>
       </c>
       <c r="T75">
-        <v>2.337069050703058</v>
+        <v>2.420595464237835</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.522393584526657</v>
+        <v>1.501820698249269</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7590,22 +7590,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1071070048766465</v>
+        <v>0.1434629876393251</v>
       </c>
       <c r="C76">
-        <v>0.3769372319353197</v>
+        <v>-0.6087389517885864</v>
       </c>
       <c r="D76">
-        <v>2.56357723193532</v>
+        <v>1.609261048211414</v>
       </c>
       <c r="E76">
-        <v>1.49464</v>
+        <v>1.526</v>
       </c>
       <c r="F76">
-        <v>2.32064</v>
+        <v>2.352</v>
       </c>
       <c r="G76">
         <v>0.134</v>
@@ -7626,45 +7626,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M76">
-        <v>0.2088576</v>
+        <v>0.3452736000000001</v>
       </c>
       <c r="N76">
-        <v>0.1048090666666666</v>
+        <v>-0.03160693333333342</v>
       </c>
       <c r="O76">
-        <v>0.02305799466666666</v>
+        <v>-0.006953525333333353</v>
       </c>
       <c r="P76">
-        <v>0.08175107199999998</v>
+        <v>-0.02465340800000007</v>
       </c>
       <c r="Q76">
-        <v>0.374751072</v>
+        <v>0.268346592</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2121500187563328</v>
+        <v>0.2214706580402934</v>
       </c>
       <c r="T76">
-        <v>2.420595464237835</v>
+        <v>2.556222122673022</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.22</v>
+        <v>0.1998608253473959</v>
       </c>
       <c r="W76">
-        <v>0.0702</v>
+        <v>0.1174604308390023</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.501820698249269</v>
+        <v>0.9084582970336179</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7672,22 +7672,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1434629876393251</v>
+        <v>0.1444729876393251</v>
       </c>
       <c r="C77">
-        <v>-0.6087389517885864</v>
+        <v>-0.6565710754931464</v>
       </c>
       <c r="D77">
-        <v>1.609261048211414</v>
+        <v>1.592788924506854</v>
       </c>
       <c r="E77">
-        <v>1.526</v>
+        <v>1.55736</v>
       </c>
       <c r="F77">
-        <v>2.352</v>
+        <v>2.38336</v>
       </c>
       <c r="G77">
         <v>0.134</v>
@@ -7708,37 +7708,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M77">
-        <v>0.3452736000000001</v>
+        <v>0.349877248</v>
       </c>
       <c r="N77">
-        <v>-0.03160693333333342</v>
+        <v>-0.03621058133333338</v>
       </c>
       <c r="O77">
-        <v>-0.006953525333333353</v>
+        <v>-0.007966327893333344</v>
       </c>
       <c r="P77">
-        <v>-0.02465340800000007</v>
+        <v>-0.02824425344000004</v>
       </c>
       <c r="Q77">
-        <v>0.268346592</v>
+        <v>0.26475574656</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2214706580402934</v>
+        <v>0.2287902687919723</v>
       </c>
       <c r="T77">
-        <v>2.556222122673022</v>
+        <v>2.662731377784398</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1998608253473959</v>
+        <v>0.1972310776454566</v>
       </c>
       <c r="W77">
-        <v>0.1174604308390023</v>
+        <v>0.117846477801647</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9084582970336179</v>
+        <v>0.8965048983884388</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7754,22 +7754,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1444729876393251</v>
+        <v>0.1454829876393251</v>
       </c>
       <c r="C78">
-        <v>-0.6565710754931464</v>
+        <v>-0.7040694041272424</v>
       </c>
       <c r="D78">
-        <v>1.592788924506854</v>
+        <v>1.576650595872758</v>
       </c>
       <c r="E78">
-        <v>1.55736</v>
+        <v>1.58872</v>
       </c>
       <c r="F78">
-        <v>2.38336</v>
+        <v>2.41472</v>
       </c>
       <c r="G78">
         <v>0.134</v>
@@ -7790,37 +7790,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M78">
-        <v>0.349877248</v>
+        <v>0.354480896</v>
       </c>
       <c r="N78">
-        <v>-0.03621058133333338</v>
+        <v>-0.0408142293333334</v>
       </c>
       <c r="O78">
-        <v>-0.007966327893333344</v>
+        <v>-0.008979130453333347</v>
       </c>
       <c r="P78">
-        <v>-0.02824425344000004</v>
+        <v>-0.03183509888000005</v>
       </c>
       <c r="Q78">
-        <v>0.26475574656</v>
+        <v>0.26116490112</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2287902687919723</v>
+        <v>0.2367463674351015</v>
       </c>
       <c r="T78">
-        <v>2.662731377784398</v>
+        <v>2.778502307253285</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1972310776454566</v>
+        <v>0.1946696350786324</v>
       </c>
       <c r="W78">
-        <v>0.117846477801647</v>
+        <v>0.1182224975704568</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8965048983884388</v>
+        <v>0.8848619776301474</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7836,22 +7836,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1454829876393251</v>
+        <v>0.1464929876393251</v>
       </c>
       <c r="C79">
-        <v>-0.7040694041272424</v>
+        <v>-0.7512439820751666</v>
       </c>
       <c r="D79">
-        <v>1.576650595872758</v>
+        <v>1.560836017924834</v>
       </c>
       <c r="E79">
-        <v>1.58872</v>
+        <v>1.62008</v>
       </c>
       <c r="F79">
-        <v>2.41472</v>
+        <v>2.44608</v>
       </c>
       <c r="G79">
         <v>0.134</v>
@@ -7872,37 +7872,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M79">
-        <v>0.354480896</v>
+        <v>0.3590845440000001</v>
       </c>
       <c r="N79">
-        <v>-0.0408142293333334</v>
+        <v>-0.04541787733333341</v>
       </c>
       <c r="O79">
-        <v>-0.008979130453333347</v>
+        <v>-0.009991933013333352</v>
       </c>
       <c r="P79">
-        <v>-0.03183509888000005</v>
+        <v>-0.03542594432000006</v>
       </c>
       <c r="Q79">
-        <v>0.26116490112</v>
+        <v>0.25757405568</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2367463674351015</v>
+        <v>0.2454257477730607</v>
       </c>
       <c r="T79">
-        <v>2.778502307253285</v>
+        <v>2.904797866673889</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1946696350786324</v>
+        <v>0.1921738705263423</v>
       </c>
       <c r="W79">
-        <v>0.1182224975704568</v>
+        <v>0.118588875806733</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8848619776301474</v>
+        <v>0.8735175933015558</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7918,22 +7918,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1464929876393251</v>
+        <v>0.1475029876393251</v>
       </c>
       <c r="C80">
-        <v>-0.7512439820751666</v>
+        <v>-0.7981044547229783</v>
       </c>
       <c r="D80">
-        <v>1.560836017924834</v>
+        <v>1.545335545277022</v>
       </c>
       <c r="E80">
-        <v>1.62008</v>
+        <v>1.65144</v>
       </c>
       <c r="F80">
-        <v>2.44608</v>
+        <v>2.47744</v>
       </c>
       <c r="G80">
         <v>0.134</v>
@@ -7954,37 +7954,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M80">
-        <v>0.3590845440000001</v>
+        <v>0.363688192</v>
       </c>
       <c r="N80">
-        <v>-0.04541787733333341</v>
+        <v>-0.05002152533333337</v>
       </c>
       <c r="O80">
-        <v>-0.009991933013333352</v>
+        <v>-0.01100473557333334</v>
       </c>
       <c r="P80">
-        <v>-0.03542594432000006</v>
+        <v>-0.03901678976000003</v>
       </c>
       <c r="Q80">
-        <v>0.25757405568</v>
+        <v>0.25398321024</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2454257477730607</v>
+        <v>0.2549317357622541</v>
       </c>
       <c r="T80">
-        <v>2.904797866673889</v>
+        <v>3.043121574610741</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1921738705263423</v>
+        <v>0.1897412898867683</v>
       </c>
       <c r="W80">
-        <v>0.118588875806733</v>
+        <v>0.1189459786446224</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8735175933015558</v>
+        <v>0.8624604085762198</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8000,22 +8000,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1475029876393251</v>
+        <v>0.1485129876393251</v>
       </c>
       <c r="C81">
-        <v>-0.7981044547229783</v>
+        <v>-0.8446600880756998</v>
       </c>
       <c r="D81">
-        <v>1.545335545277022</v>
+        <v>1.5301399119243</v>
       </c>
       <c r="E81">
-        <v>1.65144</v>
+        <v>1.682800000000001</v>
       </c>
       <c r="F81">
-        <v>2.47744</v>
+        <v>2.5088</v>
       </c>
       <c r="G81">
         <v>0.134</v>
@@ -8036,37 +8036,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M81">
-        <v>0.363688192</v>
+        <v>0.3682918400000001</v>
       </c>
       <c r="N81">
-        <v>-0.05002152533333337</v>
+        <v>-0.05462517333333344</v>
       </c>
       <c r="O81">
-        <v>-0.01100473557333334</v>
+        <v>-0.01201753813333336</v>
       </c>
       <c r="P81">
-        <v>-0.03901678976000003</v>
+        <v>-0.04260763520000008</v>
       </c>
       <c r="Q81">
-        <v>0.25398321024</v>
+        <v>0.2503923647999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2549317357622541</v>
+        <v>0.2653883225503668</v>
       </c>
       <c r="T81">
-        <v>3.043121574610741</v>
+        <v>3.195277653341278</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1897412898867683</v>
+        <v>0.1873695237631837</v>
       </c>
       <c r="W81">
-        <v>0.1189459786446224</v>
+        <v>0.1192941539115646</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8624604085762198</v>
+        <v>0.8516796534690168</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8082,22 +8082,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1485129876393251</v>
+        <v>0.1495229876393251</v>
       </c>
       <c r="C82">
-        <v>-0.8446600880756998</v>
+        <v>-0.8909197872283841</v>
       </c>
       <c r="D82">
-        <v>1.5301399119243</v>
+        <v>1.515240212771616</v>
       </c>
       <c r="E82">
-        <v>1.682800000000001</v>
+        <v>1.71416</v>
       </c>
       <c r="F82">
-        <v>2.5088</v>
+        <v>2.54016</v>
       </c>
       <c r="G82">
         <v>0.134</v>
@@ -8118,37 +8118,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M82">
-        <v>0.3682918400000001</v>
+        <v>0.3728954880000001</v>
       </c>
       <c r="N82">
-        <v>-0.05462517333333344</v>
+        <v>-0.0592288213333334</v>
       </c>
       <c r="O82">
-        <v>-0.01201753813333336</v>
+        <v>-0.01303034069333335</v>
       </c>
       <c r="P82">
-        <v>-0.04260763520000008</v>
+        <v>-0.04619848064000005</v>
       </c>
       <c r="Q82">
-        <v>0.2503923647999999</v>
+        <v>0.24680151936</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2653883225503668</v>
+        <v>0.2769456026845966</v>
       </c>
       <c r="T82">
-        <v>3.195277653341278</v>
+        <v>3.363450161411872</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1873695237631837</v>
+        <v>0.1850563197661074</v>
       </c>
       <c r="W82">
-        <v>0.1192941539115646</v>
+        <v>0.1196337322583354</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8516796534690168</v>
+        <v>0.8411650898459426</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8164,22 +8164,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1495229876393251</v>
+        <v>0.1505329876393251</v>
       </c>
       <c r="C83">
-        <v>-0.8909197872283841</v>
+        <v>-0.9368921137684199</v>
       </c>
       <c r="D83">
-        <v>1.515240212771616</v>
+        <v>1.50062788623158</v>
       </c>
       <c r="E83">
-        <v>1.71416</v>
+        <v>1.745520000000001</v>
       </c>
       <c r="F83">
-        <v>2.54016</v>
+        <v>2.57152</v>
       </c>
       <c r="G83">
         <v>0.134</v>
@@ -8200,37 +8200,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M83">
-        <v>0.3728954880000001</v>
+        <v>0.3774991360000001</v>
       </c>
       <c r="N83">
-        <v>-0.0592288213333334</v>
+        <v>-0.06383246933333347</v>
       </c>
       <c r="O83">
-        <v>-0.01303034069333335</v>
+        <v>-0.01404314325333336</v>
       </c>
       <c r="P83">
-        <v>-0.04619848064000005</v>
+        <v>-0.04978932608000011</v>
       </c>
       <c r="Q83">
-        <v>0.24680151936</v>
+        <v>0.2432106739199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2769456026845966</v>
+        <v>0.2897870250559632</v>
       </c>
       <c r="T83">
-        <v>3.363450161411872</v>
+        <v>3.550308503712531</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1850563197661074</v>
+        <v>0.1827995353787158</v>
       </c>
       <c r="W83">
-        <v>0.1196337322583354</v>
+        <v>0.1199650282064045</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8411650898459426</v>
+        <v>0.8309069789941627</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8246,22 +8246,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1505329876393251</v>
+        <v>0.1515429876393251</v>
       </c>
       <c r="C84">
-        <v>-0.9368921137684199</v>
+        <v>-0.9825853021805302</v>
       </c>
       <c r="D84">
-        <v>1.50062788623158</v>
+        <v>1.48629469781947</v>
       </c>
       <c r="E84">
-        <v>1.745520000000001</v>
+        <v>1.77688</v>
       </c>
       <c r="F84">
-        <v>2.57152</v>
+        <v>2.60288</v>
       </c>
       <c r="G84">
         <v>0.134</v>
@@ -8282,37 +8282,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M84">
-        <v>0.3774991360000001</v>
+        <v>0.3821027840000001</v>
       </c>
       <c r="N84">
-        <v>-0.06383246933333347</v>
+        <v>-0.06843611733333343</v>
       </c>
       <c r="O84">
-        <v>-0.01404314325333336</v>
+        <v>-0.01505594581333335</v>
       </c>
       <c r="P84">
-        <v>-0.04978932608000011</v>
+        <v>-0.05338017152000008</v>
       </c>
       <c r="Q84">
-        <v>0.2432106739199999</v>
+        <v>0.23961982848</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2897870250559632</v>
+        <v>0.3041392030004316</v>
       </c>
       <c r="T84">
-        <v>3.550308503712531</v>
+        <v>3.759150180401504</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1827995353787158</v>
+        <v>0.1805971313380084</v>
       </c>
       <c r="W84">
-        <v>0.1199650282064045</v>
+        <v>0.1202883411195804</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8309069789941627</v>
+        <v>0.8208960515364018</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8328,22 +8328,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1515429876393251</v>
+        <v>0.1525529876393251</v>
       </c>
       <c r="C85">
-        <v>-0.9825853021805302</v>
+        <v>-1.028007275320518</v>
       </c>
       <c r="D85">
-        <v>1.48629469781947</v>
+        <v>1.472232724679482</v>
       </c>
       <c r="E85">
-        <v>1.77688</v>
+        <v>1.80824</v>
       </c>
       <c r="F85">
-        <v>2.60288</v>
+        <v>2.63424</v>
       </c>
       <c r="G85">
         <v>0.134</v>
@@ -8364,37 +8364,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M85">
-        <v>0.3821027840000001</v>
+        <v>0.386706432</v>
       </c>
       <c r="N85">
-        <v>-0.06843611733333343</v>
+        <v>-0.0730397653333334</v>
       </c>
       <c r="O85">
-        <v>-0.01505594581333335</v>
+        <v>-0.01606874837333335</v>
       </c>
       <c r="P85">
-        <v>-0.05338017152000008</v>
+        <v>-0.05697101696000005</v>
       </c>
       <c r="Q85">
-        <v>0.23961982848</v>
+        <v>0.23602898304</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3041392030004316</v>
+        <v>0.3202854031879586</v>
       </c>
       <c r="T85">
-        <v>3.759150180401504</v>
+        <v>3.994097066676598</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1805971313380084</v>
+        <v>0.1784471654887464</v>
       </c>
       <c r="W85">
-        <v>0.1202883411195804</v>
+        <v>0.120603956106252</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8208960515364018</v>
+        <v>0.8111234794943019</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8410,22 +8410,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1525529876393251</v>
+        <v>0.1535629876393251</v>
       </c>
       <c r="C86">
-        <v>-1.028007275320518</v>
+        <v>-1.073165659018852</v>
       </c>
       <c r="D86">
-        <v>1.472232724679482</v>
+        <v>1.458434340981148</v>
       </c>
       <c r="E86">
-        <v>1.80824</v>
+        <v>1.8396</v>
       </c>
       <c r="F86">
-        <v>2.63424</v>
+        <v>2.6656</v>
       </c>
       <c r="G86">
         <v>0.134</v>
@@ -8446,37 +8446,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M86">
-        <v>0.386706432</v>
+        <v>0.3913100800000001</v>
       </c>
       <c r="N86">
-        <v>-0.0730397653333334</v>
+        <v>-0.07764341333333341</v>
       </c>
       <c r="O86">
-        <v>-0.01606874837333335</v>
+        <v>-0.01708155093333335</v>
       </c>
       <c r="P86">
-        <v>-0.05697101696000005</v>
+        <v>-0.06056186240000006</v>
       </c>
       <c r="Q86">
-        <v>0.23602898304</v>
+        <v>0.2324381376</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3202854031879584</v>
+        <v>0.3385844300671557</v>
       </c>
       <c r="T86">
-        <v>3.994097066676596</v>
+        <v>4.260370204455036</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1784471654887464</v>
+        <v>0.1763477870712317</v>
       </c>
       <c r="W86">
-        <v>0.120603956106252</v>
+        <v>0.1209121448579432</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8111234794943019</v>
+        <v>0.8015808503237806</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8492,22 +8492,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1535629876393251</v>
+        <v>0.2030954922603292</v>
       </c>
       <c r="C87">
-        <v>-1.073165659018852</v>
+        <v>-1.56378806187602</v>
       </c>
       <c r="D87">
-        <v>1.458434340981148</v>
+        <v>0.9991719381239798</v>
       </c>
       <c r="E87">
-        <v>1.8396</v>
+        <v>1.87096</v>
       </c>
       <c r="F87">
-        <v>2.6656</v>
+        <v>2.69696</v>
       </c>
       <c r="G87">
         <v>0.134</v>
@@ -8528,45 +8528,45 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M87">
-        <v>0.3913100800000001</v>
+        <v>0.5415495680000001</v>
       </c>
       <c r="N87">
-        <v>-0.07764341333333341</v>
+        <v>-0.2278829013333334</v>
       </c>
       <c r="O87">
-        <v>-0.01708155093333335</v>
+        <v>-0.05013423829333336</v>
       </c>
       <c r="P87">
-        <v>-0.06056186240000006</v>
+        <v>-0.1777486630400001</v>
       </c>
       <c r="Q87">
-        <v>0.2324381376</v>
+        <v>0.11525133696</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3385844300671557</v>
+        <v>0.3743726366505539</v>
       </c>
       <c r="T87">
-        <v>4.260370204455036</v>
+        <v>4.78113221684695</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1763477870712317</v>
+        <v>0.1274244699732946</v>
       </c>
       <c r="W87">
-        <v>0.1209121448579432</v>
+        <v>0.1752131664293624</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8015808503237806</v>
+        <v>0.5792021362422481</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8574,22 +8574,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2030954922603292</v>
+        <v>0.2046454922603293</v>
       </c>
       <c r="C88">
-        <v>-1.56378806187602</v>
+        <v>-1.604897891613423</v>
       </c>
       <c r="D88">
-        <v>0.9991719381239798</v>
+        <v>0.9894221083865766</v>
       </c>
       <c r="E88">
-        <v>1.87096</v>
+        <v>1.90232</v>
       </c>
       <c r="F88">
-        <v>2.69696</v>
+        <v>2.72832</v>
       </c>
       <c r="G88">
         <v>0.134</v>
@@ -8610,37 +8610,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M88">
-        <v>0.5415495680000001</v>
+        <v>0.547846656</v>
       </c>
       <c r="N88">
-        <v>-0.2278829013333334</v>
+        <v>-0.2341799893333334</v>
       </c>
       <c r="O88">
-        <v>-0.05013423829333336</v>
+        <v>-0.05151959765333335</v>
       </c>
       <c r="P88">
-        <v>-0.1777486630400001</v>
+        <v>-0.18266039168</v>
       </c>
       <c r="Q88">
-        <v>0.11525133696</v>
+        <v>0.11033960832</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3743726366505539</v>
+        <v>0.3996474548544427</v>
       </c>
       <c r="T88">
-        <v>4.78113221684695</v>
+        <v>5.148911618142869</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1274244699732946</v>
+        <v>0.1259598208931418</v>
       </c>
       <c r="W88">
-        <v>0.1752131664293624</v>
+        <v>0.1755072679646571</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5792021362422481</v>
+        <v>0.5725446404233717</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8656,22 +8656,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2046454922603293</v>
+        <v>0.2061954922603292</v>
       </c>
       <c r="C89">
-        <v>-1.604897891613423</v>
+        <v>-1.645819284183671</v>
       </c>
       <c r="D89">
-        <v>0.9894221083865766</v>
+        <v>0.9798607158163288</v>
       </c>
       <c r="E89">
-        <v>1.90232</v>
+        <v>1.93368</v>
       </c>
       <c r="F89">
-        <v>2.72832</v>
+        <v>2.75968</v>
       </c>
       <c r="G89">
         <v>0.134</v>
@@ -8692,37 +8692,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M89">
-        <v>0.547846656</v>
+        <v>0.554143744</v>
       </c>
       <c r="N89">
-        <v>-0.2341799893333334</v>
+        <v>-0.2404770773333333</v>
       </c>
       <c r="O89">
-        <v>-0.05151959765333335</v>
+        <v>-0.05290495701333334</v>
       </c>
       <c r="P89">
-        <v>-0.18266039168</v>
+        <v>-0.18757212032</v>
       </c>
       <c r="Q89">
-        <v>0.11033960832</v>
+        <v>0.10542787968</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3996474548544427</v>
+        <v>0.4291347427589797</v>
       </c>
       <c r="T89">
-        <v>5.148911618142869</v>
+        <v>5.577987586321443</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1259598208931418</v>
+        <v>0.1245284592920834</v>
       </c>
       <c r="W89">
-        <v>0.1755072679646571</v>
+        <v>0.1757946853741497</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5725446404233717</v>
+        <v>0.5660384513276516</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8738,22 +8738,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2061954922603292</v>
+        <v>0.2077454922603292</v>
       </c>
       <c r="C90">
-        <v>-1.645819284183671</v>
+        <v>-1.686557650251891</v>
       </c>
       <c r="D90">
-        <v>0.9798607158163288</v>
+        <v>0.9704823497481097</v>
       </c>
       <c r="E90">
-        <v>1.93368</v>
+        <v>1.96504</v>
       </c>
       <c r="F90">
-        <v>2.75968</v>
+        <v>2.79104</v>
       </c>
       <c r="G90">
         <v>0.134</v>
@@ -8774,37 +8774,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M90">
-        <v>0.554143744</v>
+        <v>0.5604408320000001</v>
       </c>
       <c r="N90">
-        <v>-0.2404770773333333</v>
+        <v>-0.2467741653333334</v>
       </c>
       <c r="O90">
-        <v>-0.05290495701333334</v>
+        <v>-0.05429031637333335</v>
       </c>
       <c r="P90">
-        <v>-0.18757212032</v>
+        <v>-0.1924838489600001</v>
       </c>
       <c r="Q90">
-        <v>0.10542787968</v>
+        <v>0.10051615104</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4291347427589797</v>
+        <v>0.4639833557370687</v>
       </c>
       <c r="T90">
-        <v>5.577987586321443</v>
+        <v>6.085077366896119</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1245284592920834</v>
+        <v>0.1231292631202622</v>
       </c>
       <c r="W90">
-        <v>0.1757946853741497</v>
+        <v>0.1760756439654514</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5660384513276516</v>
+        <v>0.5596784687284645</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8820,22 +8820,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2077454922603292</v>
+        <v>0.2092954922603293</v>
       </c>
       <c r="C91">
-        <v>-1.686557650251891</v>
+        <v>-1.727118195302481</v>
       </c>
       <c r="D91">
-        <v>0.9704823497481097</v>
+        <v>0.9612818046975191</v>
       </c>
       <c r="E91">
-        <v>1.96504</v>
+        <v>1.9964</v>
       </c>
       <c r="F91">
-        <v>2.79104</v>
+        <v>2.8224</v>
       </c>
       <c r="G91">
         <v>0.134</v>
@@ -8856,37 +8856,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M91">
-        <v>0.5604408320000001</v>
+        <v>0.56673792</v>
       </c>
       <c r="N91">
-        <v>-0.2467741653333334</v>
+        <v>-0.2530712533333334</v>
       </c>
       <c r="O91">
-        <v>-0.05429031637333335</v>
+        <v>-0.05567567573333334</v>
       </c>
       <c r="P91">
-        <v>-0.1924838489600001</v>
+        <v>-0.1973955776</v>
       </c>
       <c r="Q91">
-        <v>0.10051615104</v>
+        <v>0.09560442240000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4639833557370687</v>
+        <v>0.5058016913107757</v>
       </c>
       <c r="T91">
-        <v>6.085077366896119</v>
+        <v>6.693585103585733</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1231292631202622</v>
+        <v>0.1217611601967037</v>
       </c>
       <c r="W91">
-        <v>0.1760756439654514</v>
+        <v>0.1763503590325019</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5596784687284645</v>
+        <v>0.5534598190759261</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8902,22 +8902,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2092954922603293</v>
+        <v>0.2108454922603293</v>
       </c>
       <c r="C92">
-        <v>-1.727118195302481</v>
+        <v>-1.767505929273737</v>
       </c>
       <c r="D92">
-        <v>0.9612818046975191</v>
+        <v>0.9522540707262638</v>
       </c>
       <c r="E92">
-        <v>1.9964</v>
+        <v>2.027760000000001</v>
       </c>
       <c r="F92">
-        <v>2.8224</v>
+        <v>2.85376</v>
       </c>
       <c r="G92">
         <v>0.134</v>
@@ -8938,37 +8938,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M92">
-        <v>0.56673792</v>
+        <v>0.5730350080000001</v>
       </c>
       <c r="N92">
-        <v>-0.2530712533333334</v>
+        <v>-0.2593683413333334</v>
       </c>
       <c r="O92">
-        <v>-0.05567567573333334</v>
+        <v>-0.05706103509333335</v>
       </c>
       <c r="P92">
-        <v>-0.1973955776</v>
+        <v>-0.2023073062400001</v>
       </c>
       <c r="Q92">
-        <v>0.09560442240000003</v>
+        <v>0.09069269375999997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5058016913107757</v>
+        <v>0.5569129903453063</v>
       </c>
       <c r="T92">
-        <v>6.693585103585733</v>
+        <v>7.437316781761925</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1217611601967037</v>
+        <v>0.1204231254692674</v>
       </c>
       <c r="W92">
-        <v>0.1763503590325019</v>
+        <v>0.1766190364057711</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5534598190759261</v>
+        <v>0.5473778430421246</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8984,22 +8984,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2108454922603293</v>
+        <v>0.2123954922603293</v>
       </c>
       <c r="C93">
-        <v>-1.767505929273737</v>
+        <v>-1.807725675654624</v>
       </c>
       <c r="D93">
-        <v>0.9522540707262638</v>
+        <v>0.943394324345376</v>
       </c>
       <c r="E93">
-        <v>2.027760000000001</v>
+        <v>2.05912</v>
       </c>
       <c r="F93">
-        <v>2.85376</v>
+        <v>2.88512</v>
       </c>
       <c r="G93">
         <v>0.134</v>
@@ -9020,37 +9020,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M93">
-        <v>0.5730350080000001</v>
+        <v>0.579332096</v>
       </c>
       <c r="N93">
-        <v>-0.2593683413333334</v>
+        <v>-0.2656654293333334</v>
       </c>
       <c r="O93">
-        <v>-0.05706103509333335</v>
+        <v>-0.05844639445333334</v>
       </c>
       <c r="P93">
-        <v>-0.2023073062400001</v>
+        <v>-0.20721903488</v>
       </c>
       <c r="Q93">
-        <v>0.09069269375999997</v>
+        <v>0.08578096512</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5569129903453063</v>
+        <v>0.6208021141384698</v>
       </c>
       <c r="T93">
-        <v>7.437316781761925</v>
+        <v>8.366981379482169</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1204231254692674</v>
+        <v>0.1191141784532971</v>
       </c>
       <c r="W93">
-        <v>0.1766190364057711</v>
+        <v>0.176881872966578</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5473778430421246</v>
+        <v>0.5414280838786233</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9066,22 +9066,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2123954922603293</v>
+        <v>0.2139454922603292</v>
       </c>
       <c r="C94">
-        <v>-1.807725675654624</v>
+        <v>-1.847782080078428</v>
       </c>
       <c r="D94">
-        <v>0.943394324345376</v>
+        <v>0.9346979199215725</v>
       </c>
       <c r="E94">
-        <v>2.05912</v>
+        <v>2.09048</v>
       </c>
       <c r="F94">
-        <v>2.88512</v>
+        <v>2.91648</v>
       </c>
       <c r="G94">
         <v>0.134</v>
@@ -9102,37 +9102,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M94">
-        <v>0.579332096</v>
+        <v>0.5856291840000001</v>
       </c>
       <c r="N94">
-        <v>-0.2656654293333334</v>
+        <v>-0.2719625173333334</v>
       </c>
       <c r="O94">
-        <v>-0.05844639445333334</v>
+        <v>-0.05983175381333335</v>
       </c>
       <c r="P94">
-        <v>-0.20721903488</v>
+        <v>-0.2121307635200001</v>
       </c>
       <c r="Q94">
-        <v>0.08578096512</v>
+        <v>0.08086923647999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6208021141384698</v>
+        <v>0.7029452733011082</v>
       </c>
       <c r="T94">
-        <v>8.366981379482169</v>
+        <v>9.562264433693906</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1191141784532971</v>
+        <v>0.1178333808355197</v>
       </c>
       <c r="W94">
-        <v>0.176881872966578</v>
+        <v>0.1771390571282276</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5414280838786233</v>
+        <v>0.5356062765250896</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9148,22 +9148,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2139454922603292</v>
+        <v>0.2154954922603293</v>
       </c>
       <c r="C95">
-        <v>-1.847782080078428</v>
+        <v>-1.887679618445421</v>
       </c>
       <c r="D95">
-        <v>0.9346979199215725</v>
+        <v>0.9261603815545789</v>
       </c>
       <c r="E95">
-        <v>2.09048</v>
+        <v>2.121840000000001</v>
       </c>
       <c r="F95">
-        <v>2.91648</v>
+        <v>2.94784</v>
       </c>
       <c r="G95">
         <v>0.134</v>
@@ -9184,37 +9184,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M95">
-        <v>0.5856291840000001</v>
+        <v>0.591926272</v>
       </c>
       <c r="N95">
-        <v>-0.2719625173333334</v>
+        <v>-0.2782596053333334</v>
       </c>
       <c r="O95">
-        <v>-0.05983175381333335</v>
+        <v>-0.06121711317333334</v>
       </c>
       <c r="P95">
-        <v>-0.2121307635200001</v>
+        <v>-0.21704249216</v>
       </c>
       <c r="Q95">
-        <v>0.08086923647999997</v>
+        <v>0.07595750783999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7029452733011082</v>
+        <v>0.8124694855179599</v>
       </c>
       <c r="T95">
-        <v>9.562264433693906</v>
+        <v>11.1559751726429</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1178333808355197</v>
+        <v>0.1165798342308865</v>
       </c>
       <c r="W95">
-        <v>0.1771390571282276</v>
+        <v>0.177390769286438</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5356062765250896</v>
+        <v>0.5299083374131206</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9230,22 +9230,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2154954922603293</v>
+        <v>0.2170454922603293</v>
       </c>
       <c r="C96">
-        <v>-1.887679618445421</v>
+        <v>-1.927422604604422</v>
       </c>
       <c r="D96">
-        <v>0.9261603815545789</v>
+        <v>0.9177773953955781</v>
       </c>
       <c r="E96">
-        <v>2.121840000000001</v>
+        <v>2.153200000000001</v>
       </c>
       <c r="F96">
-        <v>2.94784</v>
+        <v>2.979200000000001</v>
       </c>
       <c r="G96">
         <v>0.134</v>
@@ -9266,37 +9266,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M96">
-        <v>0.591926272</v>
+        <v>0.5982233600000001</v>
       </c>
       <c r="N96">
-        <v>-0.2782596053333334</v>
+        <v>-0.2845566933333334</v>
       </c>
       <c r="O96">
-        <v>-0.06121711317333334</v>
+        <v>-0.06260247253333336</v>
       </c>
       <c r="P96">
-        <v>-0.21704249216</v>
+        <v>-0.2219542208000001</v>
       </c>
       <c r="Q96">
-        <v>0.07595750783999999</v>
+        <v>0.07104577919999994</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8124694855179599</v>
+        <v>0.9658033826215524</v>
       </c>
       <c r="T96">
-        <v>11.1559751726429</v>
+        <v>13.38717020717148</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1165798342308865</v>
+        <v>0.1153526780810877</v>
       </c>
       <c r="W96">
-        <v>0.177390769286438</v>
+        <v>0.1776371822413176</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5299083374131206</v>
+        <v>0.5243303549140351</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9312,22 +9312,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2170454922603293</v>
+        <v>0.2185954922603293</v>
       </c>
       <c r="C97">
-        <v>-1.927422604604422</v>
+        <v>-1.967015197620911</v>
       </c>
       <c r="D97">
-        <v>0.9177773953955781</v>
+        <v>0.9095448023790893</v>
       </c>
       <c r="E97">
-        <v>2.153200000000001</v>
+        <v>2.18456</v>
       </c>
       <c r="F97">
-        <v>2.979200000000001</v>
+        <v>3.01056</v>
       </c>
       <c r="G97">
         <v>0.134</v>
@@ -9348,37 +9348,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M97">
-        <v>0.5982233600000001</v>
+        <v>0.604520448</v>
       </c>
       <c r="N97">
-        <v>-0.2845566933333334</v>
+        <v>-0.2908537813333334</v>
       </c>
       <c r="O97">
-        <v>-0.06260247253333336</v>
+        <v>-0.06398783189333335</v>
       </c>
       <c r="P97">
-        <v>-0.2219542208000001</v>
+        <v>-0.22686594944</v>
       </c>
       <c r="Q97">
-        <v>0.07104577919999994</v>
+        <v>0.06613405055999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9658033826215524</v>
+        <v>1.195804228276941</v>
       </c>
       <c r="T97">
-        <v>13.38717020717148</v>
+        <v>16.73396275896436</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1153526780810877</v>
+        <v>0.1141510876844097</v>
       </c>
       <c r="W97">
-        <v>0.1776371822413176</v>
+        <v>0.1778784615929705</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5243303549140351</v>
+        <v>0.5188685803836806</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9394,22 +9394,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2185954922603293</v>
+        <v>0.2201454922603293</v>
       </c>
       <c r="C98">
-        <v>-1.967015197620911</v>
+        <v>-2.006461408657457</v>
       </c>
       <c r="D98">
-        <v>0.9095448023790893</v>
+        <v>0.9014585913425429</v>
       </c>
       <c r="E98">
-        <v>2.18456</v>
+        <v>2.215920000000001</v>
       </c>
       <c r="F98">
-        <v>3.01056</v>
+        <v>3.04192</v>
       </c>
       <c r="G98">
         <v>0.134</v>
@@ -9430,37 +9430,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M98">
-        <v>0.604520448</v>
+        <v>0.6108175360000001</v>
       </c>
       <c r="N98">
-        <v>-0.2908537813333334</v>
+        <v>-0.2971508693333335</v>
       </c>
       <c r="O98">
-        <v>-0.06398783189333335</v>
+        <v>-0.06537319125333337</v>
       </c>
       <c r="P98">
-        <v>-0.22686594944</v>
+        <v>-0.2317776780800001</v>
       </c>
       <c r="Q98">
-        <v>0.06613405055999999</v>
+        <v>0.06122232191999993</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.195804228276938</v>
+        <v>1.579138971035917</v>
       </c>
       <c r="T98">
-        <v>16.73396275896431</v>
+        <v>22.31195034528575</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1141510876844097</v>
+        <v>0.1129742723474571</v>
       </c>
       <c r="W98">
-        <v>0.1778784615929705</v>
+        <v>0.1781147661126306</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5188685803836806</v>
+        <v>0.5135194197611683</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9476,22 +9476,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2201454922603293</v>
+        <v>0.2216954922603293</v>
       </c>
       <c r="C99">
-        <v>-2.006461408657457</v>
+        <v>-2.045765107490358</v>
       </c>
       <c r="D99">
-        <v>0.9014585913425429</v>
+        <v>0.8935148925096417</v>
       </c>
       <c r="E99">
-        <v>2.215920000000001</v>
+        <v>2.24728</v>
       </c>
       <c r="F99">
-        <v>3.04192</v>
+        <v>3.07328</v>
       </c>
       <c r="G99">
         <v>0.134</v>
@@ -9512,37 +9512,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M99">
-        <v>0.6108175360000001</v>
+        <v>0.6171146240000001</v>
       </c>
       <c r="N99">
-        <v>-0.2971508693333335</v>
+        <v>-0.3034479573333334</v>
       </c>
       <c r="O99">
-        <v>-0.06537319125333337</v>
+        <v>-0.06675855061333336</v>
       </c>
       <c r="P99">
-        <v>-0.2317776780800001</v>
+        <v>-0.2366894067200001</v>
       </c>
       <c r="Q99">
-        <v>0.06122232191999993</v>
+        <v>0.05631059327999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.579138971035917</v>
+        <v>2.345808456553876</v>
       </c>
       <c r="T99">
-        <v>22.31195034528575</v>
+        <v>33.46792551792863</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1129742723474571</v>
+        <v>0.111821473650034</v>
       </c>
       <c r="W99">
-        <v>0.1781147661126306</v>
+        <v>0.1783462480910732</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5135194197611683</v>
+        <v>0.5082794256819729</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9558,22 +9558,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2216954922603293</v>
+        <v>0.2232454922603292</v>
       </c>
       <c r="C100">
-        <v>-2.045765107490358</v>
+        <v>-2.084930028684739</v>
       </c>
       <c r="D100">
-        <v>0.8935148925096417</v>
+        <v>0.8857099713152616</v>
       </c>
       <c r="E100">
-        <v>2.24728</v>
+        <v>2.27864</v>
       </c>
       <c r="F100">
-        <v>3.07328</v>
+        <v>3.10464</v>
       </c>
       <c r="G100">
         <v>0.134</v>
@@ -9594,37 +9594,37 @@
         <v>0.3136666666666666</v>
       </c>
       <c r="M100">
-        <v>0.6171146240000001</v>
+        <v>0.6234117120000001</v>
       </c>
       <c r="N100">
-        <v>-0.3034479573333334</v>
+        <v>-0.3097450453333335</v>
       </c>
       <c r="O100">
-        <v>-0.06675855061333336</v>
+        <v>-0.06814390997333336</v>
       </c>
       <c r="P100">
-        <v>-0.2366894067200001</v>
+        <v>-0.2416011353600001</v>
       </c>
       <c r="Q100">
-        <v>0.05631059327999999</v>
+        <v>0.05139886463999993</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.345808456553876</v>
+        <v>4.645816913107752</v>
       </c>
       <c r="T100">
-        <v>33.46792551792863</v>
+        <v>66.93585103585725</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.111821473650034</v>
+        <v>0.1106919638151852</v>
       </c>
       <c r="W100">
-        <v>0.1783462480910732</v>
+        <v>0.1785730536659108</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9632,91 +9632,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5082794256819729</v>
+        <v>0.5031452900690236</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2232454922603292</v>
-      </c>
-      <c r="C101">
-        <v>-2.084930028684739</v>
-      </c>
-      <c r="D101">
-        <v>0.8857099713152616</v>
-      </c>
-      <c r="E101">
-        <v>2.27864</v>
-      </c>
-      <c r="F101">
-        <v>3.10464</v>
-      </c>
-      <c r="G101">
-        <v>0.134</v>
-      </c>
-      <c r="H101">
-        <v>2.31</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.6066666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.293</v>
-      </c>
-      <c r="L101">
-        <v>0.3136666666666666</v>
-      </c>
-      <c r="M101">
-        <v>0.6234117120000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.3097450453333335</v>
-      </c>
-      <c r="O101">
-        <v>-0.06814390997333336</v>
-      </c>
-      <c r="P101">
-        <v>-0.2416011353600001</v>
-      </c>
-      <c r="Q101">
-        <v>0.05139886463999993</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.645816913107752</v>
-      </c>
-      <c r="T101">
-        <v>66.93585103585725</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1106919638151852</v>
-      </c>
-      <c r="W101">
-        <v>0.1785730536659108</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5031452900690236</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
